--- a/판매용_템플릿/_판매팩/여행_디럭스/08_검수시나리오.xlsx
+++ b/판매용_템플릿/_판매팩/여행_디럭스/08_검수시나리오.xlsx
@@ -727,7 +727,7 @@
         <v>확인 항목 수</v>
       </c>
       <c r="B5">
-        <v>315</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6">
@@ -735,7 +735,7 @@
         <v xml:space="preserve">  └ 공통(사이트 전체)</v>
       </c>
       <c r="B6">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -803,7 +803,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J316"/>
+  <dimension ref="A1:J323"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -1121,13 +1121,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>이미지 자리의 비율</v>
+        <v>거르는 단추 — 필터·정렬·탭이 목록을 실제로 바꾸는지</v>
       </c>
       <c r="G10" t="str">
-        <v>'400×400' 처럼 크기가 적힌 이미지 자리가 실제로 그 비율인지 본다.</v>
+        <v>필터 칩을 눌러 목록이 줄어드는지 세어 본다. 칩에 개수가 적혀 있으면(예: 기본 교육 2) 그 수만큼만 남는지 센다. 정렬도 바꿔 보고, 아무것도 안 남는 조건도 눌러 본다. ⚠ 화면을 «보는» 것으로는 안 잡힌다 — 반드시 눌러서 목록 개수를 세어야 한다.</v>
       </c>
       <c r="H10" t="str">
-        <v>적힌 대로 보인다. 목록 안에서 늘어나 타원이 되지 않는다.</v>
+        <v>색만 바뀌지 않고 «보이는 항목»이 달라진다. 적힌 개수와 실제 개수가 같다. 하나도 안 남으면 「결과가 없습니다」가 나온다.</v>
       </c>
       <c r="I10" t="str">
         <v/>
@@ -1153,13 +1153,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>공통 요소가 모든 화면에서 같은지</v>
+        <v>썸네일 · 배너 · 겹쳐 놓은 단추가 정말 눌리는지</v>
       </c>
       <c r="G11" t="str">
-        <v>여러 화면을 오가며 헤더·푸터·버튼 모양이 같은지 본다.</v>
+        <v>카드 썸네일과 배너를 하나씩 눌러 어디로 가는지 본다. 사진 위에 얹은 단추(찜 하트·빠른 담기)는 그 자리에서 `document.elementFromPoint(x, y)` 로 맨 위에 무엇이 있는지 본다. ⚠ 그림이라 눌러 보기를 잊기 쉽다.</v>
       </c>
       <c r="H11" t="str">
-        <v>화면마다 다시 만든 흔적 없이 같은 모습이다.</v>
+        <v>썸네일·배너가 모두 어딘가로 간다. 겹쳐 놓은 단추를 누르면 그 단추가 눌리지, 밑에 깔린 링크로 넘어가지 않는다.</v>
       </c>
       <c r="I11" t="str">
         <v/>
@@ -1185,13 +1185,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>좁은 화면(모바일)에서 가로 스크롤</v>
+        <v>쪽 번호가 걸러진 결과를 따라가는지</v>
       </c>
       <c r="G12" t="str">
-        <v>브라우저 폭을 375px로 좁혀 화면을 훑는다.</v>
+        <v>조건을 걸어 목록을 줄인 뒤 쪽 번호를 본다. 3쪽을 보다가 조건을 바꿔 본다.</v>
       </c>
       <c r="H12" t="str">
-        <v>가로 스크롤이 생기지 않고, 내용이 화면 밖으로 나가지 않는다.</v>
+        <v>한 쪽에 다 들어가면 쪽 번호가 사라진다. 조건을 바꾸면 1쪽으로 돌아간다. 쪽을 누르면 목록이 실제로 달라진다.</v>
       </c>
       <c r="I12" t="str">
         <v/>
@@ -1202,28 +1202,28 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B13" t="str">
-        <v>홈</v>
+        <v/>
       </c>
       <c r="C13" t="str">
-        <v>홈</v>
+        <v/>
       </c>
       <c r="D13" t="str">
-        <v>HO-01</v>
+        <v/>
       </c>
       <c r="E13" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F13" t="str">
-        <v>여행지 검색창이 얹힌 히어로 배너</v>
+        <v>화면끼리 숫자와 고른 값이 맞는지</v>
       </c>
       <c r="G13" t="str">
-        <v>'홈'의 여행지 검색창이 얹힌 히어로 배너에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>수량·옵션·할부·기간을 골라 놓고 다음 화면에서 그대로 있는지 본다. 같은 것이 나오는 화면 둘을 나란히 열어 진도·개수·합계·N/M·남은 것을 대 본다. 「이번 주」·「D-3」은 오늘 날짜로 다시 센다.</v>
       </c>
       <c r="H13" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>앞 화면에서 고른 값이 뒤 화면에 그대로 있다. 같은 값이 화면마다 같다. 합계가 항목의 합과 맞고, 12/18이면 남은 것은 6이다.</v>
       </c>
       <c r="I13" t="str">
         <v/>
@@ -1234,7 +1234,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B14" t="str">
         <v/>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>인기 여행지 바로가기 6곳</v>
+        <v>가게 정보를 바꿨을 때 옛 이름이 남는 곳</v>
       </c>
       <c r="G14" t="str">
-        <v>'홈'에서 인기 여행지 바로가기 6곳을 눌러 본다.</v>
+        <v>데이터 파일의 상호를 다른 이름으로 바꾸고 사이트를 다시 연다. 화면·머리말·꼬리말은 물론 브라우저 «탭 제목»까지 본다.</v>
       </c>
       <c r="H14" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>어느 화면에도 옛 이름이 남지 않는다. 탭 제목과 검색 설명까지 새 이름으로 바뀐다.</v>
       </c>
       <c r="I14" t="str">
         <v/>
@@ -1266,7 +1266,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B15" t="str">
         <v/>
@@ -1281,13 +1281,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>이번 주 인기 상품 8개 카드</v>
+        <v>이미지 자리의 비율</v>
       </c>
       <c r="G15" t="str">
-        <v>'홈' 화면을 열고 이번 주 인기 상품 8개 카드가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'400×400' 처럼 크기가 적힌 이미지 자리가 실제로 그 비율인지 본다.</v>
       </c>
       <c r="H15" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>적힌 대로 보인다. 목록 안에서 늘어나 타원이 되지 않는다.</v>
       </c>
       <c r="I15" t="str">
         <v/>
@@ -1298,7 +1298,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B16" t="str">
         <v/>
@@ -1313,13 +1313,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>특가</v>
+        <v>공통 요소가 모든 화면에서 같은지</v>
       </c>
       <c r="G16" t="str">
-        <v>'홈' 화면에서 특가가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>여러 화면을 오가며 헤더·푸터·버튼 모양이 같은지 본다.</v>
       </c>
       <c r="H16" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>화면마다 다시 만든 흔적 없이 같은 모습이다.</v>
       </c>
       <c r="I16" t="str">
         <v/>
@@ -1330,7 +1330,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B17" t="str">
         <v/>
@@ -1345,13 +1345,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>마감임박 상품 캐러셀</v>
+        <v>읽기 폭이 한 값인지 — 글이 주인공인 화면들</v>
       </c>
       <c r="G17" t="str">
-        <v>'홈'에서 마감임박 상품 캐러셀의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>상세 본문·안내·약관처럼 글이 긴 화면 서넛을 나란히 열어, 글줄이 시작하고 끝나는 자리가 같은지 본다.</v>
       </c>
       <c r="H17" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>화면마다 본문 폭이 같다. 어떤 화면은 넓고 어떤 화면은 좁아 서로 다른 사이트처럼 보이지 않는다.</v>
       </c>
       <c r="I17" t="str">
         <v/>
@@ -1362,7 +1362,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B18" t="str">
         <v/>
@@ -1377,13 +1377,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>패스 상품 안내 배너</v>
+        <v>줄어드는 지점이 두 곳뿐인지</v>
       </c>
       <c r="G18" t="str">
-        <v>'홈'에서 패스 상품 안내 배너를 눌러 본다.</v>
+        <v>브라우저 폭을 천천히 줄이며 칸 수가 바뀌는 지점을 세어 본다.</v>
       </c>
       <c r="H18" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>태블릿 가로(1024px)와 세로(720px), 두 곳에서만 바뀐다. 그 사이에 지어낸 지점이 없다.</v>
       </c>
       <c r="I18" t="str">
         <v/>
@@ -1394,7 +1394,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B19" t="str">
         <v/>
@@ -1409,13 +1409,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>테마별 추천 탭(투어/입장권/교통)</v>
+        <v>좁은 화면(모바일)에서 가로 스크롤</v>
       </c>
       <c r="G19" t="str">
-        <v>'홈'에서 테마별 추천 탭(투어/입장권/교통)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>브라우저 폭을 375px로 좁혀 화면을 훑는다.</v>
       </c>
       <c r="H19" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>가로 스크롤이 생기지 않고, 내용이 화면 밖으로 나가지 않는다.</v>
       </c>
       <c r="I19" t="str">
         <v/>
@@ -1429,25 +1429,25 @@
         <v>SCN-001</v>
       </c>
       <c r="B20" t="str">
-        <v/>
+        <v>홈</v>
       </c>
       <c r="C20" t="str">
-        <v/>
+        <v>홈</v>
       </c>
       <c r="D20" t="str">
-        <v/>
+        <v>HO-01</v>
       </c>
       <c r="E20" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F20" t="str">
-        <v>실제 후기 슬라이드 5개</v>
+        <v>여행지 검색창이 얹힌 히어로 배너</v>
       </c>
       <c r="G20" t="str">
-        <v>'홈' 화면을 열고 실제 후기 슬라이드 5개가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'홈'의 여행지 검색창이 얹힌 히어로 배너에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H20" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -1473,13 +1473,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>현지 라운지</v>
+        <v>인기 여행지 바로가기 6곳</v>
       </c>
       <c r="G21" t="str">
-        <v>'홈' 화면에서 현지 라운지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'홈'에서 인기 여행지 바로가기 6곳을 눌러 본다.</v>
       </c>
       <c r="H21" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I21" t="str">
         <v/>
@@ -1505,13 +1505,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>고객센터 안내</v>
+        <v>이번 주 인기 상품 8개 카드</v>
       </c>
       <c r="G22" t="str">
-        <v>'홈' 화면에서 고객센터 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'홈' 화면을 열고 이번 주 인기 상품 8개 카드가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H22" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I22" t="str">
         <v/>
@@ -1537,13 +1537,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>여행 팁 콘텐츠 4개</v>
+        <v>특가</v>
       </c>
       <c r="G23" t="str">
-        <v>'홈' 화면을 열고 여행 팁 콘텐츠 4개가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'홈' 화면에서 특가가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H23" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I23" t="str">
         <v/>
@@ -1569,13 +1569,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>하단 앱</v>
+        <v>마감임박 상품 캐러셀</v>
       </c>
       <c r="G24" t="str">
-        <v>'홈' 화면에서 하단 앱이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'홈'에서 마감임박 상품 캐러셀의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H24" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I24" t="str">
         <v/>
@@ -1601,13 +1601,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>카톡 채널 안내</v>
+        <v>패스 상품 안내 배너</v>
       </c>
       <c r="G25" t="str">
-        <v>'홈' 화면에서 카톡 채널 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'홈'에서 패스 상품 안내 배너를 눌러 본다.</v>
       </c>
       <c r="H25" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I25" t="str">
         <v/>
@@ -1618,28 +1618,28 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B26" t="str">
-        <v>홈</v>
+        <v/>
       </c>
       <c r="C26" t="str">
-        <v>여행지 홈</v>
+        <v/>
       </c>
       <c r="D26" t="str">
-        <v>HO-02</v>
+        <v/>
       </c>
       <c r="E26" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F26" t="str">
-        <v>여행지 대표 사진과 한 줄 소개</v>
+        <v>테마별 추천 탭(투어/입장권/교통)</v>
       </c>
       <c r="G26" t="str">
-        <v>'여행지 홈' 화면에서 여행지 대표 사진과 한 줄 소개가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'홈'에서 테마별 추천 탭(투어/입장권/교통)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H26" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I26" t="str">
         <v/>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B27" t="str">
         <v/>
@@ -1665,10 +1665,10 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>이 도시 인기 상품 8개</v>
+        <v>실제 후기 슬라이드 5개</v>
       </c>
       <c r="G27" t="str">
-        <v>'여행지 홈' 화면을 열고 이 도시 인기 상품 8개가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'홈' 화면을 열고 실제 후기 슬라이드 5개가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H27" t="str">
         <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B28" t="str">
         <v/>
@@ -1697,13 +1697,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>카테고리 필터(투어/입장권/교통/패스)</v>
+        <v>현지 라운지</v>
       </c>
       <c r="G28" t="str">
-        <v>'여행지 홈'에서 카테고리 필터(투어/입장권/교통/패스)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'홈' 화면에서 현지 라운지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H28" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I28" t="str">
         <v/>
@@ -1714,7 +1714,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B29" t="str">
         <v/>
@@ -1729,10 +1729,10 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>이 도시 전용 패스 안내</v>
+        <v>고객센터 안내</v>
       </c>
       <c r="G29" t="str">
-        <v>'여행지 홈' 화면에서 이 도시 전용 패스 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'홈' 화면에서 고객센터 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H29" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -1746,7 +1746,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B30" t="str">
         <v/>
@@ -1761,13 +1761,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>추천 일정 3코스</v>
+        <v>여행 팁 콘텐츠 4개</v>
       </c>
       <c r="G30" t="str">
-        <v>'여행지 홈' 화면에서 추천 일정 3코스가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'홈' 화면을 열고 여행 팁 콘텐츠 4개가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H30" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I30" t="str">
         <v/>
@@ -1778,7 +1778,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B31" t="str">
         <v/>
@@ -1793,13 +1793,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>현지 쿠폰 제휴처 목록</v>
+        <v>하단 앱</v>
       </c>
       <c r="G31" t="str">
-        <v>'여행지 홈'의 현지 쿠폰 제휴처 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'홈' 화면에서 하단 앱이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H31" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I31" t="str">
         <v/>
@@ -1810,7 +1810,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B32" t="str">
         <v/>
@@ -1825,10 +1825,10 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>날씨</v>
+        <v>카톡 채널 안내</v>
       </c>
       <c r="G32" t="str">
-        <v>'여행지 홈' 화면에서 날씨가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'홈' 화면에서 카톡 채널 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H32" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -1845,22 +1845,22 @@
         <v>SCN-002</v>
       </c>
       <c r="B33" t="str">
-        <v/>
+        <v>홈</v>
       </c>
       <c r="C33" t="str">
-        <v/>
+        <v>여행지 홈</v>
       </c>
       <c r="D33" t="str">
-        <v/>
+        <v>HO-02</v>
       </c>
       <c r="E33" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F33" t="str">
-        <v>시차</v>
+        <v>여행지 대표 사진과 한 줄 소개</v>
       </c>
       <c r="G33" t="str">
-        <v>'여행지 홈' 화면에서 시차가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'여행지 홈' 화면에서 여행지 대표 사진과 한 줄 소개가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H33" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -1889,13 +1889,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>팁 정보 카드</v>
+        <v>이 도시 인기 상품 8개</v>
       </c>
       <c r="G34" t="str">
-        <v>'여행지 홈'의 팁 정보 카드를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'여행지 홈' 화면을 열고 이 도시 인기 상품 8개가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H34" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I34" t="str">
         <v/>
@@ -1921,13 +1921,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>이 도시 후기 모음</v>
+        <v>카테고리 필터(투어/입장권/교통/패스)</v>
       </c>
       <c r="G35" t="str">
-        <v>'여행지 홈' 화면에서 이 도시 후기 모음이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'여행지 홈'에서 카테고리 필터(투어/입장권/교통/패스)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H35" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I35" t="str">
         <v/>
@@ -1938,28 +1938,28 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B36" t="str">
-        <v>홈</v>
+        <v/>
       </c>
       <c r="C36" t="str">
-        <v>검색 결과</v>
+        <v/>
       </c>
       <c r="D36" t="str">
-        <v>HO-03</v>
+        <v/>
       </c>
       <c r="E36" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F36" t="str">
-        <v>검색어와 결과 수 표시</v>
+        <v>이 도시 전용 패스 안내</v>
       </c>
       <c r="G36" t="str">
-        <v>'검색 결과'에서 검색어와 결과 수 표시의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'여행지 홈' 화면에서 이 도시 전용 패스 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H36" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I36" t="str">
         <v/>
@@ -1970,7 +1970,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B37" t="str">
         <v/>
@@ -1985,13 +1985,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>필터(여행지·카테고리·가격대·평점·소요시간)</v>
+        <v>추천 일정 3코스</v>
       </c>
       <c r="G37" t="str">
-        <v>'검색 결과'에서 필터(여행지·카테고리·가격대·평점·소요시간)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'여행지 홈' 화면에서 추천 일정 3코스가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H37" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I37" t="str">
         <v/>
@@ -2002,7 +2002,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B38" t="str">
         <v/>
@@ -2017,13 +2017,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>정렬(인기순/낮은가격순/평점순)</v>
+        <v>현지 쿠폰 제휴처 목록</v>
       </c>
       <c r="G38" t="str">
-        <v>'검색 결과'에서 정렬(인기순/낮은가격순/평점순)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'여행지 홈'의 현지 쿠폰 제휴처 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H38" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I38" t="str">
         <v/>
@@ -2034,7 +2034,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B39" t="str">
         <v/>
@@ -2049,13 +2049,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>상품 카드 목록</v>
+        <v>날씨</v>
       </c>
       <c r="G39" t="str">
-        <v>'검색 결과'의 상품 카드 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'여행지 홈' 화면에서 날씨가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H39" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I39" t="str">
         <v/>
@@ -2066,7 +2066,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B40" t="str">
         <v/>
@@ -2081,10 +2081,10 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>지도 보기 전환</v>
+        <v>시차</v>
       </c>
       <c r="G40" t="str">
-        <v>'검색 결과' 화면에서 지도 보기 전환이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'여행지 홈' 화면에서 시차가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H40" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2098,7 +2098,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B41" t="str">
         <v/>
@@ -2113,13 +2113,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>무한 스크롤</v>
+        <v>팁 정보 카드</v>
       </c>
       <c r="G41" t="str">
-        <v>'검색 결과' 화면에서 무한 스크롤이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'여행지 홈'의 팁 정보 카드를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H41" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I41" t="str">
         <v/>
@@ -2130,28 +2130,28 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>SCN-004</v>
+        <v>SCN-002</v>
       </c>
       <c r="B42" t="str">
-        <v>홈</v>
+        <v/>
       </c>
       <c r="C42" t="str">
-        <v>검색 결과 없음</v>
+        <v/>
       </c>
       <c r="D42" t="str">
-        <v>HO-04</v>
+        <v/>
       </c>
       <c r="E42" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F42" t="str">
-        <v>검색어를 포함한 안내 문구</v>
+        <v>이 도시 후기 모음</v>
       </c>
       <c r="G42" t="str">
-        <v>일부러 그 상황을 만들어 '검색 결과 없음' 화면이 나오게 한 뒤, 검색어를 포함한 안내 문구가 보이는지 확인한다.</v>
+        <v>'여행지 홈' 화면에서 이 도시 후기 모음이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H42" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I42" t="str">
         <v/>
@@ -2162,28 +2162,28 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>SCN-004</v>
+        <v>SCN-003</v>
       </c>
       <c r="B43" t="str">
-        <v/>
+        <v>홈</v>
       </c>
       <c r="C43" t="str">
-        <v/>
+        <v>검색 결과</v>
       </c>
       <c r="D43" t="str">
-        <v/>
+        <v>HO-03</v>
       </c>
       <c r="E43" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F43" t="str">
-        <v>필터 초기화 버튼</v>
+        <v>검색어와 결과 수 표시</v>
       </c>
       <c r="G43" t="str">
-        <v>일부러 그 상황을 만들어 '검색 결과 없음' 화면이 나오게 한 뒤, 필터 초기화 버튼이 보이는지 확인한다.</v>
+        <v>'검색 결과'에서 검색어와 결과 수 표시의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H43" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I43" t="str">
         <v/>
@@ -2194,7 +2194,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>SCN-004</v>
+        <v>SCN-003</v>
       </c>
       <c r="B44" t="str">
         <v/>
@@ -2209,13 +2209,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>추천 상품 4개</v>
+        <v>필터(여행지·카테고리·가격대·평점·소요시간)</v>
       </c>
       <c r="G44" t="str">
-        <v>일부러 그 상황을 만들어 '검색 결과 없음' 화면이 나오게 한 뒤, 추천 상품 4개가 보이는지 확인한다.</v>
+        <v>'검색 결과'에서 필터(여행지·카테고리·가격대·평점·소요시간)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H44" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I44" t="str">
         <v/>
@@ -2226,7 +2226,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>SCN-004</v>
+        <v>SCN-003</v>
       </c>
       <c r="B45" t="str">
         <v/>
@@ -2241,13 +2241,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>인기 검색어 칩</v>
+        <v>정렬(인기순/낮은가격순/평점순)</v>
       </c>
       <c r="G45" t="str">
-        <v>일부러 그 상황을 만들어 '검색 결과 없음' 화면이 나오게 한 뒤, 인기 검색어 칩이 보이는지 확인한다.</v>
+        <v>'검색 결과'에서 정렬(인기순/낮은가격순/평점순)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H45" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I45" t="str">
         <v/>
@@ -2258,28 +2258,28 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>SCN-005</v>
+        <v>SCN-003</v>
       </c>
       <c r="B46" t="str">
-        <v>홈</v>
+        <v/>
       </c>
       <c r="C46" t="str">
-        <v>테마 기획전</v>
+        <v/>
       </c>
       <c r="D46" t="str">
-        <v>HO-05</v>
+        <v/>
       </c>
       <c r="E46" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F46" t="str">
-        <v>기획전 대표 배너(테마명·기간·혜택 문구)</v>
+        <v>상품 카드 목록</v>
       </c>
       <c r="G46" t="str">
-        <v>'테마 기획전'에서 기획전 대표 배너(테마명·기간·혜택 문구)를 눌러 본다.</v>
+        <v>'검색 결과'의 상품 카드 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H46" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I46" t="str">
         <v/>
@@ -2290,7 +2290,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>SCN-005</v>
+        <v>SCN-003</v>
       </c>
       <c r="B47" t="str">
         <v/>
@@ -2305,13 +2305,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>테마 탭(가족여행·미식·야경·액티비티·근교 당일)</v>
+        <v>지도 보기 전환</v>
       </c>
       <c r="G47" t="str">
-        <v>'테마 기획전'에서 테마 탭(가족여행·미식·야경·액티비티·근교 당일)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'검색 결과' 화면에서 지도 보기 전환이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H47" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I47" t="str">
         <v/>
@@ -2322,7 +2322,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>SCN-005</v>
+        <v>SCN-003</v>
       </c>
       <c r="B48" t="str">
         <v/>
@@ -2337,10 +2337,10 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>기획전 소개 문구와 큐레이터 코멘트</v>
+        <v>무한 스크롤</v>
       </c>
       <c r="G48" t="str">
-        <v>'테마 기획전' 화면에서 기획전 소개 문구와 큐레이터 코멘트가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'검색 결과' 화면에서 무한 스크롤이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H48" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2354,28 +2354,28 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B49" t="str">
-        <v/>
+        <v>홈</v>
       </c>
       <c r="C49" t="str">
-        <v/>
+        <v>검색 결과 없음</v>
       </c>
       <c r="D49" t="str">
-        <v/>
+        <v>HO-04</v>
       </c>
       <c r="E49" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F49" t="str">
-        <v>남은 기간 카운트다운</v>
+        <v>검색어를 포함한 안내 문구</v>
       </c>
       <c r="G49" t="str">
-        <v>'테마 기획전'의 남은 기간 카운트다운이 실제 데이터와 같은지 대조한다.</v>
+        <v>일부러 그 상황을 만들어 '검색 결과 없음' 화면이 나오게 한 뒤, 검색어를 포함한 안내 문구가 보이는지 확인한다.</v>
       </c>
       <c r="H49" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I49" t="str">
         <v/>
@@ -2386,7 +2386,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B50" t="str">
         <v/>
@@ -2401,13 +2401,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>기획전 전용 쿠폰 다운로드</v>
+        <v>필터 초기화 버튼</v>
       </c>
       <c r="G50" t="str">
-        <v>'테마 기획전' 화면에서 기획전 전용 쿠폰 다운로드가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '검색 결과 없음' 화면이 나오게 한 뒤, 필터 초기화 버튼이 보이는지 확인한다.</v>
       </c>
       <c r="H50" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -2418,7 +2418,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B51" t="str">
         <v/>
@@ -2433,13 +2433,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>대상 상품 카드 그리드와 기획전가 표시</v>
+        <v>추천 상품 4개</v>
       </c>
       <c r="G51" t="str">
-        <v>'테마 기획전'의 대상 상품 카드 그리드와 기획전가 표시를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '검색 결과 없음' 화면이 나오게 한 뒤, 추천 상품 4개가 보이는지 확인한다.</v>
       </c>
       <c r="H51" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -2450,7 +2450,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B52" t="str">
         <v/>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>여행지별 묶음 보기</v>
+        <v>인기 검색어 칩</v>
       </c>
       <c r="G52" t="str">
-        <v>'테마 기획전' 화면에서 여행지별 묶음 보기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '검색 결과 없음' 화면이 나오게 한 뒤, 인기 검색어 칩이 보이는지 확인한다.</v>
       </c>
       <c r="H52" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -2485,25 +2485,25 @@
         <v>SCN-005</v>
       </c>
       <c r="B53" t="str">
-        <v/>
+        <v>홈</v>
       </c>
       <c r="C53" t="str">
-        <v/>
+        <v>테마 기획전</v>
       </c>
       <c r="D53" t="str">
-        <v/>
+        <v>HO-05</v>
       </c>
       <c r="E53" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F53" t="str">
-        <v>정렬(추천순·낮은 가격순·할인율순)</v>
+        <v>기획전 대표 배너(테마명·기간·혜택 문구)</v>
       </c>
       <c r="G53" t="str">
-        <v>'테마 기획전'에서 정렬(추천순·낮은 가격순·할인율순)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'테마 기획전'에서 기획전 대표 배너(테마명·기간·혜택 문구)를 눌러 본다.</v>
       </c>
       <c r="H53" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I53" t="str">
         <v/>
@@ -2529,13 +2529,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>함께 보면 좋은 기획전 3개</v>
+        <v>테마 탭(가족여행·미식·야경·액티비티·근교 당일)</v>
       </c>
       <c r="G54" t="str">
-        <v>'테마 기획전' 화면을 열고 함께 보면 좋은 기획전 3개가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'테마 기획전'에서 테마 탭(가족여행·미식·야경·액티비티·근교 당일)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H54" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I54" t="str">
         <v/>
@@ -2561,10 +2561,10 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>종료된 기획전 안내와 다음 기획전 예고</v>
+        <v>기획전 소개 문구와 큐레이터 코멘트</v>
       </c>
       <c r="G55" t="str">
-        <v>'테마 기획전' 화면에서 종료된 기획전 안내와 다음 기획전 예고가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'테마 기획전' 화면에서 기획전 소개 문구와 큐레이터 코멘트가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H55" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2578,28 +2578,28 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B56" t="str">
-        <v>상품</v>
+        <v/>
       </c>
       <c r="C56" t="str">
-        <v>상품 목록</v>
+        <v/>
       </c>
       <c r="D56" t="str">
-        <v>PR-01</v>
+        <v/>
       </c>
       <c r="E56" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F56" t="str">
-        <v>카테고리 탭</v>
+        <v>남은 기간 카운트다운</v>
       </c>
       <c r="G56" t="str">
-        <v>'상품 목록'에서 카테고리 탭의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'테마 기획전'의 남은 기간 카운트다운이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H56" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I56" t="str">
         <v/>
@@ -2610,7 +2610,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B57" t="str">
         <v/>
@@ -2625,13 +2625,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>필터(가격·평점·소요시간·언어·즉시확정)</v>
+        <v>기획전 전용 쿠폰 다운로드</v>
       </c>
       <c r="G57" t="str">
-        <v>'상품 목록'에서 필터(가격·평점·소요시간·언어·즉시확정)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'테마 기획전' 화면에서 기획전 전용 쿠폰 다운로드가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H57" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I57" t="str">
         <v/>
@@ -2642,7 +2642,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B58" t="str">
         <v/>
@@ -2657,13 +2657,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>정렬</v>
+        <v>대상 상품 카드 그리드와 기획전가 표시</v>
       </c>
       <c r="G58" t="str">
-        <v>'상품 목록'에서 정렬의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'테마 기획전'의 대상 상품 카드 그리드와 기획전가 표시를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H58" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I58" t="str">
         <v/>
@@ -2674,7 +2674,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B59" t="str">
         <v/>
@@ -2689,13 +2689,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>상품 카드 그리드</v>
+        <v>여행지별 묶음 보기</v>
       </c>
       <c r="G59" t="str">
-        <v>'상품 목록'의 상품 카드 그리드를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'테마 기획전' 화면에서 여행지별 묶음 보기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H59" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I59" t="str">
         <v/>
@@ -2706,7 +2706,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B60" t="str">
         <v/>
@@ -2721,13 +2721,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>마감임박 배지</v>
+        <v>정렬(추천순·낮은 가격순·할인율순)</v>
       </c>
       <c r="G60" t="str">
-        <v>'상품 목록' 화면에서 마감임박 배지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'테마 기획전'에서 정렬(추천순·낮은 가격순·할인율순)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H60" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I60" t="str">
         <v/>
@@ -2738,7 +2738,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B61" t="str">
         <v/>
@@ -2753,13 +2753,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>찜하기</v>
+        <v>함께 보면 좋은 기획전 3개</v>
       </c>
       <c r="G61" t="str">
-        <v>'상품 목록' 화면에서 찜하기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'테마 기획전' 화면을 열고 함께 보면 좋은 기획전 3개가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H61" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I61" t="str">
         <v/>
@@ -2770,7 +2770,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B62" t="str">
         <v/>
@@ -2785,13 +2785,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>페이지네이션</v>
+        <v>종료된 기획전 안내와 다음 기획전 예고</v>
       </c>
       <c r="G62" t="str">
-        <v>'상품 목록'에서 페이지네이션의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'테마 기획전' 화면에서 종료된 기획전 안내와 다음 기획전 예고가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H62" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I62" t="str">
         <v/>
@@ -2802,28 +2802,28 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B63" t="str">
         <v>상품</v>
       </c>
       <c r="C63" t="str">
-        <v>상품 상세</v>
+        <v>상품 목록</v>
       </c>
       <c r="D63" t="str">
-        <v>PR-02</v>
+        <v>PR-01</v>
       </c>
       <c r="E63" t="str">
         <v>기본</v>
       </c>
       <c r="F63" t="str">
-        <v>사진 갤러리</v>
+        <v>카테고리 탭</v>
       </c>
       <c r="G63" t="str">
-        <v>'상품 상세'의 사진 갤러리를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'상품 목록'에서 카테고리 탭의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H63" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I63" t="str">
         <v/>
@@ -2834,7 +2834,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B64" t="str">
         <v/>
@@ -2849,13 +2849,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>상품명과 별점</v>
+        <v>필터(가격·평점·소요시간·언어·즉시확정)</v>
       </c>
       <c r="G64" t="str">
-        <v>'상품 상세' 화면에서 상품명과 별점이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 목록'에서 필터(가격·평점·소요시간·언어·즉시확정)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H64" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I64" t="str">
         <v/>
@@ -2866,7 +2866,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B65" t="str">
         <v/>
@@ -2881,13 +2881,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>후기 수</v>
+        <v>정렬</v>
       </c>
       <c r="G65" t="str">
-        <v>'상품 상세' 화면에서 후기 수가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 목록'에서 정렬의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H65" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I65" t="str">
         <v/>
@@ -2898,7 +2898,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B66" t="str">
         <v/>
@@ -2913,13 +2913,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>핵심 정보 배지(소요시간·언어·즉시확정·미팅장소)</v>
+        <v>상품 카드 그리드</v>
       </c>
       <c r="G66" t="str">
-        <v>'상품 상세'의 핵심 정보 배지(소요시간·언어·즉시확정·미팅장소)가 실제 데이터와 같은지 대조한다.</v>
+        <v>'상품 목록'의 상품 카드 그리드를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H66" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I66" t="str">
         <v/>
@@ -2930,7 +2930,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B67" t="str">
         <v/>
@@ -2945,13 +2945,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>가격과 할인율</v>
+        <v>마감임박 배지</v>
       </c>
       <c r="G67" t="str">
-        <v>'상품 상세'의 가격과 할인율이 실제 데이터와 같은지 대조한다.</v>
+        <v>'상품 목록' 화면에서 마감임박 배지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H67" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I67" t="str">
         <v/>
@@ -2962,7 +2962,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B68" t="str">
         <v/>
@@ -2977,10 +2977,10 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>상품 소개 본문</v>
+        <v>찜하기</v>
       </c>
       <c r="G68" t="str">
-        <v>'상품 상세' 화면에서 상품 소개 본문이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 목록' 화면에서 찜하기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H68" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2994,7 +2994,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B69" t="str">
         <v/>
@@ -3009,13 +3009,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>코스 일정 타임라인</v>
+        <v>페이지네이션</v>
       </c>
       <c r="G69" t="str">
-        <v>'상품 상세' 화면에서 코스 일정 타임라인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 목록'에서 페이지네이션의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H69" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I69" t="str">
         <v/>
@@ -3029,25 +3029,25 @@
         <v>SCN-007</v>
       </c>
       <c r="B70" t="str">
-        <v/>
+        <v>상품</v>
       </c>
       <c r="C70" t="str">
-        <v/>
+        <v>상품 상세</v>
       </c>
       <c r="D70" t="str">
-        <v/>
+        <v>PR-02</v>
       </c>
       <c r="E70" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F70" t="str">
-        <v>포함/불포함 사항</v>
+        <v>사진 갤러리</v>
       </c>
       <c r="G70" t="str">
-        <v>'상품 상세' 화면에서 포함/불포함 사항이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 상세'의 사진 갤러리를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H70" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I70" t="str">
         <v/>
@@ -3073,10 +3073,10 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>미팅 장소 지도</v>
+        <v>상품명과 별점</v>
       </c>
       <c r="G71" t="str">
-        <v>'상품 상세' 화면에서 미팅 장소 지도가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 상세' 화면에서 상품명과 별점이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H71" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3105,13 +3105,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>취소</v>
+        <v>후기 수</v>
       </c>
       <c r="G72" t="str">
-        <v>'상품 상세'에서 취소를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'상품 상세' 화면에서 후기 수가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H72" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I72" t="str">
         <v/>
@@ -3137,13 +3137,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>환불 규정</v>
+        <v>핵심 정보 배지(소요시간·언어·즉시확정·미팅장소)</v>
       </c>
       <c r="G73" t="str">
-        <v>'상품 상세'에서 환불 규정을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'상품 상세'의 핵심 정보 배지(소요시간·언어·즉시확정·미팅장소)가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H73" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I73" t="str">
         <v/>
@@ -3169,13 +3169,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>후기 요약과 최신 후기 5개</v>
+        <v>가격과 할인율</v>
       </c>
       <c r="G74" t="str">
-        <v>'상품 상세' 화면을 열고 후기 요약과 최신 후기 5개가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'상품 상세'의 가격과 할인율이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H74" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I74" t="str">
         <v/>
@@ -3201,10 +3201,10 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>자주 묻는 질문</v>
+        <v>상품 소개 본문</v>
       </c>
       <c r="G75" t="str">
-        <v>'상품 상세' 화면에서 자주 묻는 질문이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 상세' 화면에서 상품 소개 본문이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H75" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3233,10 +3233,10 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>하단 고정 예약 바</v>
+        <v>코스 일정 타임라인</v>
       </c>
       <c r="G76" t="str">
-        <v>'상품 상세' 화면에서 하단 고정 예약 바가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 상세' 화면에서 코스 일정 타임라인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H76" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3250,25 +3250,25 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B77" t="str">
-        <v>상품</v>
+        <v/>
       </c>
       <c r="C77" t="str">
-        <v>날짜·옵션 선택</v>
+        <v/>
       </c>
       <c r="D77" t="str">
-        <v>PR-03</v>
+        <v/>
       </c>
       <c r="E77" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F77" t="str">
-        <v>달력에서 출발일 선택(예약 가능일만 활성)</v>
+        <v>포함/불포함 사항</v>
       </c>
       <c r="G77" t="str">
-        <v>'날짜·옵션 선택' 화면에서 달력에서 출발일 선택(예약 가능일만 활성)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 상세' 화면에서 포함/불포함 사항이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H77" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3282,7 +3282,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B78" t="str">
         <v/>
@@ -3297,10 +3297,10 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>시간대 선택</v>
+        <v>미팅 장소 지도</v>
       </c>
       <c r="G78" t="str">
-        <v>'날짜·옵션 선택' 화면에서 시간대 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 상세' 화면에서 미팅 장소 지도가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H78" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B79" t="str">
         <v/>
@@ -3329,13 +3329,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>인원 선택(성인·아동·유아)</v>
+        <v>취소</v>
       </c>
       <c r="G79" t="str">
-        <v>'날짜·옵션 선택' 화면에서 인원 선택(성인·아동·유아)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 상세'에서 취소를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H79" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I79" t="str">
         <v/>
@@ -3346,7 +3346,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B80" t="str">
         <v/>
@@ -3361,13 +3361,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>옵션 선택(픽업 여부·좌석 등급)</v>
+        <v>환불 규정</v>
       </c>
       <c r="G80" t="str">
-        <v>'날짜·옵션 선택' 화면에서 옵션 선택(픽업 여부·좌석 등급)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 상세'에서 환불 규정을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H80" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I80" t="str">
         <v/>
@@ -3378,7 +3378,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B81" t="str">
         <v/>
@@ -3393,13 +3393,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>실시간 잔여 좌석 표시</v>
+        <v>후기 요약과 최신 후기 5개</v>
       </c>
       <c r="G81" t="str">
-        <v>'날짜·옵션 선택'의 실시간 잔여 좌석 표시가 실제 데이터와 같은지 대조한다.</v>
+        <v>'상품 상세' 화면을 열고 후기 요약과 최신 후기 5개가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H81" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I81" t="str">
         <v/>
@@ -3410,7 +3410,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B82" t="str">
         <v/>
@@ -3425,13 +3425,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>총 금액 자동 계산</v>
+        <v>자주 묻는 질문</v>
       </c>
       <c r="G82" t="str">
-        <v>'날짜·옵션 선택'의 총 금액 자동 계산이 실제 데이터와 같은지 대조한다.</v>
+        <v>'상품 상세' 화면에서 자주 묻는 질문이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H82" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I82" t="str">
         <v/>
@@ -3442,28 +3442,28 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>SCN-009</v>
+        <v>SCN-007</v>
       </c>
       <c r="B83" t="str">
-        <v>상품</v>
+        <v/>
       </c>
       <c r="C83" t="str">
-        <v>패스 상품 상세</v>
+        <v/>
       </c>
       <c r="D83" t="str">
-        <v>PR-04</v>
+        <v/>
       </c>
       <c r="E83" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F83" t="str">
-        <v>패스 소개와 절약 금액 강조</v>
+        <v>하단 고정 예약 바</v>
       </c>
       <c r="G83" t="str">
-        <v>'패스 상품 상세'의 패스 소개와 절약 금액 강조가 실제 데이터와 같은지 대조한다.</v>
+        <v>'상품 상세' 화면에서 하단 고정 예약 바가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H83" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I83" t="str">
         <v/>
@@ -3474,28 +3474,28 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B84" t="str">
-        <v/>
+        <v>상품</v>
       </c>
       <c r="C84" t="str">
-        <v/>
+        <v>날짜·옵션 선택</v>
       </c>
       <c r="D84" t="str">
-        <v/>
+        <v>PR-03</v>
       </c>
       <c r="E84" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F84" t="str">
-        <v>포함 명소 목록과 개별 정가</v>
+        <v>달력에서 출발일 선택(예약 가능일만 활성)</v>
       </c>
       <c r="G84" t="str">
-        <v>'패스 상품 상세'의 포함 명소 목록과 개별 정가를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'날짜·옵션 선택' 화면에서 달력에서 출발일 선택(예약 가능일만 활성)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H84" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I84" t="str">
         <v/>
@@ -3506,7 +3506,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B85" t="str">
         <v/>
@@ -3521,10 +3521,10 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>이용 기간과 사용 규칙</v>
+        <v>시간대 선택</v>
       </c>
       <c r="G85" t="str">
-        <v>'패스 상품 상세' 화면에서 이용 기간과 사용 규칙이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'날짜·옵션 선택' 화면에서 시간대 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H85" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3538,7 +3538,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B86" t="str">
         <v/>
@@ -3553,13 +3553,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>패스 종류별 가격표(2일권·3일권)</v>
+        <v>인원 선택(성인·아동·유아)</v>
       </c>
       <c r="G86" t="str">
-        <v>'패스 상품 상세'의 패스 종류별 가격표(2일권·3일권)이 실제 데이터와 같은지 대조한다.</v>
+        <v>'날짜·옵션 선택' 화면에서 인원 선택(성인·아동·유아)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H86" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I86" t="str">
         <v/>
@@ -3570,7 +3570,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B87" t="str">
         <v/>
@@ -3585,13 +3585,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>사용 방법 3단계</v>
+        <v>옵션 선택(픽업 여부·좌석 등급)</v>
       </c>
       <c r="G87" t="str">
-        <v>'패스 상품 상세' 화면을 열고 사용 방법 3단계가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'날짜·옵션 선택' 화면에서 옵션 선택(픽업 여부·좌석 등급)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H87" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I87" t="str">
         <v/>
@@ -3602,7 +3602,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B88" t="str">
         <v/>
@@ -3617,13 +3617,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>주의사항</v>
+        <v>실시간 잔여 좌석 표시</v>
       </c>
       <c r="G88" t="str">
-        <v>'패스 상품 상세' 화면에서 주의사항이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'날짜·옵션 선택'의 실시간 잔여 좌석 표시가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H88" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I88" t="str">
         <v/>
@@ -3634,7 +3634,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B89" t="str">
         <v/>
@@ -3649,13 +3649,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>하단 고정 구매 바</v>
+        <v>총 금액 자동 계산</v>
       </c>
       <c r="G89" t="str">
-        <v>'패스 상품 상세' 화면에서 하단 고정 구매 바가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'날짜·옵션 선택'의 총 금액 자동 계산이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H89" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I89" t="str">
         <v/>
@@ -3666,28 +3666,28 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B90" t="str">
         <v>상품</v>
       </c>
       <c r="C90" t="str">
-        <v>상품 비교</v>
+        <v>패스 상품 상세</v>
       </c>
       <c r="D90" t="str">
-        <v>PR-05</v>
+        <v>PR-04</v>
       </c>
       <c r="E90" t="str">
         <v>기본</v>
       </c>
       <c r="F90" t="str">
-        <v>선택한 상품 2~3개를 표로 나란히 비교</v>
+        <v>패스 소개와 절약 금액 강조</v>
       </c>
       <c r="G90" t="str">
-        <v>'상품 비교' 화면을 열고 선택한 상품 2~3개를 표로 나란히 비교가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'패스 상품 상세'의 패스 소개와 절약 금액 강조가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H90" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I90" t="str">
         <v/>
@@ -3698,7 +3698,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B91" t="str">
         <v/>
@@ -3713,13 +3713,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>비교 항목(가격·소요시간·포함사항·미팅장소·취소규정·평점)</v>
+        <v>포함 명소 목록과 개별 정가</v>
       </c>
       <c r="G91" t="str">
-        <v>'상품 비교' 화면에서 비교 항목(가격·소요시간·포함사항·미팅장소·취소규정·평점)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'패스 상품 상세'의 포함 명소 목록과 개별 정가를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H91" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I91" t="str">
         <v/>
@@ -3730,7 +3730,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B92" t="str">
         <v/>
@@ -3745,10 +3745,10 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>차이나는 항목 강조</v>
+        <v>이용 기간과 사용 규칙</v>
       </c>
       <c r="G92" t="str">
-        <v>'상품 비교' 화면에서 차이나는 항목 강조가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'패스 상품 상세' 화면에서 이용 기간과 사용 규칙이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H92" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B93" t="str">
         <v/>
@@ -3777,13 +3777,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>각 열에서 바로 예약</v>
+        <v>패스 종류별 가격표(2일권·3일권)</v>
       </c>
       <c r="G93" t="str">
-        <v>'상품 비교' 화면에서 각 열에서 바로 예약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'패스 상품 상세'의 패스 종류별 가격표(2일권·3일권)이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H93" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I93" t="str">
         <v/>
@@ -3794,28 +3794,28 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>SCN-011</v>
+        <v>SCN-009</v>
       </c>
       <c r="B94" t="str">
-        <v>상품</v>
+        <v/>
       </c>
       <c r="C94" t="str">
-        <v>예약 마감·품절</v>
+        <v/>
       </c>
       <c r="D94" t="str">
-        <v>PR-06</v>
+        <v/>
       </c>
       <c r="E94" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F94" t="str">
-        <v>마감 사유 안내(좌석 소진·판매 종료·시즌 종료)</v>
+        <v>사용 방법 3단계</v>
       </c>
       <c r="G94" t="str">
-        <v>일부러 그 상황을 만들어 '예약 마감·품절' 화면이 나오게 한 뒤, 마감 사유 안내(좌석 소진·판매 종료·시즌 종료)가 보이는지 확인한다.</v>
+        <v>'패스 상품 상세' 화면을 열고 사용 방법 3단계가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H94" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I94" t="str">
         <v/>
@@ -3826,7 +3826,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>SCN-011</v>
+        <v>SCN-009</v>
       </c>
       <c r="B95" t="str">
         <v/>
@@ -3841,13 +3841,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>다음 예약 가능일 안내</v>
+        <v>주의사항</v>
       </c>
       <c r="G95" t="str">
-        <v>일부러 그 상황을 만들어 '예약 마감·품절' 화면이 나오게 한 뒤, 다음 예약 가능일 안내가 보이는지 확인한다.</v>
+        <v>'패스 상품 상세' 화면에서 주의사항이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H95" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I95" t="str">
         <v/>
@@ -3858,7 +3858,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>SCN-011</v>
+        <v>SCN-009</v>
       </c>
       <c r="B96" t="str">
         <v/>
@@ -3873,13 +3873,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>재입고 알림 신청</v>
+        <v>하단 고정 구매 바</v>
       </c>
       <c r="G96" t="str">
-        <v>일부러 그 상황을 만들어 '예약 마감·품절' 화면이 나오게 한 뒤, 재입고 알림 신청이 보이는지 확인한다.</v>
+        <v>'패스 상품 상세' 화면에서 하단 고정 구매 바가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H96" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I96" t="str">
         <v/>
@@ -3890,28 +3890,28 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>SCN-011</v>
+        <v>SCN-010</v>
       </c>
       <c r="B97" t="str">
-        <v/>
+        <v>상품</v>
       </c>
       <c r="C97" t="str">
-        <v/>
+        <v>상품 비교</v>
       </c>
       <c r="D97" t="str">
-        <v/>
+        <v>PR-05</v>
       </c>
       <c r="E97" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F97" t="str">
-        <v>비슷한 상품 4개 추천</v>
+        <v>선택한 상품 2~3개를 표로 나란히 비교</v>
       </c>
       <c r="G97" t="str">
-        <v>일부러 그 상황을 만들어 '예약 마감·품절' 화면이 나오게 한 뒤, 비슷한 상품 4개 추천이 보이는지 확인한다.</v>
+        <v>'상품 비교' 화면을 열고 선택한 상품 2~3개를 표로 나란히 비교가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H97" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I97" t="str">
         <v/>
@@ -3922,25 +3922,25 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>SCN-012</v>
+        <v>SCN-010</v>
       </c>
       <c r="B98" t="str">
-        <v>상품</v>
+        <v/>
       </c>
       <c r="C98" t="str">
-        <v>후기 전체보기</v>
+        <v/>
       </c>
       <c r="D98" t="str">
-        <v>PR-07</v>
+        <v/>
       </c>
       <c r="E98" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F98" t="str">
-        <v>평점 분포 막대그래프</v>
+        <v>비교 항목(가격·소요시간·포함사항·미팅장소·취소규정·평점)</v>
       </c>
       <c r="G98" t="str">
-        <v>'후기 전체보기' 화면에서 평점 분포 막대그래프가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 비교' 화면에서 비교 항목(가격·소요시간·포함사항·미팅장소·취소규정·평점)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H98" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>SCN-012</v>
+        <v>SCN-010</v>
       </c>
       <c r="B99" t="str">
         <v/>
@@ -3969,13 +3969,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>필터(별점·사진후기만·최근순)</v>
+        <v>차이나는 항목 강조</v>
       </c>
       <c r="G99" t="str">
-        <v>'후기 전체보기'에서 필터(별점·사진후기만·최근순)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'상품 비교' 화면에서 차이나는 항목 강조가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H99" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I99" t="str">
         <v/>
@@ -3986,7 +3986,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>SCN-012</v>
+        <v>SCN-010</v>
       </c>
       <c r="B100" t="str">
         <v/>
@@ -4001,13 +4001,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>후기 카드 목록(사진·별점·본문·여행일·동행유형)</v>
+        <v>각 열에서 바로 예약</v>
       </c>
       <c r="G100" t="str">
-        <v>'후기 전체보기'의 후기 카드 목록(사진·별점·본문·여행일·동행유형)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'상품 비교' 화면에서 각 열에서 바로 예약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H100" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I100" t="str">
         <v/>
@@ -4018,28 +4018,28 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>SCN-012</v>
+        <v>SCN-011</v>
       </c>
       <c r="B101" t="str">
-        <v/>
+        <v>상품</v>
       </c>
       <c r="C101" t="str">
-        <v/>
+        <v>예약 마감·품절</v>
       </c>
       <c r="D101" t="str">
-        <v/>
+        <v>PR-06</v>
       </c>
       <c r="E101" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F101" t="str">
-        <v>도움돼요 버튼</v>
+        <v>마감 사유 안내(좌석 소진·판매 종료·시즌 종료)</v>
       </c>
       <c r="G101" t="str">
-        <v>'후기 전체보기'에서 도움돼요 버튼을 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '예약 마감·품절' 화면이 나오게 한 뒤, 마감 사유 안내(좌석 소진·판매 종료·시즌 종료)가 보이는지 확인한다.</v>
       </c>
       <c r="H101" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I101" t="str">
         <v/>
@@ -4050,7 +4050,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>SCN-012</v>
+        <v>SCN-011</v>
       </c>
       <c r="B102" t="str">
         <v/>
@@ -4065,13 +4065,13 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>더보기</v>
+        <v>다음 예약 가능일 안내</v>
       </c>
       <c r="G102" t="str">
-        <v>'후기 전체보기'에서 더보기의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>일부러 그 상황을 만들어 '예약 마감·품절' 화면이 나오게 한 뒤, 다음 예약 가능일 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H102" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I102" t="str">
         <v/>
@@ -4082,28 +4082,28 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>SCN-013</v>
+        <v>SCN-011</v>
       </c>
       <c r="B103" t="str">
-        <v>상품</v>
+        <v/>
       </c>
       <c r="C103" t="str">
-        <v>찜한 상품</v>
+        <v/>
       </c>
       <c r="D103" t="str">
-        <v>PR-08</v>
+        <v/>
       </c>
       <c r="E103" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F103" t="str">
-        <v>찜한 상품 카드 목록(사진·상품명·별점·가격)</v>
+        <v>재입고 알림 신청</v>
       </c>
       <c r="G103" t="str">
-        <v>'찜한 상품'의 찜한 상품 카드 목록(사진·상품명·별점·가격)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '예약 마감·품절' 화면이 나오게 한 뒤, 재입고 알림 신청이 보이는지 확인한다.</v>
       </c>
       <c r="H103" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I103" t="str">
         <v/>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>SCN-013</v>
+        <v>SCN-011</v>
       </c>
       <c r="B104" t="str">
         <v/>
@@ -4129,13 +4129,13 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>여행지</v>
+        <v>비슷한 상품 4개 추천</v>
       </c>
       <c r="G104" t="str">
-        <v>'찜한 상품' 화면에서 여행지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '예약 마감·품절' 화면이 나오게 한 뒤, 비슷한 상품 4개 추천이 보이는지 확인한다.</v>
       </c>
       <c r="H104" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I104" t="str">
         <v/>
@@ -4146,28 +4146,28 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>상품</v>
       </c>
       <c r="C105" t="str">
-        <v/>
+        <v>후기 전체보기</v>
       </c>
       <c r="D105" t="str">
-        <v/>
+        <v>PR-07</v>
       </c>
       <c r="E105" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F105" t="str">
-        <v>카테고리 필터</v>
+        <v>평점 분포 막대그래프</v>
       </c>
       <c r="G105" t="str">
-        <v>'찜한 상품'에서 카테고리 필터의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'후기 전체보기' 화면에서 평점 분포 막대그래프가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H105" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I105" t="str">
         <v/>
@@ -4178,7 +4178,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B106" t="str">
         <v/>
@@ -4193,10 +4193,10 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>정렬(담은 순·낮은 가격순·할인율순)</v>
+        <v>필터(별점·사진후기만·최근순)</v>
       </c>
       <c r="G106" t="str">
-        <v>'찜한 상품'에서 정렬(담은 순·낮은 가격순·할인율순)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'후기 전체보기'에서 필터(별점·사진후기만·최근순)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H106" t="str">
         <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
@@ -4210,7 +4210,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B107" t="str">
         <v/>
@@ -4225,13 +4225,13 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>가격 인하 배지와 이전 가격 비교</v>
+        <v>후기 카드 목록(사진·별점·본문·여행일·동행유형)</v>
       </c>
       <c r="G107" t="str">
-        <v>'찜한 상품'의 가격 인하 배지와 이전 가격 비교가 실제 데이터와 같은지 대조한다.</v>
+        <v>'후기 전체보기'의 후기 카드 목록(사진·별점·본문·여행일·동행유형)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H107" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I107" t="str">
         <v/>
@@ -4242,7 +4242,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B108" t="str">
         <v/>
@@ -4257,13 +4257,13 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>마감임박</v>
+        <v>도움돼요 버튼</v>
       </c>
       <c r="G108" t="str">
-        <v>'찜한 상품' 화면에서 마감임박이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'후기 전체보기'에서 도움돼요 버튼을 눌러 본다.</v>
       </c>
       <c r="H108" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I108" t="str">
         <v/>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B109" t="str">
         <v/>
@@ -4289,13 +4289,13 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>품절 상태 표시</v>
+        <v>더보기</v>
       </c>
       <c r="G109" t="str">
-        <v>'찜한 상품'의 품절 상태 표시가 실제 데이터와 같은지 대조한다.</v>
+        <v>'후기 전체보기'에서 더보기의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H109" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I109" t="str">
         <v/>
@@ -4309,25 +4309,25 @@
         <v>SCN-013</v>
       </c>
       <c r="B110" t="str">
-        <v/>
+        <v>상품</v>
       </c>
       <c r="C110" t="str">
-        <v/>
+        <v>찜한 상품</v>
       </c>
       <c r="D110" t="str">
-        <v/>
+        <v>PR-08</v>
       </c>
       <c r="E110" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F110" t="str">
-        <v>개별 찜 해제와 선택 삭제</v>
+        <v>찜한 상품 카드 목록(사진·상품명·별점·가격)</v>
       </c>
       <c r="G110" t="str">
-        <v>'찜한 상품' 화면에서 개별 찜 해제와 선택 삭제가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'찜한 상품'의 찜한 상품 카드 목록(사진·상품명·별점·가격)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H110" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I110" t="str">
         <v/>
@@ -4353,10 +4353,10 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>장바구니에 담기</v>
+        <v>여행지</v>
       </c>
       <c r="G111" t="str">
-        <v>'찜한 상품' 화면에서 장바구니에 담기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'찜한 상품' 화면에서 여행지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H111" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4385,13 +4385,13 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>상품 비교에 추가</v>
+        <v>카테고리 필터</v>
       </c>
       <c r="G112" t="str">
-        <v>'찜한 상품' 화면에서 상품 비교에 추가가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'찜한 상품'에서 카테고리 필터의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H112" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I112" t="str">
         <v/>
@@ -4417,13 +4417,13 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>가격 알림 신청</v>
+        <v>정렬(담은 순·낮은 가격순·할인율순)</v>
       </c>
       <c r="G113" t="str">
-        <v>'찜한 상품'의 가격 알림 신청이 실제 데이터와 같은지 대조한다.</v>
+        <v>'찜한 상품'에서 정렬(담은 순·낮은 가격순·할인율순)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H113" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I113" t="str">
         <v/>
@@ -4449,13 +4449,13 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>찜한 상품 없을 때 추천 상품 4개</v>
+        <v>가격 인하 배지와 이전 가격 비교</v>
       </c>
       <c r="G114" t="str">
-        <v>'찜한 상품' 화면을 열고 찜한 상품 없을 때 추천 상품 4개가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'찜한 상품'의 가격 인하 배지와 이전 가격 비교가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H114" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I114" t="str">
         <v/>
@@ -4466,28 +4466,28 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B115" t="str">
-        <v>장바구니</v>
+        <v/>
       </c>
       <c r="C115" t="str">
-        <v>장바구니</v>
+        <v/>
       </c>
       <c r="D115" t="str">
-        <v>CT-01</v>
+        <v/>
       </c>
       <c r="E115" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F115" t="str">
-        <v>담은 상품 목록(사진·상품명·날짜·인원·옵션·금액)</v>
+        <v>마감임박</v>
       </c>
       <c r="G115" t="str">
-        <v>'장바구니'의 담은 상품 목록(사진·상품명·날짜·인원·옵션·금액)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'찜한 상품' 화면에서 마감임박이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H115" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I115" t="str">
         <v/>
@@ -4498,7 +4498,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B116" t="str">
         <v/>
@@ -4513,13 +4513,13 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>개별 선택 체크박스</v>
+        <v>품절 상태 표시</v>
       </c>
       <c r="G116" t="str">
-        <v>'장바구니' 화면에서 개별 선택 체크박스가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'찜한 상품'의 품절 상태 표시가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H116" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I116" t="str">
         <v/>
@@ -4530,7 +4530,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B117" t="str">
         <v/>
@@ -4545,10 +4545,10 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>수량</v>
+        <v>개별 찜 해제와 선택 삭제</v>
       </c>
       <c r="G117" t="str">
-        <v>'장바구니' 화면에서 수량이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'찜한 상품' 화면에서 개별 찜 해제와 선택 삭제가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H117" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4562,7 +4562,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B118" t="str">
         <v/>
@@ -4577,10 +4577,10 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>옵션 수정</v>
+        <v>장바구니에 담기</v>
       </c>
       <c r="G118" t="str">
-        <v>'장바구니' 화면에서 옵션 수정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'찜한 상품' 화면에서 장바구니에 담기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H118" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B119" t="str">
         <v/>
@@ -4609,10 +4609,10 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>삭제</v>
+        <v>상품 비교에 추가</v>
       </c>
       <c r="G119" t="str">
-        <v>'장바구니' 화면에서 삭제가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'찜한 상품' 화면에서 상품 비교에 추가가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H119" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4626,7 +4626,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B120" t="str">
         <v/>
@@ -4641,13 +4641,13 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>예약 불가 항목 경고</v>
+        <v>가격 알림 신청</v>
       </c>
       <c r="G120" t="str">
-        <v>'장바구니' 화면에서 예약 불가 항목 경고가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'찜한 상품'의 가격 알림 신청이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H120" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I120" t="str">
         <v/>
@@ -4658,7 +4658,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B121" t="str">
         <v/>
@@ -4673,13 +4673,13 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>금액 요약과 결제 버튼</v>
+        <v>찜한 상품 없을 때 추천 상품 4개</v>
       </c>
       <c r="G121" t="str">
-        <v>'장바구니'에서 금액 요약과 결제 버튼을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'찜한 상품' 화면을 열고 찜한 상품 없을 때 추천 상품 4개가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H121" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I121" t="str">
         <v/>
@@ -4690,28 +4690,28 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>SCN-015</v>
+        <v>SCN-014</v>
       </c>
       <c r="B122" t="str">
         <v>장바구니</v>
       </c>
       <c r="C122" t="str">
-        <v>장바구니 비어 있음</v>
+        <v>장바구니</v>
       </c>
       <c r="D122" t="str">
-        <v>CT-02</v>
+        <v>CT-01</v>
       </c>
       <c r="E122" t="str">
-        <v>예외·상태</v>
+        <v>기본</v>
       </c>
       <c r="F122" t="str">
-        <v>빈 상태 일러스트와 안내 문구</v>
+        <v>담은 상품 목록(사진·상품명·날짜·인원·옵션·금액)</v>
       </c>
       <c r="G122" t="str">
-        <v>일부러 그 상황을 만들어 '장바구니 비어 있음' 화면이 나오게 한 뒤, 빈 상태 일러스트와 안내 문구가 보이는지 확인한다.</v>
+        <v>'장바구니'의 담은 상품 목록(사진·상품명·날짜·인원·옵션·금액)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H122" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I122" t="str">
         <v/>
@@ -4722,7 +4722,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>SCN-015</v>
+        <v>SCN-014</v>
       </c>
       <c r="B123" t="str">
         <v/>
@@ -4737,13 +4737,13 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>인기 상품 둘러보기 버튼</v>
+        <v>개별 선택 체크박스</v>
       </c>
       <c r="G123" t="str">
-        <v>일부러 그 상황을 만들어 '장바구니 비어 있음' 화면이 나오게 한 뒤, 인기 상품 둘러보기 버튼이 보이는지 확인한다.</v>
+        <v>'장바구니' 화면에서 개별 선택 체크박스가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H123" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I123" t="str">
         <v/>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>SCN-015</v>
+        <v>SCN-014</v>
       </c>
       <c r="B124" t="str">
         <v/>
@@ -4769,13 +4769,13 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>최근 본 상품 4개</v>
+        <v>수량</v>
       </c>
       <c r="G124" t="str">
-        <v>일부러 그 상황을 만들어 '장바구니 비어 있음' 화면이 나오게 한 뒤, 최근 본 상품 4개가 보이는지 확인한다.</v>
+        <v>'장바구니' 화면에서 수량이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H124" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I124" t="str">
         <v/>
@@ -4786,25 +4786,25 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>SCN-016</v>
+        <v>SCN-014</v>
       </c>
       <c r="B125" t="str">
-        <v>예약·결제</v>
+        <v/>
       </c>
       <c r="C125" t="str">
-        <v>여행자 정보 입력</v>
+        <v/>
       </c>
       <c r="D125" t="str">
-        <v>BK-01</v>
+        <v/>
       </c>
       <c r="E125" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F125" t="str">
-        <v>예약 상품 요약</v>
+        <v>옵션 수정</v>
       </c>
       <c r="G125" t="str">
-        <v>'여행자 정보 입력' 화면에서 예약 상품 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장바구니' 화면에서 옵션 수정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H125" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4818,7 +4818,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>SCN-016</v>
+        <v>SCN-014</v>
       </c>
       <c r="B126" t="str">
         <v/>
@@ -4833,13 +4833,13 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>대표 예약자 정보(이름·영문명·연락처·이메일)</v>
+        <v>삭제</v>
       </c>
       <c r="G126" t="str">
-        <v>'여행자 정보 입력'의 대표 예약자 정보(이름·영문명·연락처·이메일)이 실제 데이터와 같은지 대조한다.</v>
+        <v>'장바구니' 화면에서 삭제가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H126" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I126" t="str">
         <v/>
@@ -4850,7 +4850,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>SCN-016</v>
+        <v>SCN-014</v>
       </c>
       <c r="B127" t="str">
         <v/>
@@ -4865,13 +4865,13 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>인원별 여행자 정보(영문명·생년월일)</v>
+        <v>예약 불가 항목 경고</v>
       </c>
       <c r="G127" t="str">
-        <v>'여행자 정보 입력'의 인원별 여행자 정보(영문명·생년월일)이 실제 데이터와 같은지 대조한다.</v>
+        <v>'장바구니' 화면에서 예약 불가 항목 경고가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H127" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I127" t="str">
         <v/>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>SCN-016</v>
+        <v>SCN-014</v>
       </c>
       <c r="B128" t="str">
         <v/>
@@ -4897,13 +4897,13 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>픽업 호텔 입력</v>
+        <v>금액 요약과 결제 버튼</v>
       </c>
       <c r="G128" t="str">
-        <v>'여행자 정보 입력'의 픽업 호텔 입력에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'장바구니'에서 금액 요약과 결제 버튼을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H128" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I128" t="str">
         <v/>
@@ -4914,28 +4914,28 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>SCN-016</v>
+        <v>SCN-015</v>
       </c>
       <c r="B129" t="str">
-        <v/>
+        <v>장바구니</v>
       </c>
       <c r="C129" t="str">
-        <v/>
+        <v>장바구니 비어 있음</v>
       </c>
       <c r="D129" t="str">
-        <v/>
+        <v>CT-02</v>
       </c>
       <c r="E129" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F129" t="str">
-        <v>요청사항</v>
+        <v>빈 상태 일러스트와 안내 문구</v>
       </c>
       <c r="G129" t="str">
-        <v>'여행자 정보 입력' 화면에서 요청사항이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '장바구니 비어 있음' 화면이 나오게 한 뒤, 빈 상태 일러스트와 안내 문구가 보이는지 확인한다.</v>
       </c>
       <c r="H129" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I129" t="str">
         <v/>
@@ -4946,7 +4946,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>SCN-016</v>
+        <v>SCN-015</v>
       </c>
       <c r="B130" t="str">
         <v/>
@@ -4961,13 +4961,13 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>약관 동의</v>
+        <v>인기 상품 둘러보기 버튼</v>
       </c>
       <c r="G130" t="str">
-        <v>'여행자 정보 입력' 화면에서 약관 동의가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '장바구니 비어 있음' 화면이 나오게 한 뒤, 인기 상품 둘러보기 버튼이 보이는지 확인한다.</v>
       </c>
       <c r="H130" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I130" t="str">
         <v/>
@@ -4978,28 +4978,28 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>SCN-017</v>
+        <v>SCN-015</v>
       </c>
       <c r="B131" t="str">
-        <v>예약·결제</v>
+        <v/>
       </c>
       <c r="C131" t="str">
-        <v>결제</v>
+        <v/>
       </c>
       <c r="D131" t="str">
-        <v>BK-02</v>
+        <v/>
       </c>
       <c r="E131" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F131" t="str">
-        <v>예약 내역 요약</v>
+        <v>최근 본 상품 4개</v>
       </c>
       <c r="G131" t="str">
-        <v>'결제' 화면에서 예약 내역 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '장바구니 비어 있음' 화면이 나오게 한 뒤, 최근 본 상품 4개가 보이는지 확인한다.</v>
       </c>
       <c r="H131" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I131" t="str">
         <v/>
@@ -5010,25 +5010,25 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B132" t="str">
-        <v/>
+        <v>예약·결제</v>
       </c>
       <c r="C132" t="str">
-        <v/>
+        <v>여행자 정보 입력</v>
       </c>
       <c r="D132" t="str">
-        <v/>
+        <v>BK-01</v>
       </c>
       <c r="E132" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F132" t="str">
-        <v>쿠폰</v>
+        <v>예약 상품 요약</v>
       </c>
       <c r="G132" t="str">
-        <v>'결제' 화면에서 쿠폰이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'여행자 정보 입력' 화면에서 예약 상품 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H132" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5042,7 +5042,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B133" t="str">
         <v/>
@@ -5057,13 +5057,13 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>포인트 적용</v>
+        <v>대표 예약자 정보(이름·영문명·연락처·이메일)</v>
       </c>
       <c r="G133" t="str">
-        <v>'결제' 화면에서 포인트 적용이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'여행자 정보 입력'의 대표 예약자 정보(이름·영문명·연락처·이메일)이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H133" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I133" t="str">
         <v/>
@@ -5074,7 +5074,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B134" t="str">
         <v/>
@@ -5089,13 +5089,13 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>결제 수단 선택(카드·간편결제·해외결제)</v>
+        <v>인원별 여행자 정보(영문명·생년월일)</v>
       </c>
       <c r="G134" t="str">
-        <v>'결제'에서 결제 수단 선택(카드·간편결제·해외결제)를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'여행자 정보 입력'의 인원별 여행자 정보(영문명·생년월일)이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H134" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I134" t="str">
         <v/>
@@ -5106,7 +5106,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B135" t="str">
         <v/>
@@ -5121,13 +5121,13 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>최종 금액 계산</v>
+        <v>픽업 호텔 입력</v>
       </c>
       <c r="G135" t="str">
-        <v>'결제'의 최종 금액 계산이 실제 데이터와 같은지 대조한다.</v>
+        <v>'여행자 정보 입력'의 픽업 호텔 입력에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H135" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I135" t="str">
         <v/>
@@ -5138,7 +5138,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B136" t="str">
         <v/>
@@ -5153,10 +5153,10 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>환율 안내</v>
+        <v>요청사항</v>
       </c>
       <c r="G136" t="str">
-        <v>'결제' 화면에서 환율 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'여행자 정보 입력' 화면에서 요청사항이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H136" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5170,7 +5170,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B137" t="str">
         <v/>
@@ -5185,13 +5185,13 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>결제 진행</v>
+        <v>약관 동의</v>
       </c>
       <c r="G137" t="str">
-        <v>'결제'에서 결제 진행을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'여행자 정보 입력' 화면에서 약관 동의가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H137" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I137" t="str">
         <v/>
@@ -5202,25 +5202,25 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B138" t="str">
         <v>예약·결제</v>
       </c>
       <c r="C138" t="str">
-        <v>예약 완료</v>
+        <v>결제</v>
       </c>
       <c r="D138" t="str">
-        <v>BK-03</v>
+        <v>BK-02</v>
       </c>
       <c r="E138" t="str">
         <v>기본</v>
       </c>
       <c r="F138" t="str">
-        <v>완료 아이콘과 예약번호</v>
+        <v>예약 내역 요약</v>
       </c>
       <c r="G138" t="str">
-        <v>'예약 완료' 화면에서 완료 아이콘과 예약번호가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'결제' 화면에서 예약 내역 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H138" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5234,7 +5234,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B139" t="str">
         <v/>
@@ -5249,10 +5249,10 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>예약 상품 요약</v>
+        <v>쿠폰</v>
       </c>
       <c r="G139" t="str">
-        <v>'예약 완료' 화면에서 예약 상품 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'결제' 화면에서 쿠폰이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H139" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5266,7 +5266,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B140" t="str">
         <v/>
@@ -5281,10 +5281,10 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>바우처 발급 안내</v>
+        <v>포인트 적용</v>
       </c>
       <c r="G140" t="str">
-        <v>'예약 완료' 화면에서 바우처 발급 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'결제' 화면에서 포인트 적용이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H140" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5298,7 +5298,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B141" t="str">
         <v/>
@@ -5313,13 +5313,13 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>미팅 장소와 시간 재안내</v>
+        <v>결제 수단 선택(카드·간편결제·해외결제)</v>
       </c>
       <c r="G141" t="str">
-        <v>'예약 완료' 화면에서 미팅 장소와 시간 재안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'결제'에서 결제 수단 선택(카드·간편결제·해외결제)를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H141" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I141" t="str">
         <v/>
@@ -5330,7 +5330,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B142" t="str">
         <v/>
@@ -5345,13 +5345,13 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>준비물 체크리스트</v>
+        <v>최종 금액 계산</v>
       </c>
       <c r="G142" t="str">
-        <v>'예약 완료'의 준비물 체크리스트를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'결제'의 최종 금액 계산이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H142" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I142" t="str">
         <v/>
@@ -5362,7 +5362,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B143" t="str">
         <v/>
@@ -5377,13 +5377,13 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>예약 내역 바로가기</v>
+        <v>환율 안내</v>
       </c>
       <c r="G143" t="str">
-        <v>'예약 완료'에서 예약 내역 바로가기를 눌러 본다.</v>
+        <v>'결제' 화면에서 환율 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H143" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I143" t="str">
         <v/>
@@ -5394,28 +5394,28 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>SCN-019</v>
+        <v>SCN-017</v>
       </c>
       <c r="B144" t="str">
-        <v>예약·결제</v>
+        <v/>
       </c>
       <c r="C144" t="str">
-        <v>결제 실패</v>
+        <v/>
       </c>
       <c r="D144" t="str">
-        <v>BK-04</v>
+        <v/>
       </c>
       <c r="E144" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F144" t="str">
-        <v>실패 아이콘과 사유를 쉬운 말로 안내</v>
+        <v>결제 진행</v>
       </c>
       <c r="G144" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 실패 아이콘과 사유를 쉬운 말로 안내가 보이는지 확인한다.</v>
+        <v>'결제'에서 결제 진행을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H144" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I144" t="str">
         <v/>
@@ -5426,28 +5426,28 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B145" t="str">
-        <v/>
+        <v>예약·결제</v>
       </c>
       <c r="C145" t="str">
-        <v/>
+        <v>예약 완료</v>
       </c>
       <c r="D145" t="str">
-        <v/>
+        <v>BK-03</v>
       </c>
       <c r="E145" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F145" t="str">
-        <v>자주 있는 원인 3가지</v>
+        <v>완료 아이콘과 예약번호</v>
       </c>
       <c r="G145" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 자주 있는 원인 3가지가 보이는지 확인한다.</v>
+        <v>'예약 완료' 화면에서 완료 아이콘과 예약번호가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H145" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I145" t="str">
         <v/>
@@ -5458,7 +5458,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B146" t="str">
         <v/>
@@ -5473,13 +5473,13 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>다시 시도 버튼</v>
+        <v>예약 상품 요약</v>
       </c>
       <c r="G146" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 다시 시도 버튼이 보이는지 확인한다.</v>
+        <v>'예약 완료' 화면에서 예약 상품 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H146" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I146" t="str">
         <v/>
@@ -5490,7 +5490,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B147" t="str">
         <v/>
@@ -5505,13 +5505,13 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>다른 결제 수단 안내</v>
+        <v>바우처 발급 안내</v>
       </c>
       <c r="G147" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 다른 결제 수단 안내가 보이는지 확인한다.</v>
+        <v>'예약 완료' 화면에서 바우처 발급 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H147" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I147" t="str">
         <v/>
@@ -5522,7 +5522,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B148" t="str">
         <v/>
@@ -5537,13 +5537,13 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>고객센터 연결</v>
+        <v>미팅 장소와 시간 재안내</v>
       </c>
       <c r="G148" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 고객센터 연결이 보이는지 확인한다.</v>
+        <v>'예약 완료' 화면에서 미팅 장소와 시간 재안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H148" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I148" t="str">
         <v/>
@@ -5554,28 +5554,28 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>SCN-020</v>
+        <v>SCN-018</v>
       </c>
       <c r="B149" t="str">
-        <v>예약·결제</v>
+        <v/>
       </c>
       <c r="C149" t="str">
-        <v>예약 확정 대기</v>
+        <v/>
       </c>
       <c r="D149" t="str">
-        <v>BK-05</v>
+        <v/>
       </c>
       <c r="E149" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F149" t="str">
-        <v>대기 상태 안내와 예상 확정 시각</v>
+        <v>준비물 체크리스트</v>
       </c>
       <c r="G149" t="str">
-        <v>일부러 그 상황을 만들어 '예약 확정 대기' 화면이 나오게 한 뒤, 대기 상태 안내와 예상 확정 시각이 보이는지 확인한다.</v>
+        <v>'예약 완료'의 준비물 체크리스트를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H149" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I149" t="str">
         <v/>
@@ -5586,7 +5586,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>SCN-020</v>
+        <v>SCN-018</v>
       </c>
       <c r="B150" t="str">
         <v/>
@@ -5601,13 +5601,13 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>왜 대기가 필요한지 설명</v>
+        <v>예약 내역 바로가기</v>
       </c>
       <c r="G150" t="str">
-        <v>일부러 그 상황을 만들어 '예약 확정 대기' 화면이 나오게 한 뒤, 왜 대기가 필요한지 설명이 보이는지 확인한다.</v>
+        <v>'예약 완료'에서 예약 내역 바로가기를 눌러 본다.</v>
       </c>
       <c r="H150" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I150" t="str">
         <v/>
@@ -5618,25 +5618,25 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>SCN-020</v>
+        <v>SCN-019</v>
       </c>
       <c r="B151" t="str">
-        <v/>
+        <v>예약·결제</v>
       </c>
       <c r="C151" t="str">
-        <v/>
+        <v>결제 실패</v>
       </c>
       <c r="D151" t="str">
-        <v/>
+        <v>BK-04</v>
       </c>
       <c r="E151" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F151" t="str">
-        <v>확정 알림 방법 안내</v>
+        <v>실패 아이콘과 사유를 쉬운 말로 안내</v>
       </c>
       <c r="G151" t="str">
-        <v>일부러 그 상황을 만들어 '예약 확정 대기' 화면이 나오게 한 뒤, 확정 알림 방법 안내가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 실패 아이콘과 사유를 쉬운 말로 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H151" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -5650,7 +5650,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>SCN-020</v>
+        <v>SCN-019</v>
       </c>
       <c r="B152" t="str">
         <v/>
@@ -5665,10 +5665,10 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>대기 중 취소 시 전액 환불 안내</v>
+        <v>자주 있는 원인 3가지</v>
       </c>
       <c r="G152" t="str">
-        <v>일부러 그 상황을 만들어 '예약 확정 대기' 화면이 나오게 한 뒤, 대기 중 취소 시 전액 환불 안내가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 자주 있는 원인 3가지가 보이는지 확인한다.</v>
       </c>
       <c r="H152" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -5682,7 +5682,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>SCN-020</v>
+        <v>SCN-019</v>
       </c>
       <c r="B153" t="str">
         <v/>
@@ -5697,10 +5697,10 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>예약 내역 바로가기</v>
+        <v>다시 시도 버튼</v>
       </c>
       <c r="G153" t="str">
-        <v>일부러 그 상황을 만들어 '예약 확정 대기' 화면이 나오게 한 뒤, 예약 내역 바로가기가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 다시 시도 버튼이 보이는지 확인한다.</v>
       </c>
       <c r="H153" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -5714,25 +5714,25 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>SCN-021</v>
+        <v>SCN-019</v>
       </c>
       <c r="B154" t="str">
-        <v>예약·결제</v>
+        <v/>
       </c>
       <c r="C154" t="str">
-        <v>최소 인원 미달 안내</v>
+        <v/>
       </c>
       <c r="D154" t="str">
-        <v>BK-06</v>
+        <v/>
       </c>
       <c r="E154" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F154" t="str">
-        <v>출발 확정 인원과 현재 인원 표시</v>
+        <v>다른 결제 수단 안내</v>
       </c>
       <c r="G154" t="str">
-        <v>일부러 그 상황을 만들어 '최소 인원 미달 안내' 화면이 나오게 한 뒤, 출발 확정 인원과 현재 인원 표시가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 다른 결제 수단 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H154" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -5746,7 +5746,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>SCN-021</v>
+        <v>SCN-019</v>
       </c>
       <c r="B155" t="str">
         <v/>
@@ -5761,10 +5761,10 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>확정 마감 시각 안내</v>
+        <v>고객센터 연결</v>
       </c>
       <c r="G155" t="str">
-        <v>일부러 그 상황을 만들어 '최소 인원 미달 안내' 화면이 나오게 한 뒤, 확정 마감 시각 안내가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 고객센터 연결이 보이는지 확인한다.</v>
       </c>
       <c r="H155" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -5778,25 +5778,25 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>SCN-021</v>
+        <v>SCN-020</v>
       </c>
       <c r="B156" t="str">
-        <v/>
+        <v>예약·결제</v>
       </c>
       <c r="C156" t="str">
-        <v/>
+        <v>예약 확정 대기</v>
       </c>
       <c r="D156" t="str">
-        <v/>
+        <v>BK-05</v>
       </c>
       <c r="E156" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F156" t="str">
-        <v>미달 시 전액 환불 안내</v>
+        <v>대기 상태 안내와 예상 확정 시각</v>
       </c>
       <c r="G156" t="str">
-        <v>일부러 그 상황을 만들어 '최소 인원 미달 안내' 화면이 나오게 한 뒤, 미달 시 전액 환불 안내가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '예약 확정 대기' 화면이 나오게 한 뒤, 대기 상태 안내와 예상 확정 시각이 보이는지 확인한다.</v>
       </c>
       <c r="H156" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -5810,7 +5810,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>SCN-021</v>
+        <v>SCN-020</v>
       </c>
       <c r="B157" t="str">
         <v/>
@@ -5825,10 +5825,10 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>대체 상품 추천</v>
+        <v>왜 대기가 필요한지 설명</v>
       </c>
       <c r="G157" t="str">
-        <v>일부러 그 상황을 만들어 '최소 인원 미달 안내' 화면이 나오게 한 뒤, 대체 상품 추천이 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '예약 확정 대기' 화면이 나오게 한 뒤, 왜 대기가 필요한지 설명이 보이는지 확인한다.</v>
       </c>
       <c r="H157" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -5842,7 +5842,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>SCN-021</v>
+        <v>SCN-020</v>
       </c>
       <c r="B158" t="str">
         <v/>
@@ -5857,10 +5857,10 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>친구 초대 공유</v>
+        <v>확정 알림 방법 안내</v>
       </c>
       <c r="G158" t="str">
-        <v>일부러 그 상황을 만들어 '최소 인원 미달 안내' 화면이 나오게 한 뒤, 친구 초대 공유가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '예약 확정 대기' 화면이 나오게 한 뒤, 확정 알림 방법 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H158" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -5874,28 +5874,28 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>SCN-022</v>
+        <v>SCN-020</v>
       </c>
       <c r="B159" t="str">
-        <v>바우처</v>
+        <v/>
       </c>
       <c r="C159" t="str">
-        <v>바우처 목록</v>
+        <v/>
       </c>
       <c r="D159" t="str">
-        <v>VC-01</v>
+        <v/>
       </c>
       <c r="E159" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F159" t="str">
-        <v>사용 예정</v>
+        <v>대기 중 취소 시 전액 환불 안내</v>
       </c>
       <c r="G159" t="str">
-        <v>'바우처 목록' 화면에서 사용 예정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '예약 확정 대기' 화면이 나오게 한 뒤, 대기 중 취소 시 전액 환불 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H159" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I159" t="str">
         <v/>
@@ -5906,7 +5906,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>SCN-022</v>
+        <v>SCN-020</v>
       </c>
       <c r="B160" t="str">
         <v/>
@@ -5921,13 +5921,13 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>사용 완료</v>
+        <v>예약 내역 바로가기</v>
       </c>
       <c r="G160" t="str">
-        <v>'바우처 목록' 화면에서 사용 완료가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '예약 확정 대기' 화면이 나오게 한 뒤, 예약 내역 바로가기가 보이는지 확인한다.</v>
       </c>
       <c r="H160" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I160" t="str">
         <v/>
@@ -5938,28 +5938,28 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B161" t="str">
-        <v/>
+        <v>예약·결제</v>
       </c>
       <c r="C161" t="str">
-        <v/>
+        <v>최소 인원 미달 안내</v>
       </c>
       <c r="D161" t="str">
-        <v/>
+        <v>BK-06</v>
       </c>
       <c r="E161" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F161" t="str">
-        <v>만료 탭</v>
+        <v>출발 확정 인원과 현재 인원 표시</v>
       </c>
       <c r="G161" t="str">
-        <v>'바우처 목록'에서 만료 탭의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>일부러 그 상황을 만들어 '최소 인원 미달 안내' 화면이 나오게 한 뒤, 출발 확정 인원과 현재 인원 표시가 보이는지 확인한다.</v>
       </c>
       <c r="H161" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I161" t="str">
         <v/>
@@ -5970,7 +5970,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B162" t="str">
         <v/>
@@ -5985,13 +5985,13 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>바우처 카드(상품명·사용일·QR 미리보기·상태 배지)</v>
+        <v>확정 마감 시각 안내</v>
       </c>
       <c r="G162" t="str">
-        <v>'바우처 목록'의 바우처 카드(상품명·사용일·QR 미리보기·상태 배지)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '최소 인원 미달 안내' 화면이 나오게 한 뒤, 확정 마감 시각 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H162" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I162" t="str">
         <v/>
@@ -6002,7 +6002,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B163" t="str">
         <v/>
@@ -6017,13 +6017,13 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>오프라인 저장 안내</v>
+        <v>미달 시 전액 환불 안내</v>
       </c>
       <c r="G163" t="str">
-        <v>'바우처 목록' 화면에서 오프라인 저장 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '최소 인원 미달 안내' 화면이 나오게 한 뒤, 미달 시 전액 환불 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H163" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I163" t="str">
         <v/>
@@ -6034,7 +6034,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B164" t="str">
         <v/>
@@ -6049,13 +6049,13 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>인쇄</v>
+        <v>대체 상품 추천</v>
       </c>
       <c r="G164" t="str">
-        <v>'바우처 목록' 화면에서 인쇄가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '최소 인원 미달 안내' 화면이 나오게 한 뒤, 대체 상품 추천이 보이는지 확인한다.</v>
       </c>
       <c r="H164" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I164" t="str">
         <v/>
@@ -6066,7 +6066,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B165" t="str">
         <v/>
@@ -6081,13 +6081,13 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>이미지 저장 버튼</v>
+        <v>친구 초대 공유</v>
       </c>
       <c r="G165" t="str">
-        <v>'바우처 목록'에서 이미지 저장 버튼을 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '최소 인원 미달 안내' 화면이 나오게 한 뒤, 친구 초대 공유가 보이는지 확인한다.</v>
       </c>
       <c r="H165" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I165" t="str">
         <v/>
@@ -6098,25 +6098,25 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B166" t="str">
         <v>바우처</v>
       </c>
       <c r="C166" t="str">
-        <v>바우처 상세</v>
+        <v>바우처 목록</v>
       </c>
       <c r="D166" t="str">
-        <v>VC-02</v>
+        <v>VC-01</v>
       </c>
       <c r="E166" t="str">
         <v>기본</v>
       </c>
       <c r="F166" t="str">
-        <v>큰 QR 코드와 예약번호</v>
+        <v>사용 예정</v>
       </c>
       <c r="G166" t="str">
-        <v>'바우처 상세' 화면에서 큰 QR 코드와 예약번호가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'바우처 목록' 화면에서 사용 예정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H166" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6130,7 +6130,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B167" t="str">
         <v/>
@@ -6145,10 +6145,10 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>상품명과 이용 일시</v>
+        <v>사용 완료</v>
       </c>
       <c r="G167" t="str">
-        <v>'바우처 상세' 화면에서 상품명과 이용 일시가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'바우처 목록' 화면에서 사용 완료가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H167" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6162,7 +6162,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B168" t="str">
         <v/>
@@ -6177,13 +6177,13 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>미팅 장소 지도와 길찾기</v>
+        <v>만료 탭</v>
       </c>
       <c r="G168" t="str">
-        <v>'바우처 상세' 화면에서 미팅 장소 지도와 길찾기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'바우처 목록'에서 만료 탭의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H168" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I168" t="str">
         <v/>
@@ -6194,7 +6194,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B169" t="str">
         <v/>
@@ -6209,13 +6209,13 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>현지 연락처</v>
+        <v>바우처 카드(상품명·사용일·QR 미리보기·상태 배지)</v>
       </c>
       <c r="G169" t="str">
-        <v>'바우처 상세' 화면에서 현지 연락처가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'바우처 목록'의 바우처 카드(상품명·사용일·QR 미리보기·상태 배지)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H169" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I169" t="str">
         <v/>
@@ -6226,7 +6226,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B170" t="str">
         <v/>
@@ -6241,10 +6241,10 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>이용 안내와 주의사항</v>
+        <v>오프라인 저장 안내</v>
       </c>
       <c r="G170" t="str">
-        <v>'바우처 상세' 화면에서 이용 안내와 주의사항이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'바우처 목록' 화면에서 오프라인 저장 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H170" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6258,7 +6258,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B171" t="str">
         <v/>
@@ -6273,10 +6273,10 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>화면 밝기 자동 최대 안내</v>
+        <v>인쇄</v>
       </c>
       <c r="G171" t="str">
-        <v>'바우처 상세' 화면에서 화면 밝기 자동 최대 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'바우처 목록' 화면에서 인쇄가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H171" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6290,7 +6290,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B172" t="str">
         <v/>
@@ -6305,13 +6305,13 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>저장</v>
+        <v>이미지 저장 버튼</v>
       </c>
       <c r="G172" t="str">
-        <v>'바우처 상세' 화면에서 저장이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'바우처 목록'에서 이미지 저장 버튼을 눌러 본다.</v>
       </c>
       <c r="H172" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I172" t="str">
         <v/>
@@ -6325,22 +6325,22 @@
         <v>SCN-023</v>
       </c>
       <c r="B173" t="str">
-        <v/>
+        <v>바우처</v>
       </c>
       <c r="C173" t="str">
-        <v/>
+        <v>바우처 상세</v>
       </c>
       <c r="D173" t="str">
-        <v/>
+        <v>VC-02</v>
       </c>
       <c r="E173" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F173" t="str">
-        <v>인쇄</v>
+        <v>큰 QR 코드와 예약번호</v>
       </c>
       <c r="G173" t="str">
-        <v>'바우처 상세' 화면에서 인쇄가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'바우처 상세' 화면에서 큰 QR 코드와 예약번호가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H173" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6354,28 +6354,28 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B174" t="str">
-        <v>바우처</v>
+        <v/>
       </c>
       <c r="C174" t="str">
-        <v>바우처 만료</v>
+        <v/>
       </c>
       <c r="D174" t="str">
-        <v>VC-03</v>
+        <v/>
       </c>
       <c r="E174" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F174" t="str">
-        <v>만료 안내와 만료일 표시</v>
+        <v>상품명과 이용 일시</v>
       </c>
       <c r="G174" t="str">
-        <v>일부러 그 상황을 만들어 '바우처 만료' 화면이 나오게 한 뒤, 만료 안내와 만료일 표시가 보이는지 확인한다.</v>
+        <v>'바우처 상세' 화면에서 상품명과 이용 일시가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H174" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I174" t="str">
         <v/>
@@ -6386,7 +6386,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B175" t="str">
         <v/>
@@ -6401,13 +6401,13 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>만료 사유 설명</v>
+        <v>미팅 장소 지도와 길찾기</v>
       </c>
       <c r="G175" t="str">
-        <v>일부러 그 상황을 만들어 '바우처 만료' 화면이 나오게 한 뒤, 만료 사유 설명이 보이는지 확인한다.</v>
+        <v>'바우처 상세' 화면에서 미팅 장소 지도와 길찾기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H175" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I175" t="str">
         <v/>
@@ -6418,7 +6418,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B176" t="str">
         <v/>
@@ -6433,13 +6433,13 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>재발급 가능 여부 안내</v>
+        <v>현지 연락처</v>
       </c>
       <c r="G176" t="str">
-        <v>일부러 그 상황을 만들어 '바우처 만료' 화면이 나오게 한 뒤, 재발급 가능 여부 안내가 보이는지 확인한다.</v>
+        <v>'바우처 상세' 화면에서 현지 연락처가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H176" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I176" t="str">
         <v/>
@@ -6450,7 +6450,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B177" t="str">
         <v/>
@@ -6465,13 +6465,13 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>고객센터 문의 버튼</v>
+        <v>이용 안내와 주의사항</v>
       </c>
       <c r="G177" t="str">
-        <v>일부러 그 상황을 만들어 '바우처 만료' 화면이 나오게 한 뒤, 고객센터 문의 버튼이 보이는지 확인한다.</v>
+        <v>'바우처 상세' 화면에서 이용 안내와 주의사항이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H177" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I177" t="str">
         <v/>
@@ -6482,7 +6482,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B178" t="str">
         <v/>
@@ -6497,13 +6497,13 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>같은 상품 다시 예약</v>
+        <v>화면 밝기 자동 최대 안내</v>
       </c>
       <c r="G178" t="str">
-        <v>일부러 그 상황을 만들어 '바우처 만료' 화면이 나오게 한 뒤, 같은 상품 다시 예약이 보이는지 확인한다.</v>
+        <v>'바우처 상세' 화면에서 화면 밝기 자동 최대 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H178" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I178" t="str">
         <v/>
@@ -6514,25 +6514,25 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>SCN-025</v>
+        <v>SCN-023</v>
       </c>
       <c r="B179" t="str">
-        <v>바우처</v>
+        <v/>
       </c>
       <c r="C179" t="str">
-        <v>바우처 재발급 요청</v>
+        <v/>
       </c>
       <c r="D179" t="str">
-        <v>VC-04</v>
+        <v/>
       </c>
       <c r="E179" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F179" t="str">
-        <v>재발급 사유 선택</v>
+        <v>저장</v>
       </c>
       <c r="G179" t="str">
-        <v>'바우처 재발급 요청' 화면에서 재발급 사유 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'바우처 상세' 화면에서 저장이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H179" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6546,7 +6546,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>SCN-025</v>
+        <v>SCN-023</v>
       </c>
       <c r="B180" t="str">
         <v/>
@@ -6561,10 +6561,10 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>예약번호 확인</v>
+        <v>인쇄</v>
       </c>
       <c r="G180" t="str">
-        <v>'바우처 재발급 요청' 화면에서 예약번호 확인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'바우처 상세' 화면에서 인쇄가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H180" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6578,28 +6578,28 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>SCN-025</v>
+        <v>SCN-024</v>
       </c>
       <c r="B181" t="str">
-        <v/>
+        <v>바우처</v>
       </c>
       <c r="C181" t="str">
-        <v/>
+        <v>바우처 만료</v>
       </c>
       <c r="D181" t="str">
-        <v/>
+        <v>VC-03</v>
       </c>
       <c r="E181" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F181" t="str">
-        <v>받을 이메일 입력</v>
+        <v>만료 안내와 만료일 표시</v>
       </c>
       <c r="G181" t="str">
-        <v>'바우처 재발급 요청'의 받을 이메일 입력에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>일부러 그 상황을 만들어 '바우처 만료' 화면이 나오게 한 뒤, 만료 안내와 만료일 표시가 보이는지 확인한다.</v>
       </c>
       <c r="H181" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I181" t="str">
         <v/>
@@ -6610,7 +6610,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>SCN-025</v>
+        <v>SCN-024</v>
       </c>
       <c r="B182" t="str">
         <v/>
@@ -6625,13 +6625,13 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>처리 소요시간 안내</v>
+        <v>만료 사유 설명</v>
       </c>
       <c r="G182" t="str">
-        <v>'바우처 재발급 요청' 화면에서 처리 소요시간 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '바우처 만료' 화면이 나오게 한 뒤, 만료 사유 설명이 보이는지 확인한다.</v>
       </c>
       <c r="H182" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I182" t="str">
         <v/>
@@ -6642,7 +6642,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>SCN-025</v>
+        <v>SCN-024</v>
       </c>
       <c r="B183" t="str">
         <v/>
@@ -6657,13 +6657,13 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>요청 완료 안내</v>
+        <v>재발급 가능 여부 안내</v>
       </c>
       <c r="G183" t="str">
-        <v>'바우처 재발급 요청' 화면에서 요청 완료 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '바우처 만료' 화면이 나오게 한 뒤, 재발급 가능 여부 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H183" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I183" t="str">
         <v/>
@@ -6674,28 +6674,28 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>SCN-026</v>
+        <v>SCN-024</v>
       </c>
       <c r="B184" t="str">
-        <v>마이페이지</v>
+        <v/>
       </c>
       <c r="C184" t="str">
-        <v>로그인</v>
+        <v/>
       </c>
       <c r="D184" t="str">
-        <v>MY-01</v>
+        <v/>
       </c>
       <c r="E184" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F184" t="str">
-        <v>이메일</v>
+        <v>고객센터 문의 버튼</v>
       </c>
       <c r="G184" t="str">
-        <v>'로그인' 화면에서 이메일이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '바우처 만료' 화면이 나오게 한 뒤, 고객센터 문의 버튼이 보이는지 확인한다.</v>
       </c>
       <c r="H184" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I184" t="str">
         <v/>
@@ -6706,7 +6706,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>SCN-026</v>
+        <v>SCN-024</v>
       </c>
       <c r="B185" t="str">
         <v/>
@@ -6721,13 +6721,13 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>비밀번호 입력</v>
+        <v>같은 상품 다시 예약</v>
       </c>
       <c r="G185" t="str">
-        <v>'로그인'의 비밀번호 입력에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>일부러 그 상황을 만들어 '바우처 만료' 화면이 나오게 한 뒤, 같은 상품 다시 예약이 보이는지 확인한다.</v>
       </c>
       <c r="H185" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I185" t="str">
         <v/>
@@ -6738,28 +6738,28 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B186" t="str">
-        <v/>
+        <v>바우처</v>
       </c>
       <c r="C186" t="str">
-        <v/>
+        <v>바우처 재발급 요청</v>
       </c>
       <c r="D186" t="str">
-        <v/>
+        <v>VC-04</v>
       </c>
       <c r="E186" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F186" t="str">
-        <v>소셜 로그인(카카오·구글·애플)</v>
+        <v>재발급 사유 선택</v>
       </c>
       <c r="G186" t="str">
-        <v>'로그인'에서 소셜 로그인(카카오·구글·애플)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'바우처 재발급 요청' 화면에서 재발급 사유 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H186" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I186" t="str">
         <v/>
@@ -6770,7 +6770,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B187" t="str">
         <v/>
@@ -6785,13 +6785,13 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>자동 로그인</v>
+        <v>예약번호 확인</v>
       </c>
       <c r="G187" t="str">
-        <v>'로그인'에서 자동 로그인을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'바우처 재발급 요청' 화면에서 예약번호 확인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H187" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I187" t="str">
         <v/>
@@ -6802,7 +6802,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B188" t="str">
         <v/>
@@ -6817,13 +6817,13 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>비밀번호 찾기</v>
+        <v>받을 이메일 입력</v>
       </c>
       <c r="G188" t="str">
-        <v>'로그인' 화면에서 비밀번호 찾기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'바우처 재발급 요청'의 받을 이메일 입력에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H188" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I188" t="str">
         <v/>
@@ -6834,7 +6834,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B189" t="str">
         <v/>
@@ -6849,13 +6849,13 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>비회원 예약 조회 링크</v>
+        <v>처리 소요시간 안내</v>
       </c>
       <c r="G189" t="str">
-        <v>'로그인'에서 비회원 예약 조회 링크를 눌러 본다.</v>
+        <v>'바우처 재발급 요청' 화면에서 처리 소요시간 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H189" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I189" t="str">
         <v/>
@@ -6866,25 +6866,25 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>SCN-027</v>
+        <v>SCN-025</v>
       </c>
       <c r="B190" t="str">
-        <v>마이페이지</v>
+        <v/>
       </c>
       <c r="C190" t="str">
-        <v>회원가입</v>
+        <v/>
       </c>
       <c r="D190" t="str">
-        <v>MY-02</v>
+        <v/>
       </c>
       <c r="E190" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F190" t="str">
-        <v>이메일</v>
+        <v>요청 완료 안내</v>
       </c>
       <c r="G190" t="str">
-        <v>'회원가입' 화면에서 이메일이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'바우처 재발급 요청' 화면에서 요청 완료 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H190" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6898,25 +6898,25 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B191" t="str">
-        <v/>
+        <v>마이페이지</v>
       </c>
       <c r="C191" t="str">
-        <v/>
+        <v>로그인</v>
       </c>
       <c r="D191" t="str">
-        <v/>
+        <v>MY-01</v>
       </c>
       <c r="E191" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F191" t="str">
-        <v>비밀번호</v>
+        <v>이메일</v>
       </c>
       <c r="G191" t="str">
-        <v>'회원가입' 화면에서 비밀번호가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'로그인' 화면에서 이메일이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H191" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6930,7 +6930,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B192" t="str">
         <v/>
@@ -6945,13 +6945,13 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>이름</v>
+        <v>비밀번호 입력</v>
       </c>
       <c r="G192" t="str">
-        <v>'회원가입' 화면에서 이름이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'로그인'의 비밀번호 입력에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H192" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I192" t="str">
         <v/>
@@ -6962,7 +6962,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B193" t="str">
         <v/>
@@ -6977,13 +6977,13 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>영문명 입력</v>
+        <v>소셜 로그인(카카오·구글·애플)</v>
       </c>
       <c r="G193" t="str">
-        <v>'회원가입'의 영문명 입력에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'로그인'에서 소셜 로그인(카카오·구글·애플)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H193" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I193" t="str">
         <v/>
@@ -6994,7 +6994,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B194" t="str">
         <v/>
@@ -7009,13 +7009,13 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>비밀번호 조건 실시간 표시</v>
+        <v>자동 로그인</v>
       </c>
       <c r="G194" t="str">
-        <v>'회원가입'의 비밀번호 조건 실시간 표시가 실제 데이터와 같은지 대조한다.</v>
+        <v>'로그인'에서 자동 로그인을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H194" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I194" t="str">
         <v/>
@@ -7026,7 +7026,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B195" t="str">
         <v/>
@@ -7041,10 +7041,10 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>약관 동의(필수·선택 구분)</v>
+        <v>비밀번호 찾기</v>
       </c>
       <c r="G195" t="str">
-        <v>'회원가입' 화면에서 약관 동의(필수·선택 구분)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'로그인' 화면에서 비밀번호 찾기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H195" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7058,7 +7058,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B196" t="str">
         <v/>
@@ -7073,13 +7073,13 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>마케팅 수신 동의</v>
+        <v>비회원 예약 조회 링크</v>
       </c>
       <c r="G196" t="str">
-        <v>'회원가입' 화면에서 마케팅 수신 동의가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'로그인'에서 비회원 예약 조회 링크를 눌러 본다.</v>
       </c>
       <c r="H196" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I196" t="str">
         <v/>
@@ -7093,22 +7093,22 @@
         <v>SCN-027</v>
       </c>
       <c r="B197" t="str">
-        <v/>
+        <v>마이페이지</v>
       </c>
       <c r="C197" t="str">
-        <v/>
+        <v>회원가입</v>
       </c>
       <c r="D197" t="str">
-        <v/>
+        <v>MY-02</v>
       </c>
       <c r="E197" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F197" t="str">
-        <v>가입 혜택 안내</v>
+        <v>이메일</v>
       </c>
       <c r="G197" t="str">
-        <v>'회원가입' 화면에서 가입 혜택 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'회원가입' 화면에서 이메일이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H197" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7122,28 +7122,28 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B198" t="str">
-        <v>마이페이지</v>
+        <v/>
       </c>
       <c r="C198" t="str">
-        <v>예약 내역</v>
+        <v/>
       </c>
       <c r="D198" t="str">
-        <v>MY-03</v>
+        <v/>
       </c>
       <c r="E198" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F198" t="str">
-        <v>상태 탭(예정·완료·취소)</v>
+        <v>비밀번호</v>
       </c>
       <c r="G198" t="str">
-        <v>'예약 내역'에서 상태 탭(예정·완료·취소)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'회원가입' 화면에서 비밀번호가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H198" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I198" t="str">
         <v/>
@@ -7154,7 +7154,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B199" t="str">
         <v/>
@@ -7169,13 +7169,13 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>예약 카드(상품명·날짜·인원·상태 배지·금액)</v>
+        <v>이름</v>
       </c>
       <c r="G199" t="str">
-        <v>'예약 내역'의 예약 카드(상품명·날짜·인원·상태 배지·금액)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'회원가입' 화면에서 이름이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H199" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I199" t="str">
         <v/>
@@ -7186,7 +7186,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B200" t="str">
         <v/>
@@ -7201,13 +7201,13 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>D-day 표시</v>
+        <v>영문명 입력</v>
       </c>
       <c r="G200" t="str">
-        <v>'예약 내역'의 D-day 표시가 실제 데이터와 같은지 대조한다.</v>
+        <v>'회원가입'의 영문명 입력에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H200" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I200" t="str">
         <v/>
@@ -7218,7 +7218,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B201" t="str">
         <v/>
@@ -7233,13 +7233,13 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>바우처 바로가기</v>
+        <v>비밀번호 조건 실시간 표시</v>
       </c>
       <c r="G201" t="str">
-        <v>'예약 내역'에서 바우처 바로가기를 눌러 본다.</v>
+        <v>'회원가입'의 비밀번호 조건 실시간 표시가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H201" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I201" t="str">
         <v/>
@@ -7250,7 +7250,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B202" t="str">
         <v/>
@@ -7265,10 +7265,10 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>후기 쓰기 유도</v>
+        <v>약관 동의(필수·선택 구분)</v>
       </c>
       <c r="G202" t="str">
-        <v>'예약 내역' 화면에서 후기 쓰기 유도가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'회원가입' 화면에서 약관 동의(필수·선택 구분)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H202" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7282,28 +7282,28 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>SCN-029</v>
+        <v>SCN-027</v>
       </c>
       <c r="B203" t="str">
-        <v>마이페이지</v>
+        <v/>
       </c>
       <c r="C203" t="str">
-        <v>예약 내역 없음</v>
+        <v/>
       </c>
       <c r="D203" t="str">
-        <v>MY-04</v>
+        <v/>
       </c>
       <c r="E203" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F203" t="str">
-        <v>빈 상태 일러스트와 안내</v>
+        <v>마케팅 수신 동의</v>
       </c>
       <c r="G203" t="str">
-        <v>일부러 그 상황을 만들어 '예약 내역 없음' 화면이 나오게 한 뒤, 빈 상태 일러스트와 안내가 보이는지 확인한다.</v>
+        <v>'회원가입' 화면에서 마케팅 수신 동의가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H203" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I203" t="str">
         <v/>
@@ -7314,7 +7314,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>SCN-029</v>
+        <v>SCN-027</v>
       </c>
       <c r="B204" t="str">
         <v/>
@@ -7329,13 +7329,13 @@
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>인기 여행지 바로가기</v>
+        <v>가입 혜택 안내</v>
       </c>
       <c r="G204" t="str">
-        <v>일부러 그 상황을 만들어 '예약 내역 없음' 화면이 나오게 한 뒤, 인기 여행지 바로가기가 보이는지 확인한다.</v>
+        <v>'회원가입' 화면에서 가입 혜택 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H204" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I204" t="str">
         <v/>
@@ -7346,28 +7346,28 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>SCN-029</v>
+        <v>SCN-028</v>
       </c>
       <c r="B205" t="str">
-        <v/>
+        <v>마이페이지</v>
       </c>
       <c r="C205" t="str">
-        <v/>
+        <v>예약 내역</v>
       </c>
       <c r="D205" t="str">
-        <v/>
+        <v>MY-03</v>
       </c>
       <c r="E205" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F205" t="str">
-        <v>첫 예약 쿠폰 안내</v>
+        <v>상태 탭(예정·완료·취소)</v>
       </c>
       <c r="G205" t="str">
-        <v>일부러 그 상황을 만들어 '예약 내역 없음' 화면이 나오게 한 뒤, 첫 예약 쿠폰 안내가 보이는지 확인한다.</v>
+        <v>'예약 내역'에서 상태 탭(예정·완료·취소)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H205" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I205" t="str">
         <v/>
@@ -7378,28 +7378,28 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>SCN-030</v>
+        <v>SCN-028</v>
       </c>
       <c r="B206" t="str">
-        <v>마이페이지</v>
+        <v/>
       </c>
       <c r="C206" t="str">
-        <v>예약 상세</v>
+        <v/>
       </c>
       <c r="D206" t="str">
-        <v>MY-05</v>
+        <v/>
       </c>
       <c r="E206" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F206" t="str">
-        <v>예약번호와 상태</v>
+        <v>예약 카드(상품명·날짜·인원·상태 배지·금액)</v>
       </c>
       <c r="G206" t="str">
-        <v>'예약 상세'의 예약번호와 상태가 실제 데이터와 같은지 대조한다.</v>
+        <v>'예약 내역'의 예약 카드(상품명·날짜·인원·상태 배지·금액)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H206" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I206" t="str">
         <v/>
@@ -7410,7 +7410,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>SCN-030</v>
+        <v>SCN-028</v>
       </c>
       <c r="B207" t="str">
         <v/>
@@ -7425,13 +7425,13 @@
         <v/>
       </c>
       <c r="F207" t="str">
-        <v>상품</v>
+        <v>D-day 표시</v>
       </c>
       <c r="G207" t="str">
-        <v>'예약 상세' 화면에서 상품이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'예약 내역'의 D-day 표시가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H207" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I207" t="str">
         <v/>
@@ -7442,7 +7442,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>SCN-030</v>
+        <v>SCN-028</v>
       </c>
       <c r="B208" t="str">
         <v/>
@@ -7457,13 +7457,13 @@
         <v/>
       </c>
       <c r="F208" t="str">
-        <v>일정 정보</v>
+        <v>바우처 바로가기</v>
       </c>
       <c r="G208" t="str">
-        <v>'예약 상세'의 일정 정보가 실제 데이터와 같은지 대조한다.</v>
+        <v>'예약 내역'에서 바우처 바로가기를 눌러 본다.</v>
       </c>
       <c r="H208" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I208" t="str">
         <v/>
@@ -7474,7 +7474,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>SCN-030</v>
+        <v>SCN-028</v>
       </c>
       <c r="B209" t="str">
         <v/>
@@ -7489,10 +7489,10 @@
         <v/>
       </c>
       <c r="F209" t="str">
-        <v>여행자 명단</v>
+        <v>후기 쓰기 유도</v>
       </c>
       <c r="G209" t="str">
-        <v>'예약 상세' 화면에서 여행자 명단이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'예약 내역' 화면에서 후기 쓰기 유도가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H209" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7506,28 +7506,28 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>SCN-030</v>
+        <v>SCN-029</v>
       </c>
       <c r="B210" t="str">
-        <v/>
+        <v>마이페이지</v>
       </c>
       <c r="C210" t="str">
-        <v/>
+        <v>예약 내역 없음</v>
       </c>
       <c r="D210" t="str">
-        <v/>
+        <v>MY-04</v>
       </c>
       <c r="E210" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F210" t="str">
-        <v>결제 내역(금액·수단·영수증)</v>
+        <v>빈 상태 일러스트와 안내</v>
       </c>
       <c r="G210" t="str">
-        <v>'예약 상세'에서 결제 내역(금액·수단·영수증)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>일부러 그 상황을 만들어 '예약 내역 없음' 화면이 나오게 한 뒤, 빈 상태 일러스트와 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H210" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I210" t="str">
         <v/>
@@ -7538,7 +7538,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>SCN-030</v>
+        <v>SCN-029</v>
       </c>
       <c r="B211" t="str">
         <v/>
@@ -7553,13 +7553,13 @@
         <v/>
       </c>
       <c r="F211" t="str">
-        <v>미팅 장소</v>
+        <v>인기 여행지 바로가기</v>
       </c>
       <c r="G211" t="str">
-        <v>'예약 상세' 화면에서 미팅 장소가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '예약 내역 없음' 화면이 나오게 한 뒤, 인기 여행지 바로가기가 보이는지 확인한다.</v>
       </c>
       <c r="H211" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I211" t="str">
         <v/>
@@ -7570,7 +7570,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>SCN-030</v>
+        <v>SCN-029</v>
       </c>
       <c r="B212" t="str">
         <v/>
@@ -7585,13 +7585,13 @@
         <v/>
       </c>
       <c r="F212" t="str">
-        <v>취소</v>
+        <v>첫 예약 쿠폰 안내</v>
       </c>
       <c r="G212" t="str">
-        <v>'예약 상세'에서 취소를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>일부러 그 상황을 만들어 '예약 내역 없음' 화면이 나오게 한 뒤, 첫 예약 쿠폰 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H212" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I212" t="str">
         <v/>
@@ -7605,25 +7605,25 @@
         <v>SCN-030</v>
       </c>
       <c r="B213" t="str">
-        <v/>
+        <v>마이페이지</v>
       </c>
       <c r="C213" t="str">
-        <v/>
+        <v>예약 상세</v>
       </c>
       <c r="D213" t="str">
-        <v/>
+        <v>MY-05</v>
       </c>
       <c r="E213" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F213" t="str">
-        <v>환불 규정 요약</v>
+        <v>예약번호와 상태</v>
       </c>
       <c r="G213" t="str">
-        <v>'예약 상세'에서 환불 규정 요약을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'예약 상세'의 예약번호와 상태가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H213" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I213" t="str">
         <v/>
@@ -7649,13 +7649,13 @@
         <v/>
       </c>
       <c r="F214" t="str">
-        <v>취소하기</v>
+        <v>상품</v>
       </c>
       <c r="G214" t="str">
-        <v>'예약 상세'에서 취소하기를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'예약 상세' 화면에서 상품이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H214" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I214" t="str">
         <v/>
@@ -7681,13 +7681,13 @@
         <v/>
       </c>
       <c r="F215" t="str">
-        <v>문의하기 버튼</v>
+        <v>일정 정보</v>
       </c>
       <c r="G215" t="str">
-        <v>'예약 상세'에서 문의하기 버튼을 눌러 본다.</v>
+        <v>'예약 상세'의 일정 정보가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H215" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I215" t="str">
         <v/>
@@ -7698,28 +7698,28 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B216" t="str">
-        <v>마이페이지</v>
+        <v/>
       </c>
       <c r="C216" t="str">
-        <v>예약 취소 신청</v>
+        <v/>
       </c>
       <c r="D216" t="str">
-        <v>MY-06</v>
+        <v/>
       </c>
       <c r="E216" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F216" t="str">
-        <v>출발일 기준 환불 수수료 자동 계산</v>
+        <v>여행자 명단</v>
       </c>
       <c r="G216" t="str">
-        <v>'예약 취소 신청'에서 출발일 기준 환불 수수료 자동 계산을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'예약 상세' 화면에서 여행자 명단이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H216" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I216" t="str">
         <v/>
@@ -7730,7 +7730,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B217" t="str">
         <v/>
@@ -7745,10 +7745,10 @@
         <v/>
       </c>
       <c r="F217" t="str">
-        <v>환불 예정 금액 표시</v>
+        <v>결제 내역(금액·수단·영수증)</v>
       </c>
       <c r="G217" t="str">
-        <v>'예약 취소 신청'에서 환불 예정 금액 표시를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'예약 상세'에서 결제 내역(금액·수단·영수증)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H217" t="str">
         <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
@@ -7762,7 +7762,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B218" t="str">
         <v/>
@@ -7777,13 +7777,13 @@
         <v/>
       </c>
       <c r="F218" t="str">
-        <v>취소 사유 선택</v>
+        <v>미팅 장소</v>
       </c>
       <c r="G218" t="str">
-        <v>'예약 취소 신청'에서 취소 사유 선택을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'예약 상세' 화면에서 미팅 장소가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H218" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I218" t="str">
         <v/>
@@ -7794,7 +7794,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B219" t="str">
         <v/>
@@ -7809,10 +7809,10 @@
         <v/>
       </c>
       <c r="F219" t="str">
-        <v>환불 계좌</v>
+        <v>취소</v>
       </c>
       <c r="G219" t="str">
-        <v>'예약 취소 신청'에서 환불 계좌를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'예약 상세'에서 취소를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H219" t="str">
         <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
@@ -7826,7 +7826,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B220" t="str">
         <v/>
@@ -7841,13 +7841,13 @@
         <v/>
       </c>
       <c r="F220" t="str">
-        <v>수단 확인</v>
+        <v>환불 규정 요약</v>
       </c>
       <c r="G220" t="str">
-        <v>'예약 취소 신청' 화면에서 수단 확인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'예약 상세'에서 환불 규정 요약을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H220" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I220" t="str">
         <v/>
@@ -7858,7 +7858,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B221" t="str">
         <v/>
@@ -7873,10 +7873,10 @@
         <v/>
       </c>
       <c r="F221" t="str">
-        <v>취소 확인 재확인</v>
+        <v>취소하기</v>
       </c>
       <c r="G221" t="str">
-        <v>'예약 취소 신청'에서 취소 확인 재확인을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'예약 상세'에서 취소하기를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H221" t="str">
         <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
@@ -7890,28 +7890,28 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>SCN-032</v>
+        <v>SCN-030</v>
       </c>
       <c r="B222" t="str">
-        <v>마이페이지</v>
+        <v/>
       </c>
       <c r="C222" t="str">
-        <v>취소 불가 안내</v>
+        <v/>
       </c>
       <c r="D222" t="str">
-        <v>MY-07</v>
+        <v/>
       </c>
       <c r="E222" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F222" t="str">
-        <v>취소 불가 사유와 기준일 안내</v>
+        <v>문의하기 버튼</v>
       </c>
       <c r="G222" t="str">
-        <v>일부러 그 상황을 만들어 '취소 불가 안내' 화면이 나오게 한 뒤, 취소 불가 사유와 기준일 안내가 보이는지 확인한다.</v>
+        <v>'예약 상세'에서 문의하기 버튼을 눌러 본다.</v>
       </c>
       <c r="H222" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I222" t="str">
         <v/>
@@ -7922,28 +7922,28 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>SCN-032</v>
+        <v>SCN-031</v>
       </c>
       <c r="B223" t="str">
-        <v/>
+        <v>마이페이지</v>
       </c>
       <c r="C223" t="str">
-        <v/>
+        <v>예약 취소 신청</v>
       </c>
       <c r="D223" t="str">
-        <v/>
+        <v>MY-06</v>
       </c>
       <c r="E223" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F223" t="str">
-        <v>규정 원문 표시</v>
+        <v>출발일 기준 환불 수수료 자동 계산</v>
       </c>
       <c r="G223" t="str">
-        <v>일부러 그 상황을 만들어 '취소 불가 안내' 화면이 나오게 한 뒤, 규정 원문 표시가 보이는지 확인한다.</v>
+        <v>'예약 취소 신청'에서 출발일 기준 환불 수수료 자동 계산을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H223" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I223" t="str">
         <v/>
@@ -7954,7 +7954,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>SCN-032</v>
+        <v>SCN-031</v>
       </c>
       <c r="B224" t="str">
         <v/>
@@ -7969,13 +7969,13 @@
         <v/>
       </c>
       <c r="F224" t="str">
-        <v>예외 요청 안내</v>
+        <v>환불 예정 금액 표시</v>
       </c>
       <c r="G224" t="str">
-        <v>일부러 그 상황을 만들어 '취소 불가 안내' 화면이 나오게 한 뒤, 예외 요청 안내가 보이는지 확인한다.</v>
+        <v>'예약 취소 신청'에서 환불 예정 금액 표시를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H224" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I224" t="str">
         <v/>
@@ -7986,7 +7986,7 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>SCN-032</v>
+        <v>SCN-031</v>
       </c>
       <c r="B225" t="str">
         <v/>
@@ -8001,13 +8001,13 @@
         <v/>
       </c>
       <c r="F225" t="str">
-        <v>고객센터 연결</v>
+        <v>취소 사유 선택</v>
       </c>
       <c r="G225" t="str">
-        <v>일부러 그 상황을 만들어 '취소 불가 안내' 화면이 나오게 한 뒤, 고객센터 연결이 보이는지 확인한다.</v>
+        <v>'예약 취소 신청'에서 취소 사유 선택을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H225" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I225" t="str">
         <v/>
@@ -8018,28 +8018,28 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>SCN-033</v>
+        <v>SCN-031</v>
       </c>
       <c r="B226" t="str">
-        <v>마이페이지</v>
+        <v/>
       </c>
       <c r="C226" t="str">
-        <v>후기 작성</v>
+        <v/>
       </c>
       <c r="D226" t="str">
-        <v>MY-08</v>
+        <v/>
       </c>
       <c r="E226" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F226" t="str">
-        <v>별점 선택</v>
+        <v>환불 계좌</v>
       </c>
       <c r="G226" t="str">
-        <v>'후기 작성' 화면에서 별점 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'예약 취소 신청'에서 환불 계좌를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H226" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I226" t="str">
         <v/>
@@ -8050,7 +8050,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>SCN-033</v>
+        <v>SCN-031</v>
       </c>
       <c r="B227" t="str">
         <v/>
@@ -8065,10 +8065,10 @@
         <v/>
       </c>
       <c r="F227" t="str">
-        <v>세부 항목 평가(가이드·일정·가격만족도)</v>
+        <v>수단 확인</v>
       </c>
       <c r="G227" t="str">
-        <v>'후기 작성' 화면에서 세부 항목 평가(가이드·일정·가격만족도)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'예약 취소 신청' 화면에서 수단 확인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H227" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8082,7 +8082,7 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>SCN-033</v>
+        <v>SCN-031</v>
       </c>
       <c r="B228" t="str">
         <v/>
@@ -8097,13 +8097,13 @@
         <v/>
       </c>
       <c r="F228" t="str">
-        <v>본문 입력(글자수 안내)</v>
+        <v>취소 확인 재확인</v>
       </c>
       <c r="G228" t="str">
-        <v>'후기 작성'의 본문 입력(글자수 안내)에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'예약 취소 신청'에서 취소 확인 재확인을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H228" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I228" t="str">
         <v/>
@@ -8114,28 +8114,28 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>SCN-033</v>
+        <v>SCN-032</v>
       </c>
       <c r="B229" t="str">
-        <v/>
+        <v>마이페이지</v>
       </c>
       <c r="C229" t="str">
-        <v/>
+        <v>취소 불가 안내</v>
       </c>
       <c r="D229" t="str">
-        <v/>
+        <v>MY-07</v>
       </c>
       <c r="E229" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F229" t="str">
-        <v>사진 첨부 최대 5장</v>
+        <v>취소 불가 사유와 기준일 안내</v>
       </c>
       <c r="G229" t="str">
-        <v>'후기 작성' 화면을 열고 사진 첨부 최대 5장이 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>일부러 그 상황을 만들어 '취소 불가 안내' 화면이 나오게 한 뒤, 취소 불가 사유와 기준일 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H229" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I229" t="str">
         <v/>
@@ -8146,7 +8146,7 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>SCN-033</v>
+        <v>SCN-032</v>
       </c>
       <c r="B230" t="str">
         <v/>
@@ -8161,13 +8161,13 @@
         <v/>
       </c>
       <c r="F230" t="str">
-        <v>동행 유형 선택</v>
+        <v>규정 원문 표시</v>
       </c>
       <c r="G230" t="str">
-        <v>'후기 작성' 화면에서 동행 유형 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '취소 불가 안내' 화면이 나오게 한 뒤, 규정 원문 표시가 보이는지 확인한다.</v>
       </c>
       <c r="H230" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I230" t="str">
         <v/>
@@ -8178,7 +8178,7 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>SCN-033</v>
+        <v>SCN-032</v>
       </c>
       <c r="B231" t="str">
         <v/>
@@ -8193,13 +8193,13 @@
         <v/>
       </c>
       <c r="F231" t="str">
-        <v>포인트 지급 안내</v>
+        <v>예외 요청 안내</v>
       </c>
       <c r="G231" t="str">
-        <v>'후기 작성' 화면에서 포인트 지급 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '취소 불가 안내' 화면이 나오게 한 뒤, 예외 요청 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H231" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I231" t="str">
         <v/>
@@ -8210,28 +8210,28 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>SCN-034</v>
+        <v>SCN-032</v>
       </c>
       <c r="B232" t="str">
-        <v>마이페이지</v>
+        <v/>
       </c>
       <c r="C232" t="str">
-        <v>쿠폰함</v>
+        <v/>
       </c>
       <c r="D232" t="str">
-        <v>MY-09</v>
+        <v/>
       </c>
       <c r="E232" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F232" t="str">
-        <v>사용 가능</v>
+        <v>고객센터 연결</v>
       </c>
       <c r="G232" t="str">
-        <v>'쿠폰함' 화면에서 사용 가능이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '취소 불가 안내' 화면이 나오게 한 뒤, 고객센터 연결이 보이는지 확인한다.</v>
       </c>
       <c r="H232" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I232" t="str">
         <v/>
@@ -8242,25 +8242,25 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B233" t="str">
-        <v/>
+        <v>마이페이지</v>
       </c>
       <c r="C233" t="str">
-        <v/>
+        <v>후기 작성</v>
       </c>
       <c r="D233" t="str">
-        <v/>
+        <v>MY-08</v>
       </c>
       <c r="E233" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F233" t="str">
-        <v>사용 완료</v>
+        <v>별점 선택</v>
       </c>
       <c r="G233" t="str">
-        <v>'쿠폰함' 화면에서 사용 완료가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'후기 작성' 화면에서 별점 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H233" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8274,7 +8274,7 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B234" t="str">
         <v/>
@@ -8289,13 +8289,13 @@
         <v/>
       </c>
       <c r="F234" t="str">
-        <v>만료 탭</v>
+        <v>세부 항목 평가(가이드·일정·가격만족도)</v>
       </c>
       <c r="G234" t="str">
-        <v>'쿠폰함'에서 만료 탭의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'후기 작성' 화면에서 세부 항목 평가(가이드·일정·가격만족도)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H234" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I234" t="str">
         <v/>
@@ -8306,7 +8306,7 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B235" t="str">
         <v/>
@@ -8321,13 +8321,13 @@
         <v/>
       </c>
       <c r="F235" t="str">
-        <v>쿠폰 카드(할인율·최소금액·유효기간·적용 대상)</v>
+        <v>본문 입력(글자수 안내)</v>
       </c>
       <c r="G235" t="str">
-        <v>'쿠폰함'의 쿠폰 카드(할인율·최소금액·유효기간·적용 대상)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'후기 작성'의 본문 입력(글자수 안내)에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H235" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I235" t="str">
         <v/>
@@ -8338,7 +8338,7 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B236" t="str">
         <v/>
@@ -8353,13 +8353,13 @@
         <v/>
       </c>
       <c r="F236" t="str">
-        <v>만료 임박 강조</v>
+        <v>사진 첨부 최대 5장</v>
       </c>
       <c r="G236" t="str">
-        <v>'쿠폰함' 화면에서 만료 임박 강조가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'후기 작성' 화면을 열고 사진 첨부 최대 5장이 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H236" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I236" t="str">
         <v/>
@@ -8370,7 +8370,7 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B237" t="str">
         <v/>
@@ -8385,13 +8385,13 @@
         <v/>
       </c>
       <c r="F237" t="str">
-        <v>쿠폰 코드 등록</v>
+        <v>동행 유형 선택</v>
       </c>
       <c r="G237" t="str">
-        <v>'쿠폰함'의 쿠폰 코드 등록에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'후기 작성' 화면에서 동행 유형 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H237" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I237" t="str">
         <v/>
@@ -8402,28 +8402,28 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>SCN-035</v>
+        <v>SCN-033</v>
       </c>
       <c r="B238" t="str">
-        <v>마이페이지</v>
+        <v/>
       </c>
       <c r="C238" t="str">
-        <v>내 여정</v>
+        <v/>
       </c>
       <c r="D238" t="str">
-        <v>MY-10</v>
+        <v/>
       </c>
       <c r="E238" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F238" t="str">
-        <v>여행 단위 카드(도시·기간·예약 건수)</v>
+        <v>포인트 지급 안내</v>
       </c>
       <c r="G238" t="str">
-        <v>'내 여정'의 여행 단위 카드(도시·기간·예약 건수)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'후기 작성' 화면에서 포인트 지급 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H238" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I238" t="str">
         <v/>
@@ -8434,25 +8434,25 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B239" t="str">
-        <v/>
+        <v>마이페이지</v>
       </c>
       <c r="C239" t="str">
-        <v/>
+        <v>쿠폰함</v>
       </c>
       <c r="D239" t="str">
-        <v/>
+        <v>MY-09</v>
       </c>
       <c r="E239" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F239" t="str">
-        <v>날짜별 타임라인에 예약을 시간순 배치</v>
+        <v>사용 가능</v>
       </c>
       <c r="G239" t="str">
-        <v>'내 여정' 화면에서 날짜별 타임라인에 예약을 시간순 배치가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'쿠폰함' 화면에서 사용 가능이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H239" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8466,7 +8466,7 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B240" t="str">
         <v/>
@@ -8481,10 +8481,10 @@
         <v/>
       </c>
       <c r="F240" t="str">
-        <v>시간이 겹치는 예약 경고</v>
+        <v>사용 완료</v>
       </c>
       <c r="G240" t="str">
-        <v>'내 여정' 화면에서 시간이 겹치는 예약 경고가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'쿠폰함' 화면에서 사용 완료가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H240" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8498,7 +8498,7 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B241" t="str">
         <v/>
@@ -8513,13 +8513,13 @@
         <v/>
       </c>
       <c r="F241" t="str">
-        <v>앞뒤 일정 사이 이동 시간 여유 안내</v>
+        <v>만료 탭</v>
       </c>
       <c r="G241" t="str">
-        <v>'내 여정'에서 앞뒤 일정 사이 이동 시간 여유 안내를 눌러 본다.</v>
+        <v>'쿠폰함'에서 만료 탭의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H241" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I241" t="str">
         <v/>
@@ -8530,7 +8530,7 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B242" t="str">
         <v/>
@@ -8545,13 +8545,13 @@
         <v/>
       </c>
       <c r="F242" t="str">
-        <v>현지 시각과 한국 시차 표시</v>
+        <v>쿠폰 카드(할인율·최소금액·유효기간·적용 대상)</v>
       </c>
       <c r="G242" t="str">
-        <v>'내 여정'의 현지 시각과 한국 시차 표시가 실제 데이터와 같은지 대조한다.</v>
+        <v>'쿠폰함'의 쿠폰 카드(할인율·최소금액·유효기간·적용 대상)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H242" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I242" t="str">
         <v/>
@@ -8562,7 +8562,7 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B243" t="str">
         <v/>
@@ -8577,10 +8577,10 @@
         <v/>
       </c>
       <c r="F243" t="str">
-        <v>빈 시간대에 추천 상품 노출</v>
+        <v>만료 임박 강조</v>
       </c>
       <c r="G243" t="str">
-        <v>'내 여정' 화면에서 빈 시간대에 추천 상품 노출이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'쿠폰함' 화면에서 만료 임박 강조가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H243" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8594,7 +8594,7 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B244" t="str">
         <v/>
@@ -8609,13 +8609,13 @@
         <v/>
       </c>
       <c r="F244" t="str">
-        <v>일정별 바우처</v>
+        <v>쿠폰 코드 등록</v>
       </c>
       <c r="G244" t="str">
-        <v>'내 여정' 화면에서 일정별 바우처가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'쿠폰함'의 쿠폰 코드 등록에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H244" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I244" t="str">
         <v/>
@@ -8629,25 +8629,25 @@
         <v>SCN-035</v>
       </c>
       <c r="B245" t="str">
-        <v/>
+        <v>마이페이지</v>
       </c>
       <c r="C245" t="str">
-        <v/>
+        <v>내 여정</v>
       </c>
       <c r="D245" t="str">
-        <v/>
+        <v>MY-10</v>
       </c>
       <c r="E245" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F245" t="str">
-        <v>예약 상세 바로가기</v>
+        <v>여행 단위 카드(도시·기간·예약 건수)</v>
       </c>
       <c r="G245" t="str">
-        <v>'내 여정'에서 예약 상세 바로가기를 눌러 본다.</v>
+        <v>'내 여정'의 여행 단위 카드(도시·기간·예약 건수)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H245" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I245" t="str">
         <v/>
@@ -8673,10 +8673,10 @@
         <v/>
       </c>
       <c r="F246" t="str">
-        <v>당일 날씨와 준비물 체크</v>
+        <v>날짜별 타임라인에 예약을 시간순 배치</v>
       </c>
       <c r="G246" t="str">
-        <v>'내 여정' 화면에서 당일 날씨와 준비물 체크가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 여정' 화면에서 날짜별 타임라인에 예약을 시간순 배치가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H246" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8705,10 +8705,10 @@
         <v/>
       </c>
       <c r="F247" t="str">
-        <v>동행자에게 일정 공유</v>
+        <v>시간이 겹치는 예약 경고</v>
       </c>
       <c r="G247" t="str">
-        <v>'내 여정' 화면에서 동행자에게 일정 공유가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 여정' 화면에서 시간이 겹치는 예약 경고가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H247" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8737,13 +8737,13 @@
         <v/>
       </c>
       <c r="F248" t="str">
-        <v>일정표 이미지</v>
+        <v>앞뒤 일정 사이 이동 시간 여유 안내</v>
       </c>
       <c r="G248" t="str">
-        <v>'내 여정' 화면에서 일정표 이미지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 여정'에서 앞뒤 일정 사이 이동 시간 여유 안내를 눌러 본다.</v>
       </c>
       <c r="H248" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I248" t="str">
         <v/>
@@ -8769,13 +8769,13 @@
         <v/>
       </c>
       <c r="F249" t="str">
-        <v>PDF 저장</v>
+        <v>현지 시각과 한국 시차 표시</v>
       </c>
       <c r="G249" t="str">
-        <v>'내 여정' 화면에서 PDF 저장이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 여정'의 현지 시각과 한국 시차 표시가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H249" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I249" t="str">
         <v/>
@@ -8786,28 +8786,28 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B250" t="str">
-        <v>마이페이지</v>
+        <v/>
       </c>
       <c r="C250" t="str">
-        <v>내 후기</v>
+        <v/>
       </c>
       <c r="D250" t="str">
-        <v>MY-11</v>
+        <v/>
       </c>
       <c r="E250" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F250" t="str">
-        <v>작성 가능</v>
+        <v>빈 시간대에 추천 상품 노출</v>
       </c>
       <c r="G250" t="str">
-        <v>'내 후기'의 작성 가능에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'내 여정' 화면에서 빈 시간대에 추천 상품 노출이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H250" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I250" t="str">
         <v/>
@@ -8818,7 +8818,7 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B251" t="str">
         <v/>
@@ -8833,13 +8833,13 @@
         <v/>
       </c>
       <c r="F251" t="str">
-        <v>작성 완료 탭</v>
+        <v>일정별 바우처</v>
       </c>
       <c r="G251" t="str">
-        <v>'내 후기'의 작성 완료 탭에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'내 여정' 화면에서 일정별 바우처가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H251" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I251" t="str">
         <v/>
@@ -8850,7 +8850,7 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B252" t="str">
         <v/>
@@ -8865,13 +8865,13 @@
         <v/>
       </c>
       <c r="F252" t="str">
-        <v>미작성 후기 카드(상품·이용일·작성 기한 D-day)</v>
+        <v>예약 상세 바로가기</v>
       </c>
       <c r="G252" t="str">
-        <v>'내 후기'의 미작성 후기 카드(상품·이용일·작성 기한 D-day)에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'내 여정'에서 예약 상세 바로가기를 눌러 본다.</v>
       </c>
       <c r="H252" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I252" t="str">
         <v/>
@@ -8882,7 +8882,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B253" t="str">
         <v/>
@@ -8897,13 +8897,13 @@
         <v/>
       </c>
       <c r="F253" t="str">
-        <v>작성한 후기 목록(별점·본문·사진·작성일)</v>
+        <v>당일 날씨와 준비물 체크</v>
       </c>
       <c r="G253" t="str">
-        <v>'내 후기'의 작성한 후기 목록(별점·본문·사진·작성일)에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'내 여정' 화면에서 당일 날씨와 준비물 체크가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H253" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I253" t="str">
         <v/>
@@ -8914,7 +8914,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B254" t="str">
         <v/>
@@ -8929,10 +8929,10 @@
         <v/>
       </c>
       <c r="F254" t="str">
-        <v>후기 수정과 삭제</v>
+        <v>동행자에게 일정 공유</v>
       </c>
       <c r="G254" t="str">
-        <v>'내 후기' 화면에서 후기 수정과 삭제가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 여정' 화면에서 동행자에게 일정 공유가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H254" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8946,7 +8946,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B255" t="str">
         <v/>
@@ -8961,13 +8961,13 @@
         <v/>
       </c>
       <c r="F255" t="str">
-        <v>판매자 답변 표시</v>
+        <v>일정표 이미지</v>
       </c>
       <c r="G255" t="str">
-        <v>'내 후기'의 판매자 답변 표시가 실제 데이터와 같은지 대조한다.</v>
+        <v>'내 여정' 화면에서 일정표 이미지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H255" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I255" t="str">
         <v/>
@@ -8978,7 +8978,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B256" t="str">
         <v/>
@@ -8993,10 +8993,10 @@
         <v/>
       </c>
       <c r="F256" t="str">
-        <v>받은 도움돼요 수</v>
+        <v>PDF 저장</v>
       </c>
       <c r="G256" t="str">
-        <v>'내 후기' 화면에서 받은 도움돼요 수가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 여정' 화면에서 PDF 저장이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H256" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9013,25 +9013,25 @@
         <v>SCN-036</v>
       </c>
       <c r="B257" t="str">
-        <v/>
+        <v>마이페이지</v>
       </c>
       <c r="C257" t="str">
-        <v/>
+        <v>내 후기</v>
       </c>
       <c r="D257" t="str">
-        <v/>
+        <v>MY-11</v>
       </c>
       <c r="E257" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F257" t="str">
-        <v>후기로 받은 포인트 합계</v>
+        <v>작성 가능</v>
       </c>
       <c r="G257" t="str">
-        <v>'내 후기'의 후기로 받은 포인트 합계가 실제 데이터와 같은지 대조한다.</v>
+        <v>'내 후기'의 작성 가능에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H257" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I257" t="str">
         <v/>
@@ -9057,10 +9057,10 @@
         <v/>
       </c>
       <c r="F258" t="str">
-        <v>작성 기한 만료 안내</v>
+        <v>작성 완료 탭</v>
       </c>
       <c r="G258" t="str">
-        <v>'내 후기'의 작성 기한 만료 안내에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'내 후기'의 작성 완료 탭에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H258" t="str">
         <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
@@ -9089,13 +9089,13 @@
         <v/>
       </c>
       <c r="F259" t="str">
-        <v>후기가 없을 때 빈 상태</v>
+        <v>미작성 후기 카드(상품·이용일·작성 기한 D-day)</v>
       </c>
       <c r="G259" t="str">
-        <v>'내 후기'의 후기가 없을 때 빈 상태가 실제 데이터와 같은지 대조한다.</v>
+        <v>'내 후기'의 미작성 후기 카드(상품·이용일·작성 기한 D-day)에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H259" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I259" t="str">
         <v/>
@@ -9121,13 +9121,13 @@
         <v/>
       </c>
       <c r="F260" t="str">
-        <v>상품 상세로 이동</v>
+        <v>작성한 후기 목록(별점·본문·사진·작성일)</v>
       </c>
       <c r="G260" t="str">
-        <v>'내 후기'에서 상품 상세로 이동을 눌러 본다.</v>
+        <v>'내 후기'의 작성한 후기 목록(별점·본문·사진·작성일)에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H260" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I260" t="str">
         <v/>
@@ -9138,25 +9138,25 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B261" t="str">
-        <v>마이페이지</v>
+        <v/>
       </c>
       <c r="C261" t="str">
-        <v>알림함</v>
+        <v/>
       </c>
       <c r="D261" t="str">
-        <v>MY-12</v>
+        <v/>
       </c>
       <c r="E261" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F261" t="str">
-        <v>전체</v>
+        <v>후기 수정과 삭제</v>
       </c>
       <c r="G261" t="str">
-        <v>'알림함' 화면에서 전체가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 후기' 화면에서 후기 수정과 삭제가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H261" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9170,7 +9170,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B262" t="str">
         <v/>
@@ -9185,13 +9185,13 @@
         <v/>
       </c>
       <c r="F262" t="str">
-        <v>예약</v>
+        <v>판매자 답변 표시</v>
       </c>
       <c r="G262" t="str">
-        <v>'알림함' 화면에서 예약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 후기'의 판매자 답변 표시가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H262" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I262" t="str">
         <v/>
@@ -9202,7 +9202,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B263" t="str">
         <v/>
@@ -9217,10 +9217,10 @@
         <v/>
       </c>
       <c r="F263" t="str">
-        <v>혜택</v>
+        <v>받은 도움돼요 수</v>
       </c>
       <c r="G263" t="str">
-        <v>'알림함' 화면에서 혜택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 후기' 화면에서 받은 도움돼요 수가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H263" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9234,7 +9234,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B264" t="str">
         <v/>
@@ -9249,13 +9249,13 @@
         <v/>
       </c>
       <c r="F264" t="str">
-        <v>공지 탭</v>
+        <v>후기로 받은 포인트 합계</v>
       </c>
       <c r="G264" t="str">
-        <v>'알림함'에서 공지 탭의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'내 후기'의 후기로 받은 포인트 합계가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H264" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I264" t="str">
         <v/>
@@ -9266,7 +9266,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B265" t="str">
         <v/>
@@ -9281,13 +9281,13 @@
         <v/>
       </c>
       <c r="F265" t="str">
-        <v>알림 카드(아이콘·제목·본문 요약·받은 시각)</v>
+        <v>작성 기한 만료 안내</v>
       </c>
       <c r="G265" t="str">
-        <v>'알림함'의 알림 카드(아이콘·제목·본문 요약·받은 시각)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'내 후기'의 작성 기한 만료 안내에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H265" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I265" t="str">
         <v/>
@@ -9298,7 +9298,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B266" t="str">
         <v/>
@@ -9313,10 +9313,10 @@
         <v/>
       </c>
       <c r="F266" t="str">
-        <v>읽지 않음 점 표시와 모두 읽음 처리</v>
+        <v>후기가 없을 때 빈 상태</v>
       </c>
       <c r="G266" t="str">
-        <v>'알림함'의 읽지 않음 점 표시와 모두 읽음 처리가 실제 데이터와 같은지 대조한다.</v>
+        <v>'내 후기'의 후기가 없을 때 빈 상태가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H266" t="str">
         <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
@@ -9330,7 +9330,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B267" t="str">
         <v/>
@@ -9345,10 +9345,10 @@
         <v/>
       </c>
       <c r="F267" t="str">
-        <v>알림별 관련 화면 바로가기</v>
+        <v>상품 상세로 이동</v>
       </c>
       <c r="G267" t="str">
-        <v>'알림함'에서 알림별 관련 화면 바로가기를 눌러 본다.</v>
+        <v>'내 후기'에서 상품 상세로 이동을 눌러 본다.</v>
       </c>
       <c r="H267" t="str">
         <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
@@ -9365,22 +9365,22 @@
         <v>SCN-037</v>
       </c>
       <c r="B268" t="str">
-        <v/>
+        <v>마이페이지</v>
       </c>
       <c r="C268" t="str">
-        <v/>
+        <v>알림함</v>
       </c>
       <c r="D268" t="str">
-        <v/>
+        <v>MY-12</v>
       </c>
       <c r="E268" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F268" t="str">
-        <v>출발 임박</v>
+        <v>전체</v>
       </c>
       <c r="G268" t="str">
-        <v>'알림함' 화면에서 출발 임박이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'알림함' 화면에서 전체가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H268" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9409,10 +9409,10 @@
         <v/>
       </c>
       <c r="F269" t="str">
-        <v>확정 알림 상단 고정</v>
+        <v>예약</v>
       </c>
       <c r="G269" t="str">
-        <v>'알림함' 화면에서 확정 알림 상단 고정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'알림함' 화면에서 예약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H269" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9441,10 +9441,10 @@
         <v/>
       </c>
       <c r="F270" t="str">
-        <v>현지 이슈 알림 붉게 강조</v>
+        <v>혜택</v>
       </c>
       <c r="G270" t="str">
-        <v>'알림함' 화면에서 현지 이슈 알림 붉게 강조가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'알림함' 화면에서 혜택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H270" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9473,13 +9473,13 @@
         <v/>
       </c>
       <c r="F271" t="str">
-        <v>개별 삭제와 전체 비우기</v>
+        <v>공지 탭</v>
       </c>
       <c r="G271" t="str">
-        <v>'알림함' 화면에서 개별 삭제와 전체 비우기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'알림함'에서 공지 탭의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H271" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I271" t="str">
         <v/>
@@ -9505,13 +9505,13 @@
         <v/>
       </c>
       <c r="F272" t="str">
-        <v>알림 수신 설정 바로가기</v>
+        <v>알림 카드(아이콘·제목·본문 요약·받은 시각)</v>
       </c>
       <c r="G272" t="str">
-        <v>'알림함'에서 알림 수신 설정 바로가기를 눌러 본다.</v>
+        <v>'알림함'의 알림 카드(아이콘·제목·본문 요약·받은 시각)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H272" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I272" t="str">
         <v/>
@@ -9537,13 +9537,13 @@
         <v/>
       </c>
       <c r="F273" t="str">
-        <v>30일 지난 알림 자동 삭제 안내</v>
+        <v>읽지 않음 점 표시와 모두 읽음 처리</v>
       </c>
       <c r="G273" t="str">
-        <v>'알림함' 화면에서 30일 지난 알림 자동 삭제 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'알림함'의 읽지 않음 점 표시와 모두 읽음 처리가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H273" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I273" t="str">
         <v/>
@@ -9569,13 +9569,13 @@
         <v/>
       </c>
       <c r="F274" t="str">
-        <v>알림이 없을 때 빈 상태</v>
+        <v>알림별 관련 화면 바로가기</v>
       </c>
       <c r="G274" t="str">
-        <v>'알림함'의 알림이 없을 때 빈 상태가 실제 데이터와 같은지 대조한다.</v>
+        <v>'알림함'에서 알림별 관련 화면 바로가기를 눌러 본다.</v>
       </c>
       <c r="H274" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I274" t="str">
         <v/>
@@ -9586,28 +9586,28 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>SCN-038</v>
+        <v>SCN-037</v>
       </c>
       <c r="B275" t="str">
-        <v>마이페이지</v>
+        <v/>
       </c>
       <c r="C275" t="str">
-        <v>계정 설정</v>
+        <v/>
       </c>
       <c r="D275" t="str">
-        <v>MY-13</v>
+        <v/>
       </c>
       <c r="E275" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F275" t="str">
-        <v>프로필 정보 수정(이름·여권 영문명·연락처)</v>
+        <v>출발 임박</v>
       </c>
       <c r="G275" t="str">
-        <v>'계정 설정'의 프로필 정보 수정(이름·여권 영문명·연락처)가 실제 데이터와 같은지 대조한다.</v>
+        <v>'알림함' 화면에서 출발 임박이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H275" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I275" t="str">
         <v/>
@@ -9618,7 +9618,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>SCN-038</v>
+        <v>SCN-037</v>
       </c>
       <c r="B276" t="str">
         <v/>
@@ -9633,10 +9633,10 @@
         <v/>
       </c>
       <c r="F276" t="str">
-        <v>이메일 변경과 인증 메일 발송</v>
+        <v>확정 알림 상단 고정</v>
       </c>
       <c r="G276" t="str">
-        <v>'계정 설정' 화면에서 이메일 변경과 인증 메일 발송이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'알림함' 화면에서 확정 알림 상단 고정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H276" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9650,7 +9650,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>SCN-038</v>
+        <v>SCN-037</v>
       </c>
       <c r="B277" t="str">
         <v/>
@@ -9665,10 +9665,10 @@
         <v/>
       </c>
       <c r="F277" t="str">
-        <v>비밀번호 변경(현재·새 비밀번호·조건 표시)</v>
+        <v>현지 이슈 알림 붉게 강조</v>
       </c>
       <c r="G277" t="str">
-        <v>'계정 설정' 화면에서 비밀번호 변경(현재·새 비밀번호·조건 표시)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'알림함' 화면에서 현지 이슈 알림 붉게 강조가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H277" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9682,7 +9682,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>SCN-038</v>
+        <v>SCN-037</v>
       </c>
       <c r="B278" t="str">
         <v/>
@@ -9697,10 +9697,10 @@
         <v/>
       </c>
       <c r="F278" t="str">
-        <v>소셜 계정 연결과 해제</v>
+        <v>개별 삭제와 전체 비우기</v>
       </c>
       <c r="G278" t="str">
-        <v>'계정 설정' 화면에서 소셜 계정 연결과 해제가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'알림함' 화면에서 개별 삭제와 전체 비우기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H278" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9714,7 +9714,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>SCN-038</v>
+        <v>SCN-037</v>
       </c>
       <c r="B279" t="str">
         <v/>
@@ -9729,13 +9729,13 @@
         <v/>
       </c>
       <c r="F279" t="str">
-        <v>알림 수신 설정(카톡·이메일·앱 푸시 개별 토글)</v>
+        <v>알림 수신 설정 바로가기</v>
       </c>
       <c r="G279" t="str">
-        <v>'계정 설정' 화면에서 알림 수신 설정(카톡·이메일·앱 푸시 개별 토글)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'알림함'에서 알림 수신 설정 바로가기를 눌러 본다.</v>
       </c>
       <c r="H279" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I279" t="str">
         <v/>
@@ -9746,7 +9746,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>SCN-038</v>
+        <v>SCN-037</v>
       </c>
       <c r="B280" t="str">
         <v/>
@@ -9761,10 +9761,10 @@
         <v/>
       </c>
       <c r="F280" t="str">
-        <v>마케팅 수신 동의와 변경 이력</v>
+        <v>30일 지난 알림 자동 삭제 안내</v>
       </c>
       <c r="G280" t="str">
-        <v>'계정 설정' 화면에서 마케팅 수신 동의와 변경 이력이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'알림함' 화면에서 30일 지난 알림 자동 삭제 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H280" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9778,7 +9778,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>SCN-038</v>
+        <v>SCN-037</v>
       </c>
       <c r="B281" t="str">
         <v/>
@@ -9793,13 +9793,13 @@
         <v/>
       </c>
       <c r="F281" t="str">
-        <v>표시 언어와 결제 통화 설정</v>
+        <v>알림이 없을 때 빈 상태</v>
       </c>
       <c r="G281" t="str">
-        <v>'계정 설정'에서 표시 언어와 결제 통화 설정을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'알림함'의 알림이 없을 때 빈 상태가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H281" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I281" t="str">
         <v/>
@@ -9813,22 +9813,22 @@
         <v>SCN-038</v>
       </c>
       <c r="B282" t="str">
-        <v/>
+        <v>마이페이지</v>
       </c>
       <c r="C282" t="str">
-        <v/>
+        <v>계정 설정</v>
       </c>
       <c r="D282" t="str">
-        <v/>
+        <v>MY-13</v>
       </c>
       <c r="E282" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F282" t="str">
-        <v>자주 쓰는 여행자 정보 저장</v>
+        <v>프로필 정보 수정(이름·여권 영문명·연락처)</v>
       </c>
       <c r="G282" t="str">
-        <v>'계정 설정'의 자주 쓰는 여행자 정보 저장이 실제 데이터와 같은지 대조한다.</v>
+        <v>'계정 설정'의 프로필 정보 수정(이름·여권 영문명·연락처)가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H282" t="str">
         <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
@@ -9857,10 +9857,10 @@
         <v/>
       </c>
       <c r="F283" t="str">
-        <v>관리</v>
+        <v>이메일 변경과 인증 메일 발송</v>
       </c>
       <c r="G283" t="str">
-        <v>'계정 설정' 화면에서 관리가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'계정 설정' 화면에서 이메일 변경과 인증 메일 발송이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H283" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9889,13 +9889,13 @@
         <v/>
       </c>
       <c r="F284" t="str">
-        <v>내 개인정보 내려받기</v>
+        <v>비밀번호 변경(현재·새 비밀번호·조건 표시)</v>
       </c>
       <c r="G284" t="str">
-        <v>'계정 설정'의 내 개인정보 내려받기가 실제 데이터와 같은지 대조한다.</v>
+        <v>'계정 설정' 화면에서 비밀번호 변경(현재·새 비밀번호·조건 표시)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H284" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I284" t="str">
         <v/>
@@ -9921,10 +9921,10 @@
         <v/>
       </c>
       <c r="F285" t="str">
-        <v>회원 탈퇴와 유의사항</v>
+        <v>소셜 계정 연결과 해제</v>
       </c>
       <c r="G285" t="str">
-        <v>'계정 설정' 화면에서 회원 탈퇴와 유의사항이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'계정 설정' 화면에서 소셜 계정 연결과 해제가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H285" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9938,28 +9938,28 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>SCN-039</v>
+        <v>SCN-038</v>
       </c>
       <c r="B286" t="str">
-        <v>고객센터</v>
+        <v/>
       </c>
       <c r="C286" t="str">
-        <v>자주 묻는 질문</v>
+        <v/>
       </c>
       <c r="D286" t="str">
-        <v>CS-01</v>
+        <v/>
       </c>
       <c r="E286" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F286" t="str">
-        <v>카테고리 탭(예약·결제·취소환불·바우처·현지이용)</v>
+        <v>알림 수신 설정(카톡·이메일·앱 푸시 개별 토글)</v>
       </c>
       <c r="G286" t="str">
-        <v>'자주 묻는 질문'에서 카테고리 탭(예약·결제·취소환불·바우처·현지이용)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'계정 설정' 화면에서 알림 수신 설정(카톡·이메일·앱 푸시 개별 토글)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H286" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I286" t="str">
         <v/>
@@ -9970,7 +9970,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>SCN-039</v>
+        <v>SCN-038</v>
       </c>
       <c r="B287" t="str">
         <v/>
@@ -9985,13 +9985,13 @@
         <v/>
       </c>
       <c r="F287" t="str">
-        <v>검색창</v>
+        <v>마케팅 수신 동의와 변경 이력</v>
       </c>
       <c r="G287" t="str">
-        <v>'자주 묻는 질문'의 검색창에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'계정 설정' 화면에서 마케팅 수신 동의와 변경 이력이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H287" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I287" t="str">
         <v/>
@@ -10002,7 +10002,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>SCN-039</v>
+        <v>SCN-038</v>
       </c>
       <c r="B288" t="str">
         <v/>
@@ -10017,13 +10017,13 @@
         <v/>
       </c>
       <c r="F288" t="str">
-        <v>아코디언 질문 목록</v>
+        <v>표시 언어와 결제 통화 설정</v>
       </c>
       <c r="G288" t="str">
-        <v>'자주 묻는 질문'의 아코디언 질문 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'계정 설정'에서 표시 언어와 결제 통화 설정을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H288" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I288" t="str">
         <v/>
@@ -10034,7 +10034,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>SCN-039</v>
+        <v>SCN-038</v>
       </c>
       <c r="B289" t="str">
         <v/>
@@ -10049,13 +10049,13 @@
         <v/>
       </c>
       <c r="F289" t="str">
-        <v>도움됐어요 버튼</v>
+        <v>자주 쓰는 여행자 정보 저장</v>
       </c>
       <c r="G289" t="str">
-        <v>'자주 묻는 질문'에서 도움됐어요 버튼을 눌러 본다.</v>
+        <v>'계정 설정'의 자주 쓰는 여행자 정보 저장이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H289" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I289" t="str">
         <v/>
@@ -10066,7 +10066,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>SCN-039</v>
+        <v>SCN-038</v>
       </c>
       <c r="B290" t="str">
         <v/>
@@ -10081,10 +10081,10 @@
         <v/>
       </c>
       <c r="F290" t="str">
-        <v>문의하기 유도</v>
+        <v>관리</v>
       </c>
       <c r="G290" t="str">
-        <v>'자주 묻는 질문' 화면에서 문의하기 유도가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'계정 설정' 화면에서 관리가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H290" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10098,28 +10098,28 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>SCN-040</v>
+        <v>SCN-038</v>
       </c>
       <c r="B291" t="str">
-        <v>고객센터</v>
+        <v/>
       </c>
       <c r="C291" t="str">
-        <v>1:1 문의 작성</v>
+        <v/>
       </c>
       <c r="D291" t="str">
-        <v>CS-02</v>
+        <v/>
       </c>
       <c r="E291" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F291" t="str">
-        <v>문의 유형 선택</v>
+        <v>내 개인정보 내려받기</v>
       </c>
       <c r="G291" t="str">
-        <v>'1:1 문의 작성' 화면에서 문의 유형 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'계정 설정'의 내 개인정보 내려받기가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H291" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I291" t="str">
         <v/>
@@ -10130,7 +10130,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>SCN-040</v>
+        <v>SCN-038</v>
       </c>
       <c r="B292" t="str">
         <v/>
@@ -10145,10 +10145,10 @@
         <v/>
       </c>
       <c r="F292" t="str">
-        <v>관련 예약 선택</v>
+        <v>회원 탈퇴와 유의사항</v>
       </c>
       <c r="G292" t="str">
-        <v>'1:1 문의 작성' 화면에서 관련 예약 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'계정 설정' 화면에서 회원 탈퇴와 유의사항이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H292" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10162,28 +10162,28 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>SCN-040</v>
+        <v>SCN-039</v>
       </c>
       <c r="B293" t="str">
-        <v/>
+        <v>고객센터</v>
       </c>
       <c r="C293" t="str">
-        <v/>
+        <v>자주 묻는 질문</v>
       </c>
       <c r="D293" t="str">
-        <v/>
+        <v>CS-01</v>
       </c>
       <c r="E293" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F293" t="str">
-        <v>제목</v>
+        <v>카테고리 탭(예약·결제·취소환불·바우처·현지이용)</v>
       </c>
       <c r="G293" t="str">
-        <v>'1:1 문의 작성' 화면에서 제목이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'자주 묻는 질문'에서 카테고리 탭(예약·결제·취소환불·바우처·현지이용)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H293" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I293" t="str">
         <v/>
@@ -10194,7 +10194,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>SCN-040</v>
+        <v>SCN-039</v>
       </c>
       <c r="B294" t="str">
         <v/>
@@ -10209,10 +10209,10 @@
         <v/>
       </c>
       <c r="F294" t="str">
-        <v>내용 입력</v>
+        <v>검색창</v>
       </c>
       <c r="G294" t="str">
-        <v>'1:1 문의 작성'의 내용 입력에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'자주 묻는 질문'의 검색창에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H294" t="str">
         <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
@@ -10226,7 +10226,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>SCN-040</v>
+        <v>SCN-039</v>
       </c>
       <c r="B295" t="str">
         <v/>
@@ -10241,13 +10241,13 @@
         <v/>
       </c>
       <c r="F295" t="str">
-        <v>파일 첨부</v>
+        <v>아코디언 질문 목록</v>
       </c>
       <c r="G295" t="str">
-        <v>'1:1 문의 작성'의 파일 첨부에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'자주 묻는 질문'의 아코디언 질문 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H295" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I295" t="str">
         <v/>
@@ -10258,7 +10258,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>SCN-040</v>
+        <v>SCN-039</v>
       </c>
       <c r="B296" t="str">
         <v/>
@@ -10273,13 +10273,13 @@
         <v/>
       </c>
       <c r="F296" t="str">
-        <v>답변 받을 방법 선택</v>
+        <v>도움됐어요 버튼</v>
       </c>
       <c r="G296" t="str">
-        <v>'1:1 문의 작성' 화면에서 답변 받을 방법 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'자주 묻는 질문'에서 도움됐어요 버튼을 눌러 본다.</v>
       </c>
       <c r="H296" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I296" t="str">
         <v/>
@@ -10290,7 +10290,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>SCN-040</v>
+        <v>SCN-039</v>
       </c>
       <c r="B297" t="str">
         <v/>
@@ -10305,10 +10305,10 @@
         <v/>
       </c>
       <c r="F297" t="str">
-        <v>예상 답변 시간 안내</v>
+        <v>문의하기 유도</v>
       </c>
       <c r="G297" t="str">
-        <v>'1:1 문의 작성' 화면에서 예상 답변 시간 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'자주 묻는 질문' 화면에서 문의하기 유도가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H297" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10322,28 +10322,28 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>SCN-041</v>
+        <v>SCN-040</v>
       </c>
       <c r="B298" t="str">
         <v>고객센터</v>
       </c>
       <c r="C298" t="str">
-        <v>문의 내역</v>
+        <v>1:1 문의 작성</v>
       </c>
       <c r="D298" t="str">
-        <v>CS-03</v>
+        <v>CS-02</v>
       </c>
       <c r="E298" t="str">
         <v>기본</v>
       </c>
       <c r="F298" t="str">
-        <v>문의 목록(제목·유형·작성일·상태 배지)</v>
+        <v>문의 유형 선택</v>
       </c>
       <c r="G298" t="str">
-        <v>'문의 내역'의 문의 목록(제목·유형·작성일·상태 배지)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'1:1 문의 작성' 화면에서 문의 유형 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H298" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I298" t="str">
         <v/>
@@ -10354,7 +10354,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>SCN-041</v>
+        <v>SCN-040</v>
       </c>
       <c r="B299" t="str">
         <v/>
@@ -10369,13 +10369,13 @@
         <v/>
       </c>
       <c r="F299" t="str">
-        <v>답변 완료 여부 표시</v>
+        <v>관련 예약 선택</v>
       </c>
       <c r="G299" t="str">
-        <v>'문의 내역'의 답변 완료 여부 표시가 실제 데이터와 같은지 대조한다.</v>
+        <v>'1:1 문의 작성' 화면에서 관련 예약 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H299" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I299" t="str">
         <v/>
@@ -10386,7 +10386,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>SCN-041</v>
+        <v>SCN-040</v>
       </c>
       <c r="B300" t="str">
         <v/>
@@ -10401,10 +10401,10 @@
         <v/>
       </c>
       <c r="F300" t="str">
-        <v>문의 상세 펼치기</v>
+        <v>제목</v>
       </c>
       <c r="G300" t="str">
-        <v>'문의 내역' 화면에서 문의 상세 펼치기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'1:1 문의 작성' 화면에서 제목이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H300" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10418,7 +10418,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>SCN-041</v>
+        <v>SCN-040</v>
       </c>
       <c r="B301" t="str">
         <v/>
@@ -10433,13 +10433,13 @@
         <v/>
       </c>
       <c r="F301" t="str">
-        <v>추가 질문 이어쓰기</v>
+        <v>내용 입력</v>
       </c>
       <c r="G301" t="str">
-        <v>'문의 내역' 화면에서 추가 질문 이어쓰기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'1:1 문의 작성'의 내용 입력에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H301" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I301" t="str">
         <v/>
@@ -10450,28 +10450,28 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>SCN-042</v>
+        <v>SCN-040</v>
       </c>
       <c r="B302" t="str">
-        <v>고객센터</v>
+        <v/>
       </c>
       <c r="C302" t="str">
-        <v>공지사항</v>
+        <v/>
       </c>
       <c r="D302" t="str">
-        <v>CS-04</v>
+        <v/>
       </c>
       <c r="E302" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F302" t="str">
-        <v>중요 공지 상단 고정</v>
+        <v>파일 첨부</v>
       </c>
       <c r="G302" t="str">
-        <v>'공지사항' 화면에서 중요 공지 상단 고정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'1:1 문의 작성'의 파일 첨부에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H302" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I302" t="str">
         <v/>
@@ -10482,7 +10482,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>SCN-042</v>
+        <v>SCN-040</v>
       </c>
       <c r="B303" t="str">
         <v/>
@@ -10497,13 +10497,13 @@
         <v/>
       </c>
       <c r="F303" t="str">
-        <v>공지 목록(제목·작성일·카테고리)</v>
+        <v>답변 받을 방법 선택</v>
       </c>
       <c r="G303" t="str">
-        <v>'공지사항'의 공지 목록(제목·작성일·카테고리)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'1:1 문의 작성' 화면에서 답변 받을 방법 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H303" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I303" t="str">
         <v/>
@@ -10514,7 +10514,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>SCN-042</v>
+        <v>SCN-040</v>
       </c>
       <c r="B304" t="str">
         <v/>
@@ -10529,10 +10529,10 @@
         <v/>
       </c>
       <c r="F304" t="str">
-        <v>상세 펼치기</v>
+        <v>예상 답변 시간 안내</v>
       </c>
       <c r="G304" t="str">
-        <v>'공지사항' 화면에서 상세 펼치기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'1:1 문의 작성' 화면에서 예상 답변 시간 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H304" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10546,28 +10546,28 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>SCN-042</v>
+        <v>SCN-041</v>
       </c>
       <c r="B305" t="str">
-        <v/>
+        <v>고객센터</v>
       </c>
       <c r="C305" t="str">
-        <v/>
+        <v>문의 내역</v>
       </c>
       <c r="D305" t="str">
-        <v/>
+        <v>CS-03</v>
       </c>
       <c r="E305" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F305" t="str">
-        <v>현지 이슈 알림 배너</v>
+        <v>문의 목록(제목·유형·작성일·상태 배지)</v>
       </c>
       <c r="G305" t="str">
-        <v>'공지사항'에서 현지 이슈 알림 배너를 눌러 본다.</v>
+        <v>'문의 내역'의 문의 목록(제목·유형·작성일·상태 배지)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H305" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I305" t="str">
         <v/>
@@ -10578,28 +10578,28 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>SCN-043</v>
+        <v>SCN-041</v>
       </c>
       <c r="B306" t="str">
-        <v>고객센터</v>
+        <v/>
       </c>
       <c r="C306" t="str">
-        <v>취소·환불 규정 안내</v>
+        <v/>
       </c>
       <c r="D306" t="str">
-        <v>CS-05</v>
+        <v/>
       </c>
       <c r="E306" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F306" t="str">
-        <v>상품 유형별 환불 규정 표(투어·입장권·패스)</v>
+        <v>답변 완료 여부 표시</v>
       </c>
       <c r="G306" t="str">
-        <v>'취소·환불 규정 안내'에서 상품 유형별 환불 규정 표(투어·입장권·패스)를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'문의 내역'의 답변 완료 여부 표시가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H306" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I306" t="str">
         <v/>
@@ -10610,7 +10610,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>SCN-043</v>
+        <v>SCN-041</v>
       </c>
       <c r="B307" t="str">
         <v/>
@@ -10625,10 +10625,10 @@
         <v/>
       </c>
       <c r="F307" t="str">
-        <v>출발일 기준 수수료율 단계</v>
+        <v>문의 상세 펼치기</v>
       </c>
       <c r="G307" t="str">
-        <v>'취소·환불 규정 안내' 화면에서 출발일 기준 수수료율 단계가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'문의 내역' 화면에서 문의 상세 펼치기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H307" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10642,7 +10642,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>SCN-043</v>
+        <v>SCN-041</v>
       </c>
       <c r="B308" t="str">
         <v/>
@@ -10657,13 +10657,13 @@
         <v/>
       </c>
       <c r="F308" t="str">
-        <v>무료 취소 기한 계산 예시</v>
+        <v>추가 질문 이어쓰기</v>
       </c>
       <c r="G308" t="str">
-        <v>'취소·환불 규정 안내'에서 무료 취소 기한 계산 예시를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'문의 내역' 화면에서 추가 질문 이어쓰기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H308" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I308" t="str">
         <v/>
@@ -10674,25 +10674,25 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>SCN-043</v>
+        <v>SCN-042</v>
       </c>
       <c r="B309" t="str">
-        <v/>
+        <v>고객센터</v>
       </c>
       <c r="C309" t="str">
-        <v/>
+        <v>공지사항</v>
       </c>
       <c r="D309" t="str">
-        <v/>
+        <v>CS-04</v>
       </c>
       <c r="E309" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F309" t="str">
-        <v>현지 시각 기준이라는 안내</v>
+        <v>중요 공지 상단 고정</v>
       </c>
       <c r="G309" t="str">
-        <v>'취소·환불 규정 안내' 화면에서 현지 시각 기준이라는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공지사항' 화면에서 중요 공지 상단 고정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H309" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10706,7 +10706,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>SCN-043</v>
+        <v>SCN-042</v>
       </c>
       <c r="B310" t="str">
         <v/>
@@ -10721,13 +10721,13 @@
         <v/>
       </c>
       <c r="F310" t="str">
-        <v>기상</v>
+        <v>공지 목록(제목·작성일·카테고리)</v>
       </c>
       <c r="G310" t="str">
-        <v>'취소·환불 규정 안내' 화면에서 기상이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공지사항'의 공지 목록(제목·작성일·카테고리)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H310" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I310" t="str">
         <v/>
@@ -10738,7 +10738,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>SCN-043</v>
+        <v>SCN-042</v>
       </c>
       <c r="B311" t="str">
         <v/>
@@ -10753,13 +10753,13 @@
         <v/>
       </c>
       <c r="F311" t="str">
-        <v>천재지변 취소 처리</v>
+        <v>상세 펼치기</v>
       </c>
       <c r="G311" t="str">
-        <v>'취소·환불 규정 안내'에서 천재지변 취소 처리를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'공지사항' 화면에서 상세 펼치기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H311" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I311" t="str">
         <v/>
@@ -10770,7 +10770,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>SCN-043</v>
+        <v>SCN-042</v>
       </c>
       <c r="B312" t="str">
         <v/>
@@ -10785,13 +10785,13 @@
         <v/>
       </c>
       <c r="F312" t="str">
-        <v>최소 인원 미달 자동 취소와 전액 환불</v>
+        <v>현지 이슈 알림 배너</v>
       </c>
       <c r="G312" t="str">
-        <v>'취소·환불 규정 안내'에서 최소 인원 미달 자동 취소와 전액 환불을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'공지사항'에서 현지 이슈 알림 배너를 눌러 본다.</v>
       </c>
       <c r="H312" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I312" t="str">
         <v/>
@@ -10805,25 +10805,25 @@
         <v>SCN-043</v>
       </c>
       <c r="B313" t="str">
-        <v/>
+        <v>고객센터</v>
       </c>
       <c r="C313" t="str">
-        <v/>
+        <v>취소·환불 규정 안내</v>
       </c>
       <c r="D313" t="str">
-        <v/>
+        <v>CS-05</v>
       </c>
       <c r="E313" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F313" t="str">
-        <v>노쇼와 부분 사용 처리 기준</v>
+        <v>상품 유형별 환불 규정 표(투어·입장권·패스)</v>
       </c>
       <c r="G313" t="str">
-        <v>'취소·환불 규정 안내' 화면에서 노쇼와 부분 사용 처리 기준이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'취소·환불 규정 안내'에서 상품 유형별 환불 규정 표(투어·입장권·패스)를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H313" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I313" t="str">
         <v/>
@@ -10849,13 +10849,13 @@
         <v/>
       </c>
       <c r="F314" t="str">
-        <v>환불 소요 기간과 결제 수단별 차이</v>
+        <v>출발일 기준 수수료율 단계</v>
       </c>
       <c r="G314" t="str">
-        <v>'취소·환불 규정 안내'에서 환불 소요 기간과 결제 수단별 차이를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'취소·환불 규정 안내' 화면에서 출발일 기준 수수료율 단계가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H314" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I314" t="str">
         <v/>
@@ -10881,10 +10881,10 @@
         <v/>
       </c>
       <c r="F315" t="str">
-        <v>자주 묻는 취소 질문 5개</v>
+        <v>무료 취소 기한 계산 예시</v>
       </c>
       <c r="G315" t="str">
-        <v>'취소·환불 규정 안내'에서 자주 묻는 취소 질문 5개를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'취소·환불 규정 안내'에서 무료 취소 기한 계산 예시를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H315" t="str">
         <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
@@ -10913,24 +10913,248 @@
         <v/>
       </c>
       <c r="F316" t="str">
+        <v>현지 시각 기준이라는 안내</v>
+      </c>
+      <c r="G316" t="str">
+        <v>'취소·환불 규정 안내' 화면에서 현지 시각 기준이라는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+      </c>
+      <c r="H316" t="str">
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+      </c>
+      <c r="I316" t="str">
+        <v/>
+      </c>
+      <c r="J316" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>SCN-043</v>
+      </c>
+      <c r="B317" t="str">
+        <v/>
+      </c>
+      <c r="C317" t="str">
+        <v/>
+      </c>
+      <c r="D317" t="str">
+        <v/>
+      </c>
+      <c r="E317" t="str">
+        <v/>
+      </c>
+      <c r="F317" t="str">
+        <v>기상</v>
+      </c>
+      <c r="G317" t="str">
+        <v>'취소·환불 규정 안내' 화면에서 기상이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+      </c>
+      <c r="H317" t="str">
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+      </c>
+      <c r="I317" t="str">
+        <v/>
+      </c>
+      <c r="J317" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>SCN-043</v>
+      </c>
+      <c r="B318" t="str">
+        <v/>
+      </c>
+      <c r="C318" t="str">
+        <v/>
+      </c>
+      <c r="D318" t="str">
+        <v/>
+      </c>
+      <c r="E318" t="str">
+        <v/>
+      </c>
+      <c r="F318" t="str">
+        <v>천재지변 취소 처리</v>
+      </c>
+      <c r="G318" t="str">
+        <v>'취소·환불 규정 안내'에서 천재지변 취소 처리를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+      </c>
+      <c r="H318" t="str">
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+      </c>
+      <c r="I318" t="str">
+        <v/>
+      </c>
+      <c r="J318" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
+        <v>SCN-043</v>
+      </c>
+      <c r="B319" t="str">
+        <v/>
+      </c>
+      <c r="C319" t="str">
+        <v/>
+      </c>
+      <c r="D319" t="str">
+        <v/>
+      </c>
+      <c r="E319" t="str">
+        <v/>
+      </c>
+      <c r="F319" t="str">
+        <v>최소 인원 미달 자동 취소와 전액 환불</v>
+      </c>
+      <c r="G319" t="str">
+        <v>'취소·환불 규정 안내'에서 최소 인원 미달 자동 취소와 전액 환불을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+      </c>
+      <c r="H319" t="str">
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+      </c>
+      <c r="I319" t="str">
+        <v/>
+      </c>
+      <c r="J319" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>SCN-043</v>
+      </c>
+      <c r="B320" t="str">
+        <v/>
+      </c>
+      <c r="C320" t="str">
+        <v/>
+      </c>
+      <c r="D320" t="str">
+        <v/>
+      </c>
+      <c r="E320" t="str">
+        <v/>
+      </c>
+      <c r="F320" t="str">
+        <v>노쇼와 부분 사용 처리 기준</v>
+      </c>
+      <c r="G320" t="str">
+        <v>'취소·환불 규정 안내' 화면에서 노쇼와 부분 사용 처리 기준이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+      </c>
+      <c r="H320" t="str">
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+      </c>
+      <c r="I320" t="str">
+        <v/>
+      </c>
+      <c r="J320" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>SCN-043</v>
+      </c>
+      <c r="B321" t="str">
+        <v/>
+      </c>
+      <c r="C321" t="str">
+        <v/>
+      </c>
+      <c r="D321" t="str">
+        <v/>
+      </c>
+      <c r="E321" t="str">
+        <v/>
+      </c>
+      <c r="F321" t="str">
+        <v>환불 소요 기간과 결제 수단별 차이</v>
+      </c>
+      <c r="G321" t="str">
+        <v>'취소·환불 규정 안내'에서 환불 소요 기간과 결제 수단별 차이를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+      </c>
+      <c r="H321" t="str">
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+      </c>
+      <c r="I321" t="str">
+        <v/>
+      </c>
+      <c r="J321" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>SCN-043</v>
+      </c>
+      <c r="B322" t="str">
+        <v/>
+      </c>
+      <c r="C322" t="str">
+        <v/>
+      </c>
+      <c r="D322" t="str">
+        <v/>
+      </c>
+      <c r="E322" t="str">
+        <v/>
+      </c>
+      <c r="F322" t="str">
+        <v>자주 묻는 취소 질문 5개</v>
+      </c>
+      <c r="G322" t="str">
+        <v>'취소·환불 규정 안내'에서 자주 묻는 취소 질문 5개를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+      </c>
+      <c r="H322" t="str">
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+      </c>
+      <c r="I322" t="str">
+        <v/>
+      </c>
+      <c r="J322" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>SCN-043</v>
+      </c>
+      <c r="B323" t="str">
+        <v/>
+      </c>
+      <c r="C323" t="str">
+        <v/>
+      </c>
+      <c r="D323" t="str">
+        <v/>
+      </c>
+      <c r="E323" t="str">
+        <v/>
+      </c>
+      <c r="F323" t="str">
         <v>내 예약의 규정 바로 확인</v>
       </c>
-      <c r="G316" t="str">
+      <c r="G323" t="str">
         <v>'취소·환불 규정 안내' 화면에서 내 예약의 규정 바로 확인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
-      <c r="H316" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
-      </c>
-      <c r="I316" t="str">
-        <v/>
-      </c>
-      <c r="J316" t="str">
+      <c r="H323" t="str">
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+      </c>
+      <c r="I323" t="str">
+        <v/>
+      </c>
+      <c r="J323" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J316"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J323"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/판매용_템플릿/_판매팩/여행_디럭스/08_검수시나리오.xlsx
+++ b/판매용_템플릿/_판매팩/여행_디럭스/08_검수시나리오.xlsx
@@ -727,7 +727,7 @@
         <v>확인 항목 수</v>
       </c>
       <c r="B5">
-        <v>322</v>
+        <v>328</v>
       </c>
     </row>
     <row r="6">
@@ -735,7 +735,7 @@
         <v xml:space="preserve">  └ 공통(사이트 전체)</v>
       </c>
       <c r="B6">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
@@ -803,7 +803,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J323"/>
+  <dimension ref="A1:J329"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -1426,28 +1426,28 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B20" t="str">
-        <v>홈</v>
+        <v/>
       </c>
       <c r="C20" t="str">
-        <v>홈</v>
+        <v/>
       </c>
       <c r="D20" t="str">
-        <v>HO-01</v>
+        <v/>
       </c>
       <c r="E20" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F20" t="str">
-        <v>여행지 검색창이 얹힌 히어로 배너</v>
+        <v>끊어진 링크 — 갈 곳이 실제로 있는지</v>
       </c>
       <c r="G20" t="str">
-        <v>'홈'의 여행지 검색창이 얹힌 히어로 배너에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>스펙팩 7-9-2 의 검사 글을 사이트 «뿌리»에서 한 번 돌린다. ⚠ pages/ 만 주면 한 층 위의 화면 목록을 못 봐서 멀쩡한 화면이 외톨이로 잘못 잡힌다.</v>
       </c>
       <c r="H20" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>끊어진 링크 0건. `href` 가 가리키는 .html 이 모두 실제로 있다.</v>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -1458,7 +1458,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B21" t="str">
         <v/>
@@ -1473,13 +1473,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>인기 여행지 바로가기 6곳</v>
+        <v>없는 그림 · 빈 파일</v>
       </c>
       <c r="G21" t="str">
-        <v>'홈'에서 인기 여행지 바로가기 6곳을 눌러 본다.</v>
+        <v>같은 검사 글의 결과에서 «없는 그림»과 «빈 파일» 줄을 본다.</v>
       </c>
       <c r="H21" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>둘 다 0건. `src` 가 가리키는 파일이 모두 있고, 0바이트로 남은 화면이 없다.</v>
       </c>
       <c r="I21" t="str">
         <v/>
@@ -1490,7 +1490,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B22" t="str">
         <v/>
@@ -1505,13 +1505,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>이번 주 인기 상품 8개 카드</v>
+        <v>외톨이 화면 — 아무 데서도 안 이어지는 화면</v>
       </c>
       <c r="G22" t="str">
-        <v>'홈' 화면을 열고 이번 주 인기 상품 8개 카드가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>같은 검사 글의 «외톨이» 줄을 본다. 나온 화면은 어디서 이어져야 맞는지 정하고 그 링크를 놓는다.</v>
       </c>
       <c r="H22" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>외톨이 0건. 만들어 놓고 갈 길이 없는 화면이 없다.</v>
       </c>
       <c r="I22" t="str">
         <v/>
@@ -1522,7 +1522,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B23" t="str">
         <v/>
@@ -1537,13 +1537,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>특가</v>
+        <v>화면 수가 약속한 수와 같은지</v>
       </c>
       <c r="G23" t="str">
-        <v>'홈' 화면에서 특가가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>만든 .html 수를 세어 스펙팩 4장의 화면 수와 견준다.</v>
       </c>
       <c r="H23" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>두 수가 같다. 목록에는 있는데 안 만든 화면, 만들었는데 목록에 없는 화면 둘 다 0.</v>
       </c>
       <c r="I23" t="str">
         <v/>
@@ -1554,7 +1554,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B24" t="str">
         <v/>
@@ -1569,13 +1569,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>마감임박 상품 캐러셀</v>
+        <v>글자 대비 — 색을 고른 뒤 반드시 잰다</v>
       </c>
       <c r="G24" t="str">
-        <v>'홈'에서 마감임박 상품 캐러셀의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>스펙팩 7-9-2 가 가리키는 대로 브라우저에서 잰다. ⚠ 반투명 배경(10% 배지 등)은 «쌓아서» 진짜 바탕색을 구한 뒤 재야 한다 — 알파를 빼고 재면 멀쩡한 배지가 미달로 잡힌다.</v>
       </c>
       <c r="H24" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>본문 4.5 이상, 24px 이상이거나 굵은 18.66px 이상은 3.0 이상. 미달 0건.</v>
       </c>
       <c r="I24" t="str">
         <v/>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B25" t="str">
         <v/>
@@ -1601,13 +1601,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>패스 상품 안내 배너</v>
+        <v>굳은 날짜 — 견본 날짜가 오늘에서 거꾸로 잡혔는지</v>
       </c>
       <c r="G25" t="str">
-        <v>'홈'에서 패스 상품 안내 배너를 눌러 본다.</v>
+        <v>목록·상세의 날짜와 요일을 오늘 기준으로 다시 센다. 요일은 눈으로 세지 말고 달력과 맞춘다.</v>
       </c>
       <c r="H25" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>지난 날짜가 「예정」으로 보이지 않는다. 요일이 그 날짜의 실제 요일과 같다.</v>
       </c>
       <c r="I25" t="str">
         <v/>
@@ -1621,25 +1621,25 @@
         <v>SCN-001</v>
       </c>
       <c r="B26" t="str">
-        <v/>
+        <v>홈</v>
       </c>
       <c r="C26" t="str">
-        <v/>
+        <v>홈</v>
       </c>
       <c r="D26" t="str">
-        <v/>
+        <v>HO-01</v>
       </c>
       <c r="E26" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F26" t="str">
-        <v>테마별 추천 탭(투어/입장권/교통)</v>
+        <v>여행지 검색창이 얹힌 히어로 배너</v>
       </c>
       <c r="G26" t="str">
-        <v>'홈'에서 테마별 추천 탭(투어/입장권/교통)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'홈'의 여행지 검색창이 얹힌 히어로 배너에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H26" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I26" t="str">
         <v/>
@@ -1665,13 +1665,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>실제 후기 슬라이드 5개</v>
+        <v>인기 여행지 바로가기 6곳</v>
       </c>
       <c r="G27" t="str">
-        <v>'홈' 화면을 열고 실제 후기 슬라이드 5개가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'홈'에서 인기 여행지 바로가기 6곳을 눌러 본다.</v>
       </c>
       <c r="H27" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I27" t="str">
         <v/>
@@ -1697,13 +1697,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>현지 라운지</v>
+        <v>이번 주 인기 상품 8개 카드</v>
       </c>
       <c r="G28" t="str">
-        <v>'홈' 화면에서 현지 라운지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'홈' 화면을 열고 이번 주 인기 상품 8개 카드가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H28" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I28" t="str">
         <v/>
@@ -1729,10 +1729,10 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>고객센터 안내</v>
+        <v>특가</v>
       </c>
       <c r="G29" t="str">
-        <v>'홈' 화면에서 고객센터 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'홈' 화면에서 특가가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H29" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -1761,13 +1761,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>여행 팁 콘텐츠 4개</v>
+        <v>마감임박 상품 캐러셀</v>
       </c>
       <c r="G30" t="str">
-        <v>'홈' 화면을 열고 여행 팁 콘텐츠 4개가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'홈'에서 마감임박 상품 캐러셀의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H30" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I30" t="str">
         <v/>
@@ -1793,13 +1793,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>하단 앱</v>
+        <v>패스 상품 안내 배너</v>
       </c>
       <c r="G31" t="str">
-        <v>'홈' 화면에서 하단 앱이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'홈'에서 패스 상품 안내 배너를 눌러 본다.</v>
       </c>
       <c r="H31" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I31" t="str">
         <v/>
@@ -1825,13 +1825,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>카톡 채널 안내</v>
+        <v>테마별 추천 탭(투어/입장권/교통)</v>
       </c>
       <c r="G32" t="str">
-        <v>'홈' 화면에서 카톡 채널 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'홈'에서 테마별 추천 탭(투어/입장권/교통)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H32" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I32" t="str">
         <v/>
@@ -1842,28 +1842,28 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B33" t="str">
-        <v>홈</v>
+        <v/>
       </c>
       <c r="C33" t="str">
-        <v>여행지 홈</v>
+        <v/>
       </c>
       <c r="D33" t="str">
-        <v>HO-02</v>
+        <v/>
       </c>
       <c r="E33" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F33" t="str">
-        <v>여행지 대표 사진과 한 줄 소개</v>
+        <v>실제 후기 슬라이드 5개</v>
       </c>
       <c r="G33" t="str">
-        <v>'여행지 홈' 화면에서 여행지 대표 사진과 한 줄 소개가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'홈' 화면을 열고 실제 후기 슬라이드 5개가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H33" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I33" t="str">
         <v/>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B34" t="str">
         <v/>
@@ -1889,13 +1889,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>이 도시 인기 상품 8개</v>
+        <v>현지 라운지</v>
       </c>
       <c r="G34" t="str">
-        <v>'여행지 홈' 화면을 열고 이 도시 인기 상품 8개가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'홈' 화면에서 현지 라운지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H34" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I34" t="str">
         <v/>
@@ -1906,7 +1906,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B35" t="str">
         <v/>
@@ -1921,13 +1921,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>카테고리 필터(투어/입장권/교통/패스)</v>
+        <v>고객센터 안내</v>
       </c>
       <c r="G35" t="str">
-        <v>'여행지 홈'에서 카테고리 필터(투어/입장권/교통/패스)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'홈' 화면에서 고객센터 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H35" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I35" t="str">
         <v/>
@@ -1938,7 +1938,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B36" t="str">
         <v/>
@@ -1953,13 +1953,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>이 도시 전용 패스 안내</v>
+        <v>여행 팁 콘텐츠 4개</v>
       </c>
       <c r="G36" t="str">
-        <v>'여행지 홈' 화면에서 이 도시 전용 패스 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'홈' 화면을 열고 여행 팁 콘텐츠 4개가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H36" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I36" t="str">
         <v/>
@@ -1970,7 +1970,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B37" t="str">
         <v/>
@@ -1985,10 +1985,10 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>추천 일정 3코스</v>
+        <v>하단 앱</v>
       </c>
       <c r="G37" t="str">
-        <v>'여행지 홈' 화면에서 추천 일정 3코스가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'홈' 화면에서 하단 앱이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H37" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2002,7 +2002,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B38" t="str">
         <v/>
@@ -2017,13 +2017,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>현지 쿠폰 제휴처 목록</v>
+        <v>카톡 채널 안내</v>
       </c>
       <c r="G38" t="str">
-        <v>'여행지 홈'의 현지 쿠폰 제휴처 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'홈' 화면에서 카톡 채널 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H38" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I38" t="str">
         <v/>
@@ -2037,22 +2037,22 @@
         <v>SCN-002</v>
       </c>
       <c r="B39" t="str">
-        <v/>
+        <v>홈</v>
       </c>
       <c r="C39" t="str">
-        <v/>
+        <v>여행지 홈</v>
       </c>
       <c r="D39" t="str">
-        <v/>
+        <v>HO-02</v>
       </c>
       <c r="E39" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F39" t="str">
-        <v>날씨</v>
+        <v>여행지 대표 사진과 한 줄 소개</v>
       </c>
       <c r="G39" t="str">
-        <v>'여행지 홈' 화면에서 날씨가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'여행지 홈' 화면에서 여행지 대표 사진과 한 줄 소개가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H39" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2081,13 +2081,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>시차</v>
+        <v>이 도시 인기 상품 8개</v>
       </c>
       <c r="G40" t="str">
-        <v>'여행지 홈' 화면에서 시차가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'여행지 홈' 화면을 열고 이 도시 인기 상품 8개가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H40" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I40" t="str">
         <v/>
@@ -2113,13 +2113,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>팁 정보 카드</v>
+        <v>카테고리 필터(투어/입장권/교통/패스)</v>
       </c>
       <c r="G41" t="str">
-        <v>'여행지 홈'의 팁 정보 카드를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'여행지 홈'에서 카테고리 필터(투어/입장권/교통/패스)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H41" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I41" t="str">
         <v/>
@@ -2145,10 +2145,10 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>이 도시 후기 모음</v>
+        <v>이 도시 전용 패스 안내</v>
       </c>
       <c r="G42" t="str">
-        <v>'여행지 홈' 화면에서 이 도시 후기 모음이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'여행지 홈' 화면에서 이 도시 전용 패스 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H42" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2162,28 +2162,28 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B43" t="str">
-        <v>홈</v>
+        <v/>
       </c>
       <c r="C43" t="str">
-        <v>검색 결과</v>
+        <v/>
       </c>
       <c r="D43" t="str">
-        <v>HO-03</v>
+        <v/>
       </c>
       <c r="E43" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F43" t="str">
-        <v>검색어와 결과 수 표시</v>
+        <v>추천 일정 3코스</v>
       </c>
       <c r="G43" t="str">
-        <v>'검색 결과'에서 검색어와 결과 수 표시의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'여행지 홈' 화면에서 추천 일정 3코스가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H43" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I43" t="str">
         <v/>
@@ -2194,7 +2194,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B44" t="str">
         <v/>
@@ -2209,13 +2209,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>필터(여행지·카테고리·가격대·평점·소요시간)</v>
+        <v>현지 쿠폰 제휴처 목록</v>
       </c>
       <c r="G44" t="str">
-        <v>'검색 결과'에서 필터(여행지·카테고리·가격대·평점·소요시간)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'여행지 홈'의 현지 쿠폰 제휴처 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H44" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I44" t="str">
         <v/>
@@ -2226,7 +2226,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B45" t="str">
         <v/>
@@ -2241,13 +2241,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>정렬(인기순/낮은가격순/평점순)</v>
+        <v>날씨</v>
       </c>
       <c r="G45" t="str">
-        <v>'검색 결과'에서 정렬(인기순/낮은가격순/평점순)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'여행지 홈' 화면에서 날씨가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H45" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I45" t="str">
         <v/>
@@ -2258,7 +2258,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B46" t="str">
         <v/>
@@ -2273,13 +2273,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>상품 카드 목록</v>
+        <v>시차</v>
       </c>
       <c r="G46" t="str">
-        <v>'검색 결과'의 상품 카드 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'여행지 홈' 화면에서 시차가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H46" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I46" t="str">
         <v/>
@@ -2290,7 +2290,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B47" t="str">
         <v/>
@@ -2305,13 +2305,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>지도 보기 전환</v>
+        <v>팁 정보 카드</v>
       </c>
       <c r="G47" t="str">
-        <v>'검색 결과' 화면에서 지도 보기 전환이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'여행지 홈'의 팁 정보 카드를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H47" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I47" t="str">
         <v/>
@@ -2322,7 +2322,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B48" t="str">
         <v/>
@@ -2337,10 +2337,10 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>무한 스크롤</v>
+        <v>이 도시 후기 모음</v>
       </c>
       <c r="G48" t="str">
-        <v>'검색 결과' 화면에서 무한 스크롤이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'여행지 홈' 화면에서 이 도시 후기 모음이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H48" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2354,28 +2354,28 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>SCN-004</v>
+        <v>SCN-003</v>
       </c>
       <c r="B49" t="str">
         <v>홈</v>
       </c>
       <c r="C49" t="str">
-        <v>검색 결과 없음</v>
+        <v>검색 결과</v>
       </c>
       <c r="D49" t="str">
-        <v>HO-04</v>
+        <v>HO-03</v>
       </c>
       <c r="E49" t="str">
-        <v>예외·상태</v>
+        <v>기본</v>
       </c>
       <c r="F49" t="str">
-        <v>검색어를 포함한 안내 문구</v>
+        <v>검색어와 결과 수 표시</v>
       </c>
       <c r="G49" t="str">
-        <v>일부러 그 상황을 만들어 '검색 결과 없음' 화면이 나오게 한 뒤, 검색어를 포함한 안내 문구가 보이는지 확인한다.</v>
+        <v>'검색 결과'에서 검색어와 결과 수 표시의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H49" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I49" t="str">
         <v/>
@@ -2386,7 +2386,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>SCN-004</v>
+        <v>SCN-003</v>
       </c>
       <c r="B50" t="str">
         <v/>
@@ -2401,13 +2401,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>필터 초기화 버튼</v>
+        <v>필터(여행지·카테고리·가격대·평점·소요시간)</v>
       </c>
       <c r="G50" t="str">
-        <v>일부러 그 상황을 만들어 '검색 결과 없음' 화면이 나오게 한 뒤, 필터 초기화 버튼이 보이는지 확인한다.</v>
+        <v>'검색 결과'에서 필터(여행지·카테고리·가격대·평점·소요시간)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H50" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -2418,7 +2418,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>SCN-004</v>
+        <v>SCN-003</v>
       </c>
       <c r="B51" t="str">
         <v/>
@@ -2433,13 +2433,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>추천 상품 4개</v>
+        <v>정렬(인기순/낮은가격순/평점순)</v>
       </c>
       <c r="G51" t="str">
-        <v>일부러 그 상황을 만들어 '검색 결과 없음' 화면이 나오게 한 뒤, 추천 상품 4개가 보이는지 확인한다.</v>
+        <v>'검색 결과'에서 정렬(인기순/낮은가격순/평점순)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H51" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -2450,7 +2450,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>SCN-004</v>
+        <v>SCN-003</v>
       </c>
       <c r="B52" t="str">
         <v/>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>인기 검색어 칩</v>
+        <v>상품 카드 목록</v>
       </c>
       <c r="G52" t="str">
-        <v>일부러 그 상황을 만들어 '검색 결과 없음' 화면이 나오게 한 뒤, 인기 검색어 칩이 보이는지 확인한다.</v>
+        <v>'검색 결과'의 상품 카드 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H52" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -2482,28 +2482,28 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>SCN-005</v>
+        <v>SCN-003</v>
       </c>
       <c r="B53" t="str">
-        <v>홈</v>
+        <v/>
       </c>
       <c r="C53" t="str">
-        <v>테마 기획전</v>
+        <v/>
       </c>
       <c r="D53" t="str">
-        <v>HO-05</v>
+        <v/>
       </c>
       <c r="E53" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F53" t="str">
-        <v>기획전 대표 배너(테마명·기간·혜택 문구)</v>
+        <v>지도 보기 전환</v>
       </c>
       <c r="G53" t="str">
-        <v>'테마 기획전'에서 기획전 대표 배너(테마명·기간·혜택 문구)를 눌러 본다.</v>
+        <v>'검색 결과' 화면에서 지도 보기 전환이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H53" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I53" t="str">
         <v/>
@@ -2514,7 +2514,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>SCN-005</v>
+        <v>SCN-003</v>
       </c>
       <c r="B54" t="str">
         <v/>
@@ -2529,13 +2529,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>테마 탭(가족여행·미식·야경·액티비티·근교 당일)</v>
+        <v>무한 스크롤</v>
       </c>
       <c r="G54" t="str">
-        <v>'테마 기획전'에서 테마 탭(가족여행·미식·야경·액티비티·근교 당일)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'검색 결과' 화면에서 무한 스크롤이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H54" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I54" t="str">
         <v/>
@@ -2546,28 +2546,28 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B55" t="str">
-        <v/>
+        <v>홈</v>
       </c>
       <c r="C55" t="str">
-        <v/>
+        <v>검색 결과 없음</v>
       </c>
       <c r="D55" t="str">
-        <v/>
+        <v>HO-04</v>
       </c>
       <c r="E55" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F55" t="str">
-        <v>기획전 소개 문구와 큐레이터 코멘트</v>
+        <v>검색어를 포함한 안내 문구</v>
       </c>
       <c r="G55" t="str">
-        <v>'테마 기획전' 화면에서 기획전 소개 문구와 큐레이터 코멘트가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '검색 결과 없음' 화면이 나오게 한 뒤, 검색어를 포함한 안내 문구가 보이는지 확인한다.</v>
       </c>
       <c r="H55" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I55" t="str">
         <v/>
@@ -2578,7 +2578,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B56" t="str">
         <v/>
@@ -2593,13 +2593,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>남은 기간 카운트다운</v>
+        <v>필터 초기화 버튼</v>
       </c>
       <c r="G56" t="str">
-        <v>'테마 기획전'의 남은 기간 카운트다운이 실제 데이터와 같은지 대조한다.</v>
+        <v>일부러 그 상황을 만들어 '검색 결과 없음' 화면이 나오게 한 뒤, 필터 초기화 버튼이 보이는지 확인한다.</v>
       </c>
       <c r="H56" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I56" t="str">
         <v/>
@@ -2610,7 +2610,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B57" t="str">
         <v/>
@@ -2625,13 +2625,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>기획전 전용 쿠폰 다운로드</v>
+        <v>추천 상품 4개</v>
       </c>
       <c r="G57" t="str">
-        <v>'테마 기획전' 화면에서 기획전 전용 쿠폰 다운로드가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '검색 결과 없음' 화면이 나오게 한 뒤, 추천 상품 4개가 보이는지 확인한다.</v>
       </c>
       <c r="H57" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I57" t="str">
         <v/>
@@ -2642,7 +2642,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B58" t="str">
         <v/>
@@ -2657,13 +2657,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>대상 상품 카드 그리드와 기획전가 표시</v>
+        <v>인기 검색어 칩</v>
       </c>
       <c r="G58" t="str">
-        <v>'테마 기획전'의 대상 상품 카드 그리드와 기획전가 표시를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '검색 결과 없음' 화면이 나오게 한 뒤, 인기 검색어 칩이 보이는지 확인한다.</v>
       </c>
       <c r="H58" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I58" t="str">
         <v/>
@@ -2677,25 +2677,25 @@
         <v>SCN-005</v>
       </c>
       <c r="B59" t="str">
-        <v/>
+        <v>홈</v>
       </c>
       <c r="C59" t="str">
-        <v/>
+        <v>테마 기획전</v>
       </c>
       <c r="D59" t="str">
-        <v/>
+        <v>HO-05</v>
       </c>
       <c r="E59" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F59" t="str">
-        <v>여행지별 묶음 보기</v>
+        <v>기획전 대표 배너(테마명·기간·혜택 문구)</v>
       </c>
       <c r="G59" t="str">
-        <v>'테마 기획전' 화면에서 여행지별 묶음 보기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'테마 기획전'에서 기획전 대표 배너(테마명·기간·혜택 문구)를 눌러 본다.</v>
       </c>
       <c r="H59" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I59" t="str">
         <v/>
@@ -2721,10 +2721,10 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>정렬(추천순·낮은 가격순·할인율순)</v>
+        <v>테마 탭(가족여행·미식·야경·액티비티·근교 당일)</v>
       </c>
       <c r="G60" t="str">
-        <v>'테마 기획전'에서 정렬(추천순·낮은 가격순·할인율순)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'테마 기획전'에서 테마 탭(가족여행·미식·야경·액티비티·근교 당일)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H60" t="str">
         <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
@@ -2753,13 +2753,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>함께 보면 좋은 기획전 3개</v>
+        <v>기획전 소개 문구와 큐레이터 코멘트</v>
       </c>
       <c r="G61" t="str">
-        <v>'테마 기획전' 화면을 열고 함께 보면 좋은 기획전 3개가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'테마 기획전' 화면에서 기획전 소개 문구와 큐레이터 코멘트가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H61" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I61" t="str">
         <v/>
@@ -2785,13 +2785,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>종료된 기획전 안내와 다음 기획전 예고</v>
+        <v>남은 기간 카운트다운</v>
       </c>
       <c r="G62" t="str">
-        <v>'테마 기획전' 화면에서 종료된 기획전 안내와 다음 기획전 예고가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'테마 기획전'의 남은 기간 카운트다운이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H62" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I62" t="str">
         <v/>
@@ -2802,28 +2802,28 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B63" t="str">
-        <v>상품</v>
+        <v/>
       </c>
       <c r="C63" t="str">
-        <v>상품 목록</v>
+        <v/>
       </c>
       <c r="D63" t="str">
-        <v>PR-01</v>
+        <v/>
       </c>
       <c r="E63" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F63" t="str">
-        <v>카테고리 탭</v>
+        <v>기획전 전용 쿠폰 다운로드</v>
       </c>
       <c r="G63" t="str">
-        <v>'상품 목록'에서 카테고리 탭의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'테마 기획전' 화면에서 기획전 전용 쿠폰 다운로드가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H63" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I63" t="str">
         <v/>
@@ -2834,7 +2834,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B64" t="str">
         <v/>
@@ -2849,13 +2849,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>필터(가격·평점·소요시간·언어·즉시확정)</v>
+        <v>대상 상품 카드 그리드와 기획전가 표시</v>
       </c>
       <c r="G64" t="str">
-        <v>'상품 목록'에서 필터(가격·평점·소요시간·언어·즉시확정)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'테마 기획전'의 대상 상품 카드 그리드와 기획전가 표시를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H64" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I64" t="str">
         <v/>
@@ -2866,7 +2866,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B65" t="str">
         <v/>
@@ -2881,13 +2881,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>정렬</v>
+        <v>여행지별 묶음 보기</v>
       </c>
       <c r="G65" t="str">
-        <v>'상품 목록'에서 정렬의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'테마 기획전' 화면에서 여행지별 묶음 보기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H65" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I65" t="str">
         <v/>
@@ -2898,7 +2898,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B66" t="str">
         <v/>
@@ -2913,13 +2913,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>상품 카드 그리드</v>
+        <v>정렬(추천순·낮은 가격순·할인율순)</v>
       </c>
       <c r="G66" t="str">
-        <v>'상품 목록'의 상품 카드 그리드를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'테마 기획전'에서 정렬(추천순·낮은 가격순·할인율순)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H66" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I66" t="str">
         <v/>
@@ -2930,7 +2930,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B67" t="str">
         <v/>
@@ -2945,13 +2945,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>마감임박 배지</v>
+        <v>함께 보면 좋은 기획전 3개</v>
       </c>
       <c r="G67" t="str">
-        <v>'상품 목록' 화면에서 마감임박 배지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'테마 기획전' 화면을 열고 함께 보면 좋은 기획전 3개가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H67" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I67" t="str">
         <v/>
@@ -2962,7 +2962,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B68" t="str">
         <v/>
@@ -2977,10 +2977,10 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>찜하기</v>
+        <v>종료된 기획전 안내와 다음 기획전 예고</v>
       </c>
       <c r="G68" t="str">
-        <v>'상품 목록' 화면에서 찜하기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'테마 기획전' 화면에서 종료된 기획전 안내와 다음 기획전 예고가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H68" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2997,22 +2997,22 @@
         <v>SCN-006</v>
       </c>
       <c r="B69" t="str">
-        <v/>
+        <v>상품</v>
       </c>
       <c r="C69" t="str">
-        <v/>
+        <v>상품 목록</v>
       </c>
       <c r="D69" t="str">
-        <v/>
+        <v>PR-01</v>
       </c>
       <c r="E69" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F69" t="str">
-        <v>페이지네이션</v>
+        <v>카테고리 탭</v>
       </c>
       <c r="G69" t="str">
-        <v>'상품 목록'에서 페이지네이션의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'상품 목록'에서 카테고리 탭의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H69" t="str">
         <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
@@ -3026,28 +3026,28 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B70" t="str">
-        <v>상품</v>
+        <v/>
       </c>
       <c r="C70" t="str">
-        <v>상품 상세</v>
+        <v/>
       </c>
       <c r="D70" t="str">
-        <v>PR-02</v>
+        <v/>
       </c>
       <c r="E70" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F70" t="str">
-        <v>사진 갤러리</v>
+        <v>필터(가격·평점·소요시간·언어·즉시확정)</v>
       </c>
       <c r="G70" t="str">
-        <v>'상품 상세'의 사진 갤러리를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'상품 목록'에서 필터(가격·평점·소요시간·언어·즉시확정)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H70" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I70" t="str">
         <v/>
@@ -3058,7 +3058,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B71" t="str">
         <v/>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>상품명과 별점</v>
+        <v>정렬</v>
       </c>
       <c r="G71" t="str">
-        <v>'상품 상세' 화면에서 상품명과 별점이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 목록'에서 정렬의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H71" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I71" t="str">
         <v/>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B72" t="str">
         <v/>
@@ -3105,13 +3105,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>후기 수</v>
+        <v>상품 카드 그리드</v>
       </c>
       <c r="G72" t="str">
-        <v>'상품 상세' 화면에서 후기 수가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 목록'의 상품 카드 그리드를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H72" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I72" t="str">
         <v/>
@@ -3122,7 +3122,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B73" t="str">
         <v/>
@@ -3137,13 +3137,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>핵심 정보 배지(소요시간·언어·즉시확정·미팅장소)</v>
+        <v>마감임박 배지</v>
       </c>
       <c r="G73" t="str">
-        <v>'상품 상세'의 핵심 정보 배지(소요시간·언어·즉시확정·미팅장소)가 실제 데이터와 같은지 대조한다.</v>
+        <v>'상품 목록' 화면에서 마감임박 배지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H73" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I73" t="str">
         <v/>
@@ -3154,7 +3154,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B74" t="str">
         <v/>
@@ -3169,13 +3169,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>가격과 할인율</v>
+        <v>찜하기</v>
       </c>
       <c r="G74" t="str">
-        <v>'상품 상세'의 가격과 할인율이 실제 데이터와 같은지 대조한다.</v>
+        <v>'상품 목록' 화면에서 찜하기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H74" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I74" t="str">
         <v/>
@@ -3186,7 +3186,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B75" t="str">
         <v/>
@@ -3201,13 +3201,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>상품 소개 본문</v>
+        <v>페이지네이션</v>
       </c>
       <c r="G75" t="str">
-        <v>'상품 상세' 화면에서 상품 소개 본문이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 목록'에서 페이지네이션의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H75" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I75" t="str">
         <v/>
@@ -3221,25 +3221,25 @@
         <v>SCN-007</v>
       </c>
       <c r="B76" t="str">
-        <v/>
+        <v>상품</v>
       </c>
       <c r="C76" t="str">
-        <v/>
+        <v>상품 상세</v>
       </c>
       <c r="D76" t="str">
-        <v/>
+        <v>PR-02</v>
       </c>
       <c r="E76" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F76" t="str">
-        <v>코스 일정 타임라인</v>
+        <v>사진 갤러리</v>
       </c>
       <c r="G76" t="str">
-        <v>'상품 상세' 화면에서 코스 일정 타임라인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 상세'의 사진 갤러리를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H76" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I76" t="str">
         <v/>
@@ -3265,10 +3265,10 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>포함/불포함 사항</v>
+        <v>상품명과 별점</v>
       </c>
       <c r="G77" t="str">
-        <v>'상품 상세' 화면에서 포함/불포함 사항이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 상세' 화면에서 상품명과 별점이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H77" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3297,10 +3297,10 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>미팅 장소 지도</v>
+        <v>후기 수</v>
       </c>
       <c r="G78" t="str">
-        <v>'상품 상세' 화면에서 미팅 장소 지도가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 상세' 화면에서 후기 수가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H78" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3329,13 +3329,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>취소</v>
+        <v>핵심 정보 배지(소요시간·언어·즉시확정·미팅장소)</v>
       </c>
       <c r="G79" t="str">
-        <v>'상품 상세'에서 취소를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'상품 상세'의 핵심 정보 배지(소요시간·언어·즉시확정·미팅장소)가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H79" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I79" t="str">
         <v/>
@@ -3361,13 +3361,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>환불 규정</v>
+        <v>가격과 할인율</v>
       </c>
       <c r="G80" t="str">
-        <v>'상품 상세'에서 환불 규정을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'상품 상세'의 가격과 할인율이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H80" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I80" t="str">
         <v/>
@@ -3393,13 +3393,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>후기 요약과 최신 후기 5개</v>
+        <v>상품 소개 본문</v>
       </c>
       <c r="G81" t="str">
-        <v>'상품 상세' 화면을 열고 후기 요약과 최신 후기 5개가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'상품 상세' 화면에서 상품 소개 본문이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H81" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I81" t="str">
         <v/>
@@ -3425,10 +3425,10 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>자주 묻는 질문</v>
+        <v>코스 일정 타임라인</v>
       </c>
       <c r="G82" t="str">
-        <v>'상품 상세' 화면에서 자주 묻는 질문이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 상세' 화면에서 코스 일정 타임라인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H82" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3457,10 +3457,10 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>하단 고정 예약 바</v>
+        <v>포함/불포함 사항</v>
       </c>
       <c r="G83" t="str">
-        <v>'상품 상세' 화면에서 하단 고정 예약 바가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 상세' 화면에서 포함/불포함 사항이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H83" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3474,25 +3474,25 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B84" t="str">
-        <v>상품</v>
+        <v/>
       </c>
       <c r="C84" t="str">
-        <v>날짜·옵션 선택</v>
+        <v/>
       </c>
       <c r="D84" t="str">
-        <v>PR-03</v>
+        <v/>
       </c>
       <c r="E84" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F84" t="str">
-        <v>달력에서 출발일 선택(예약 가능일만 활성)</v>
+        <v>미팅 장소 지도</v>
       </c>
       <c r="G84" t="str">
-        <v>'날짜·옵션 선택' 화면에서 달력에서 출발일 선택(예약 가능일만 활성)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 상세' 화면에서 미팅 장소 지도가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H84" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3506,7 +3506,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B85" t="str">
         <v/>
@@ -3521,13 +3521,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>시간대 선택</v>
+        <v>취소</v>
       </c>
       <c r="G85" t="str">
-        <v>'날짜·옵션 선택' 화면에서 시간대 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 상세'에서 취소를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H85" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I85" t="str">
         <v/>
@@ -3538,7 +3538,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B86" t="str">
         <v/>
@@ -3553,13 +3553,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>인원 선택(성인·아동·유아)</v>
+        <v>환불 규정</v>
       </c>
       <c r="G86" t="str">
-        <v>'날짜·옵션 선택' 화면에서 인원 선택(성인·아동·유아)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 상세'에서 환불 규정을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H86" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I86" t="str">
         <v/>
@@ -3570,7 +3570,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B87" t="str">
         <v/>
@@ -3585,13 +3585,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>옵션 선택(픽업 여부·좌석 등급)</v>
+        <v>후기 요약과 최신 후기 5개</v>
       </c>
       <c r="G87" t="str">
-        <v>'날짜·옵션 선택' 화면에서 옵션 선택(픽업 여부·좌석 등급)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 상세' 화면을 열고 후기 요약과 최신 후기 5개가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H87" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I87" t="str">
         <v/>
@@ -3602,7 +3602,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B88" t="str">
         <v/>
@@ -3617,13 +3617,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>실시간 잔여 좌석 표시</v>
+        <v>자주 묻는 질문</v>
       </c>
       <c r="G88" t="str">
-        <v>'날짜·옵션 선택'의 실시간 잔여 좌석 표시가 실제 데이터와 같은지 대조한다.</v>
+        <v>'상품 상세' 화면에서 자주 묻는 질문이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H88" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I88" t="str">
         <v/>
@@ -3634,7 +3634,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B89" t="str">
         <v/>
@@ -3649,13 +3649,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>총 금액 자동 계산</v>
+        <v>하단 고정 예약 바</v>
       </c>
       <c r="G89" t="str">
-        <v>'날짜·옵션 선택'의 총 금액 자동 계산이 실제 데이터와 같은지 대조한다.</v>
+        <v>'상품 상세' 화면에서 하단 고정 예약 바가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H89" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I89" t="str">
         <v/>
@@ -3666,28 +3666,28 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B90" t="str">
         <v>상품</v>
       </c>
       <c r="C90" t="str">
-        <v>패스 상품 상세</v>
+        <v>날짜·옵션 선택</v>
       </c>
       <c r="D90" t="str">
-        <v>PR-04</v>
+        <v>PR-03</v>
       </c>
       <c r="E90" t="str">
         <v>기본</v>
       </c>
       <c r="F90" t="str">
-        <v>패스 소개와 절약 금액 강조</v>
+        <v>달력에서 출발일 선택(예약 가능일만 활성)</v>
       </c>
       <c r="G90" t="str">
-        <v>'패스 상품 상세'의 패스 소개와 절약 금액 강조가 실제 데이터와 같은지 대조한다.</v>
+        <v>'날짜·옵션 선택' 화면에서 달력에서 출발일 선택(예약 가능일만 활성)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H90" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I90" t="str">
         <v/>
@@ -3698,7 +3698,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B91" t="str">
         <v/>
@@ -3713,13 +3713,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>포함 명소 목록과 개별 정가</v>
+        <v>시간대 선택</v>
       </c>
       <c r="G91" t="str">
-        <v>'패스 상품 상세'의 포함 명소 목록과 개별 정가를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'날짜·옵션 선택' 화면에서 시간대 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H91" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I91" t="str">
         <v/>
@@ -3730,7 +3730,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B92" t="str">
         <v/>
@@ -3745,10 +3745,10 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>이용 기간과 사용 규칙</v>
+        <v>인원 선택(성인·아동·유아)</v>
       </c>
       <c r="G92" t="str">
-        <v>'패스 상품 상세' 화면에서 이용 기간과 사용 규칙이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'날짜·옵션 선택' 화면에서 인원 선택(성인·아동·유아)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H92" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B93" t="str">
         <v/>
@@ -3777,13 +3777,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>패스 종류별 가격표(2일권·3일권)</v>
+        <v>옵션 선택(픽업 여부·좌석 등급)</v>
       </c>
       <c r="G93" t="str">
-        <v>'패스 상품 상세'의 패스 종류별 가격표(2일권·3일권)이 실제 데이터와 같은지 대조한다.</v>
+        <v>'날짜·옵션 선택' 화면에서 옵션 선택(픽업 여부·좌석 등급)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H93" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I93" t="str">
         <v/>
@@ -3794,7 +3794,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B94" t="str">
         <v/>
@@ -3809,13 +3809,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>사용 방법 3단계</v>
+        <v>실시간 잔여 좌석 표시</v>
       </c>
       <c r="G94" t="str">
-        <v>'패스 상품 상세' 화면을 열고 사용 방법 3단계가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'날짜·옵션 선택'의 실시간 잔여 좌석 표시가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H94" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I94" t="str">
         <v/>
@@ -3826,7 +3826,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B95" t="str">
         <v/>
@@ -3841,13 +3841,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>주의사항</v>
+        <v>총 금액 자동 계산</v>
       </c>
       <c r="G95" t="str">
-        <v>'패스 상품 상세' 화면에서 주의사항이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'날짜·옵션 선택'의 총 금액 자동 계산이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H95" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I95" t="str">
         <v/>
@@ -3861,25 +3861,25 @@
         <v>SCN-009</v>
       </c>
       <c r="B96" t="str">
-        <v/>
+        <v>상품</v>
       </c>
       <c r="C96" t="str">
-        <v/>
+        <v>패스 상품 상세</v>
       </c>
       <c r="D96" t="str">
-        <v/>
+        <v>PR-04</v>
       </c>
       <c r="E96" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F96" t="str">
-        <v>하단 고정 구매 바</v>
+        <v>패스 소개와 절약 금액 강조</v>
       </c>
       <c r="G96" t="str">
-        <v>'패스 상품 상세' 화면에서 하단 고정 구매 바가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'패스 상품 상세'의 패스 소개와 절약 금액 강조가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H96" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I96" t="str">
         <v/>
@@ -3890,28 +3890,28 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B97" t="str">
-        <v>상품</v>
+        <v/>
       </c>
       <c r="C97" t="str">
-        <v>상품 비교</v>
+        <v/>
       </c>
       <c r="D97" t="str">
-        <v>PR-05</v>
+        <v/>
       </c>
       <c r="E97" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F97" t="str">
-        <v>선택한 상품 2~3개를 표로 나란히 비교</v>
+        <v>포함 명소 목록과 개별 정가</v>
       </c>
       <c r="G97" t="str">
-        <v>'상품 비교' 화면을 열고 선택한 상품 2~3개를 표로 나란히 비교가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'패스 상품 상세'의 포함 명소 목록과 개별 정가를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H97" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I97" t="str">
         <v/>
@@ -3922,7 +3922,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B98" t="str">
         <v/>
@@ -3937,10 +3937,10 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>비교 항목(가격·소요시간·포함사항·미팅장소·취소규정·평점)</v>
+        <v>이용 기간과 사용 규칙</v>
       </c>
       <c r="G98" t="str">
-        <v>'상품 비교' 화면에서 비교 항목(가격·소요시간·포함사항·미팅장소·취소규정·평점)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'패스 상품 상세' 화면에서 이용 기간과 사용 규칙이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H98" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B99" t="str">
         <v/>
@@ -3969,13 +3969,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>차이나는 항목 강조</v>
+        <v>패스 종류별 가격표(2일권·3일권)</v>
       </c>
       <c r="G99" t="str">
-        <v>'상품 비교' 화면에서 차이나는 항목 강조가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'패스 상품 상세'의 패스 종류별 가격표(2일권·3일권)이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H99" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I99" t="str">
         <v/>
@@ -3986,7 +3986,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B100" t="str">
         <v/>
@@ -4001,13 +4001,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>각 열에서 바로 예약</v>
+        <v>사용 방법 3단계</v>
       </c>
       <c r="G100" t="str">
-        <v>'상품 비교' 화면에서 각 열에서 바로 예약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'패스 상품 상세' 화면을 열고 사용 방법 3단계가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H100" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I100" t="str">
         <v/>
@@ -4018,28 +4018,28 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>SCN-011</v>
+        <v>SCN-009</v>
       </c>
       <c r="B101" t="str">
-        <v>상품</v>
+        <v/>
       </c>
       <c r="C101" t="str">
-        <v>예약 마감·품절</v>
+        <v/>
       </c>
       <c r="D101" t="str">
-        <v>PR-06</v>
+        <v/>
       </c>
       <c r="E101" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F101" t="str">
-        <v>마감 사유 안내(좌석 소진·판매 종료·시즌 종료)</v>
+        <v>주의사항</v>
       </c>
       <c r="G101" t="str">
-        <v>일부러 그 상황을 만들어 '예약 마감·품절' 화면이 나오게 한 뒤, 마감 사유 안내(좌석 소진·판매 종료·시즌 종료)가 보이는지 확인한다.</v>
+        <v>'패스 상품 상세' 화면에서 주의사항이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H101" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I101" t="str">
         <v/>
@@ -4050,7 +4050,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>SCN-011</v>
+        <v>SCN-009</v>
       </c>
       <c r="B102" t="str">
         <v/>
@@ -4065,13 +4065,13 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>다음 예약 가능일 안내</v>
+        <v>하단 고정 구매 바</v>
       </c>
       <c r="G102" t="str">
-        <v>일부러 그 상황을 만들어 '예약 마감·품절' 화면이 나오게 한 뒤, 다음 예약 가능일 안내가 보이는지 확인한다.</v>
+        <v>'패스 상품 상세' 화면에서 하단 고정 구매 바가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H102" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I102" t="str">
         <v/>
@@ -4082,28 +4082,28 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>SCN-011</v>
+        <v>SCN-010</v>
       </c>
       <c r="B103" t="str">
-        <v/>
+        <v>상품</v>
       </c>
       <c r="C103" t="str">
-        <v/>
+        <v>상품 비교</v>
       </c>
       <c r="D103" t="str">
-        <v/>
+        <v>PR-05</v>
       </c>
       <c r="E103" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F103" t="str">
-        <v>재입고 알림 신청</v>
+        <v>선택한 상품 2~3개를 표로 나란히 비교</v>
       </c>
       <c r="G103" t="str">
-        <v>일부러 그 상황을 만들어 '예약 마감·품절' 화면이 나오게 한 뒤, 재입고 알림 신청이 보이는지 확인한다.</v>
+        <v>'상품 비교' 화면을 열고 선택한 상품 2~3개를 표로 나란히 비교가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H103" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I103" t="str">
         <v/>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>SCN-011</v>
+        <v>SCN-010</v>
       </c>
       <c r="B104" t="str">
         <v/>
@@ -4129,13 +4129,13 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>비슷한 상품 4개 추천</v>
+        <v>비교 항목(가격·소요시간·포함사항·미팅장소·취소규정·평점)</v>
       </c>
       <c r="G104" t="str">
-        <v>일부러 그 상황을 만들어 '예약 마감·품절' 화면이 나오게 한 뒤, 비슷한 상품 4개 추천이 보이는지 확인한다.</v>
+        <v>'상품 비교' 화면에서 비교 항목(가격·소요시간·포함사항·미팅장소·취소규정·평점)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H104" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I104" t="str">
         <v/>
@@ -4146,25 +4146,25 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>SCN-012</v>
+        <v>SCN-010</v>
       </c>
       <c r="B105" t="str">
-        <v>상품</v>
+        <v/>
       </c>
       <c r="C105" t="str">
-        <v>후기 전체보기</v>
+        <v/>
       </c>
       <c r="D105" t="str">
-        <v>PR-07</v>
+        <v/>
       </c>
       <c r="E105" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F105" t="str">
-        <v>평점 분포 막대그래프</v>
+        <v>차이나는 항목 강조</v>
       </c>
       <c r="G105" t="str">
-        <v>'후기 전체보기' 화면에서 평점 분포 막대그래프가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'상품 비교' 화면에서 차이나는 항목 강조가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H105" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4178,7 +4178,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>SCN-012</v>
+        <v>SCN-010</v>
       </c>
       <c r="B106" t="str">
         <v/>
@@ -4193,13 +4193,13 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>필터(별점·사진후기만·최근순)</v>
+        <v>각 열에서 바로 예약</v>
       </c>
       <c r="G106" t="str">
-        <v>'후기 전체보기'에서 필터(별점·사진후기만·최근순)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'상품 비교' 화면에서 각 열에서 바로 예약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H106" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I106" t="str">
         <v/>
@@ -4210,28 +4210,28 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>SCN-012</v>
+        <v>SCN-011</v>
       </c>
       <c r="B107" t="str">
-        <v/>
+        <v>상품</v>
       </c>
       <c r="C107" t="str">
-        <v/>
+        <v>예약 마감·품절</v>
       </c>
       <c r="D107" t="str">
-        <v/>
+        <v>PR-06</v>
       </c>
       <c r="E107" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F107" t="str">
-        <v>후기 카드 목록(사진·별점·본문·여행일·동행유형)</v>
+        <v>마감 사유 안내(좌석 소진·판매 종료·시즌 종료)</v>
       </c>
       <c r="G107" t="str">
-        <v>'후기 전체보기'의 후기 카드 목록(사진·별점·본문·여행일·동행유형)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '예약 마감·품절' 화면이 나오게 한 뒤, 마감 사유 안내(좌석 소진·판매 종료·시즌 종료)가 보이는지 확인한다.</v>
       </c>
       <c r="H107" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I107" t="str">
         <v/>
@@ -4242,7 +4242,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>SCN-012</v>
+        <v>SCN-011</v>
       </c>
       <c r="B108" t="str">
         <v/>
@@ -4257,13 +4257,13 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>도움돼요 버튼</v>
+        <v>다음 예약 가능일 안내</v>
       </c>
       <c r="G108" t="str">
-        <v>'후기 전체보기'에서 도움돼요 버튼을 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '예약 마감·품절' 화면이 나오게 한 뒤, 다음 예약 가능일 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H108" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I108" t="str">
         <v/>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>SCN-012</v>
+        <v>SCN-011</v>
       </c>
       <c r="B109" t="str">
         <v/>
@@ -4289,13 +4289,13 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>더보기</v>
+        <v>재입고 알림 신청</v>
       </c>
       <c r="G109" t="str">
-        <v>'후기 전체보기'에서 더보기의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>일부러 그 상황을 만들어 '예약 마감·품절' 화면이 나오게 한 뒤, 재입고 알림 신청이 보이는지 확인한다.</v>
       </c>
       <c r="H109" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I109" t="str">
         <v/>
@@ -4306,28 +4306,28 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>SCN-013</v>
+        <v>SCN-011</v>
       </c>
       <c r="B110" t="str">
-        <v>상품</v>
+        <v/>
       </c>
       <c r="C110" t="str">
-        <v>찜한 상품</v>
+        <v/>
       </c>
       <c r="D110" t="str">
-        <v>PR-08</v>
+        <v/>
       </c>
       <c r="E110" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F110" t="str">
-        <v>찜한 상품 카드 목록(사진·상품명·별점·가격)</v>
+        <v>비슷한 상품 4개 추천</v>
       </c>
       <c r="G110" t="str">
-        <v>'찜한 상품'의 찜한 상품 카드 목록(사진·상품명·별점·가격)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '예약 마감·품절' 화면이 나오게 한 뒤, 비슷한 상품 4개 추천이 보이는지 확인한다.</v>
       </c>
       <c r="H110" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I110" t="str">
         <v/>
@@ -4338,25 +4338,25 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B111" t="str">
-        <v/>
+        <v>상품</v>
       </c>
       <c r="C111" t="str">
-        <v/>
+        <v>후기 전체보기</v>
       </c>
       <c r="D111" t="str">
-        <v/>
+        <v>PR-07</v>
       </c>
       <c r="E111" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F111" t="str">
-        <v>여행지</v>
+        <v>평점 분포 막대그래프</v>
       </c>
       <c r="G111" t="str">
-        <v>'찜한 상품' 화면에서 여행지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'후기 전체보기' 화면에서 평점 분포 막대그래프가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H111" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4370,7 +4370,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B112" t="str">
         <v/>
@@ -4385,10 +4385,10 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>카테고리 필터</v>
+        <v>필터(별점·사진후기만·최근순)</v>
       </c>
       <c r="G112" t="str">
-        <v>'찜한 상품'에서 카테고리 필터의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'후기 전체보기'에서 필터(별점·사진후기만·최근순)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H112" t="str">
         <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
@@ -4402,7 +4402,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B113" t="str">
         <v/>
@@ -4417,13 +4417,13 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>정렬(담은 순·낮은 가격순·할인율순)</v>
+        <v>후기 카드 목록(사진·별점·본문·여행일·동행유형)</v>
       </c>
       <c r="G113" t="str">
-        <v>'찜한 상품'에서 정렬(담은 순·낮은 가격순·할인율순)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'후기 전체보기'의 후기 카드 목록(사진·별점·본문·여행일·동행유형)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H113" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I113" t="str">
         <v/>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B114" t="str">
         <v/>
@@ -4449,13 +4449,13 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>가격 인하 배지와 이전 가격 비교</v>
+        <v>도움돼요 버튼</v>
       </c>
       <c r="G114" t="str">
-        <v>'찜한 상품'의 가격 인하 배지와 이전 가격 비교가 실제 데이터와 같은지 대조한다.</v>
+        <v>'후기 전체보기'에서 도움돼요 버튼을 눌러 본다.</v>
       </c>
       <c r="H114" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I114" t="str">
         <v/>
@@ -4466,7 +4466,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B115" t="str">
         <v/>
@@ -4481,13 +4481,13 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>마감임박</v>
+        <v>더보기</v>
       </c>
       <c r="G115" t="str">
-        <v>'찜한 상품' 화면에서 마감임박이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'후기 전체보기'에서 더보기의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H115" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I115" t="str">
         <v/>
@@ -4501,25 +4501,25 @@
         <v>SCN-013</v>
       </c>
       <c r="B116" t="str">
-        <v/>
+        <v>상품</v>
       </c>
       <c r="C116" t="str">
-        <v/>
+        <v>찜한 상품</v>
       </c>
       <c r="D116" t="str">
-        <v/>
+        <v>PR-08</v>
       </c>
       <c r="E116" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F116" t="str">
-        <v>품절 상태 표시</v>
+        <v>찜한 상품 카드 목록(사진·상품명·별점·가격)</v>
       </c>
       <c r="G116" t="str">
-        <v>'찜한 상품'의 품절 상태 표시가 실제 데이터와 같은지 대조한다.</v>
+        <v>'찜한 상품'의 찜한 상품 카드 목록(사진·상품명·별점·가격)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H116" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I116" t="str">
         <v/>
@@ -4545,10 +4545,10 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>개별 찜 해제와 선택 삭제</v>
+        <v>여행지</v>
       </c>
       <c r="G117" t="str">
-        <v>'찜한 상품' 화면에서 개별 찜 해제와 선택 삭제가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'찜한 상품' 화면에서 여행지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H117" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4577,13 +4577,13 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>장바구니에 담기</v>
+        <v>카테고리 필터</v>
       </c>
       <c r="G118" t="str">
-        <v>'찜한 상품' 화면에서 장바구니에 담기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'찜한 상품'에서 카테고리 필터의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H118" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I118" t="str">
         <v/>
@@ -4609,13 +4609,13 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>상품 비교에 추가</v>
+        <v>정렬(담은 순·낮은 가격순·할인율순)</v>
       </c>
       <c r="G119" t="str">
-        <v>'찜한 상품' 화면에서 상품 비교에 추가가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'찜한 상품'에서 정렬(담은 순·낮은 가격순·할인율순)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H119" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I119" t="str">
         <v/>
@@ -4641,10 +4641,10 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>가격 알림 신청</v>
+        <v>가격 인하 배지와 이전 가격 비교</v>
       </c>
       <c r="G120" t="str">
-        <v>'찜한 상품'의 가격 알림 신청이 실제 데이터와 같은지 대조한다.</v>
+        <v>'찜한 상품'의 가격 인하 배지와 이전 가격 비교가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H120" t="str">
         <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
@@ -4673,13 +4673,13 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>찜한 상품 없을 때 추천 상품 4개</v>
+        <v>마감임박</v>
       </c>
       <c r="G121" t="str">
-        <v>'찜한 상품' 화면을 열고 찜한 상품 없을 때 추천 상품 4개가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'찜한 상품' 화면에서 마감임박이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H121" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I121" t="str">
         <v/>
@@ -4690,28 +4690,28 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B122" t="str">
-        <v>장바구니</v>
+        <v/>
       </c>
       <c r="C122" t="str">
-        <v>장바구니</v>
+        <v/>
       </c>
       <c r="D122" t="str">
-        <v>CT-01</v>
+        <v/>
       </c>
       <c r="E122" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F122" t="str">
-        <v>담은 상품 목록(사진·상품명·날짜·인원·옵션·금액)</v>
+        <v>품절 상태 표시</v>
       </c>
       <c r="G122" t="str">
-        <v>'장바구니'의 담은 상품 목록(사진·상품명·날짜·인원·옵션·금액)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'찜한 상품'의 품절 상태 표시가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H122" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I122" t="str">
         <v/>
@@ -4722,7 +4722,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B123" t="str">
         <v/>
@@ -4737,10 +4737,10 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>개별 선택 체크박스</v>
+        <v>개별 찜 해제와 선택 삭제</v>
       </c>
       <c r="G123" t="str">
-        <v>'장바구니' 화면에서 개별 선택 체크박스가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'찜한 상품' 화면에서 개별 찜 해제와 선택 삭제가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H123" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B124" t="str">
         <v/>
@@ -4769,10 +4769,10 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>수량</v>
+        <v>장바구니에 담기</v>
       </c>
       <c r="G124" t="str">
-        <v>'장바구니' 화면에서 수량이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'찜한 상품' 화면에서 장바구니에 담기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H124" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4786,7 +4786,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B125" t="str">
         <v/>
@@ -4801,10 +4801,10 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>옵션 수정</v>
+        <v>상품 비교에 추가</v>
       </c>
       <c r="G125" t="str">
-        <v>'장바구니' 화면에서 옵션 수정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'찜한 상품' 화면에서 상품 비교에 추가가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H125" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4818,7 +4818,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B126" t="str">
         <v/>
@@ -4833,13 +4833,13 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>삭제</v>
+        <v>가격 알림 신청</v>
       </c>
       <c r="G126" t="str">
-        <v>'장바구니' 화면에서 삭제가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'찜한 상품'의 가격 알림 신청이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H126" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I126" t="str">
         <v/>
@@ -4850,7 +4850,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B127" t="str">
         <v/>
@@ -4865,13 +4865,13 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>예약 불가 항목 경고</v>
+        <v>찜한 상품 없을 때 추천 상품 4개</v>
       </c>
       <c r="G127" t="str">
-        <v>'장바구니' 화면에서 예약 불가 항목 경고가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'찜한 상품' 화면을 열고 찜한 상품 없을 때 추천 상품 4개가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H127" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I127" t="str">
         <v/>
@@ -4885,25 +4885,25 @@
         <v>SCN-014</v>
       </c>
       <c r="B128" t="str">
-        <v/>
+        <v>장바구니</v>
       </c>
       <c r="C128" t="str">
-        <v/>
+        <v>장바구니</v>
       </c>
       <c r="D128" t="str">
-        <v/>
+        <v>CT-01</v>
       </c>
       <c r="E128" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F128" t="str">
-        <v>금액 요약과 결제 버튼</v>
+        <v>담은 상품 목록(사진·상품명·날짜·인원·옵션·금액)</v>
       </c>
       <c r="G128" t="str">
-        <v>'장바구니'에서 금액 요약과 결제 버튼을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'장바구니'의 담은 상품 목록(사진·상품명·날짜·인원·옵션·금액)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H128" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I128" t="str">
         <v/>
@@ -4914,28 +4914,28 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>SCN-015</v>
+        <v>SCN-014</v>
       </c>
       <c r="B129" t="str">
-        <v>장바구니</v>
+        <v/>
       </c>
       <c r="C129" t="str">
-        <v>장바구니 비어 있음</v>
+        <v/>
       </c>
       <c r="D129" t="str">
-        <v>CT-02</v>
+        <v/>
       </c>
       <c r="E129" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F129" t="str">
-        <v>빈 상태 일러스트와 안내 문구</v>
+        <v>개별 선택 체크박스</v>
       </c>
       <c r="G129" t="str">
-        <v>일부러 그 상황을 만들어 '장바구니 비어 있음' 화면이 나오게 한 뒤, 빈 상태 일러스트와 안내 문구가 보이는지 확인한다.</v>
+        <v>'장바구니' 화면에서 개별 선택 체크박스가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H129" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I129" t="str">
         <v/>
@@ -4946,7 +4946,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>SCN-015</v>
+        <v>SCN-014</v>
       </c>
       <c r="B130" t="str">
         <v/>
@@ -4961,13 +4961,13 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>인기 상품 둘러보기 버튼</v>
+        <v>수량</v>
       </c>
       <c r="G130" t="str">
-        <v>일부러 그 상황을 만들어 '장바구니 비어 있음' 화면이 나오게 한 뒤, 인기 상품 둘러보기 버튼이 보이는지 확인한다.</v>
+        <v>'장바구니' 화면에서 수량이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H130" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I130" t="str">
         <v/>
@@ -4978,7 +4978,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>SCN-015</v>
+        <v>SCN-014</v>
       </c>
       <c r="B131" t="str">
         <v/>
@@ -4993,13 +4993,13 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>최근 본 상품 4개</v>
+        <v>옵션 수정</v>
       </c>
       <c r="G131" t="str">
-        <v>일부러 그 상황을 만들어 '장바구니 비어 있음' 화면이 나오게 한 뒤, 최근 본 상품 4개가 보이는지 확인한다.</v>
+        <v>'장바구니' 화면에서 옵션 수정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H131" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I131" t="str">
         <v/>
@@ -5010,25 +5010,25 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>SCN-016</v>
+        <v>SCN-014</v>
       </c>
       <c r="B132" t="str">
-        <v>예약·결제</v>
+        <v/>
       </c>
       <c r="C132" t="str">
-        <v>여행자 정보 입력</v>
+        <v/>
       </c>
       <c r="D132" t="str">
-        <v>BK-01</v>
+        <v/>
       </c>
       <c r="E132" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F132" t="str">
-        <v>예약 상품 요약</v>
+        <v>삭제</v>
       </c>
       <c r="G132" t="str">
-        <v>'여행자 정보 입력' 화면에서 예약 상품 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장바구니' 화면에서 삭제가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H132" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5042,7 +5042,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>SCN-016</v>
+        <v>SCN-014</v>
       </c>
       <c r="B133" t="str">
         <v/>
@@ -5057,13 +5057,13 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>대표 예약자 정보(이름·영문명·연락처·이메일)</v>
+        <v>예약 불가 항목 경고</v>
       </c>
       <c r="G133" t="str">
-        <v>'여행자 정보 입력'의 대표 예약자 정보(이름·영문명·연락처·이메일)이 실제 데이터와 같은지 대조한다.</v>
+        <v>'장바구니' 화면에서 예약 불가 항목 경고가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H133" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I133" t="str">
         <v/>
@@ -5074,7 +5074,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>SCN-016</v>
+        <v>SCN-014</v>
       </c>
       <c r="B134" t="str">
         <v/>
@@ -5089,13 +5089,13 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>인원별 여행자 정보(영문명·생년월일)</v>
+        <v>금액 요약과 결제 버튼</v>
       </c>
       <c r="G134" t="str">
-        <v>'여행자 정보 입력'의 인원별 여행자 정보(영문명·생년월일)이 실제 데이터와 같은지 대조한다.</v>
+        <v>'장바구니'에서 금액 요약과 결제 버튼을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H134" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I134" t="str">
         <v/>
@@ -5106,28 +5106,28 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>SCN-016</v>
+        <v>SCN-015</v>
       </c>
       <c r="B135" t="str">
-        <v/>
+        <v>장바구니</v>
       </c>
       <c r="C135" t="str">
-        <v/>
+        <v>장바구니 비어 있음</v>
       </c>
       <c r="D135" t="str">
-        <v/>
+        <v>CT-02</v>
       </c>
       <c r="E135" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F135" t="str">
-        <v>픽업 호텔 입력</v>
+        <v>빈 상태 일러스트와 안내 문구</v>
       </c>
       <c r="G135" t="str">
-        <v>'여행자 정보 입력'의 픽업 호텔 입력에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>일부러 그 상황을 만들어 '장바구니 비어 있음' 화면이 나오게 한 뒤, 빈 상태 일러스트와 안내 문구가 보이는지 확인한다.</v>
       </c>
       <c r="H135" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I135" t="str">
         <v/>
@@ -5138,7 +5138,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>SCN-016</v>
+        <v>SCN-015</v>
       </c>
       <c r="B136" t="str">
         <v/>
@@ -5153,13 +5153,13 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>요청사항</v>
+        <v>인기 상품 둘러보기 버튼</v>
       </c>
       <c r="G136" t="str">
-        <v>'여행자 정보 입력' 화면에서 요청사항이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '장바구니 비어 있음' 화면이 나오게 한 뒤, 인기 상품 둘러보기 버튼이 보이는지 확인한다.</v>
       </c>
       <c r="H136" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I136" t="str">
         <v/>
@@ -5170,7 +5170,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>SCN-016</v>
+        <v>SCN-015</v>
       </c>
       <c r="B137" t="str">
         <v/>
@@ -5185,13 +5185,13 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>약관 동의</v>
+        <v>최근 본 상품 4개</v>
       </c>
       <c r="G137" t="str">
-        <v>'여행자 정보 입력' 화면에서 약관 동의가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '장바구니 비어 있음' 화면이 나오게 한 뒤, 최근 본 상품 4개가 보이는지 확인한다.</v>
       </c>
       <c r="H137" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I137" t="str">
         <v/>
@@ -5202,25 +5202,25 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B138" t="str">
         <v>예약·결제</v>
       </c>
       <c r="C138" t="str">
-        <v>결제</v>
+        <v>여행자 정보 입력</v>
       </c>
       <c r="D138" t="str">
-        <v>BK-02</v>
+        <v>BK-01</v>
       </c>
       <c r="E138" t="str">
         <v>기본</v>
       </c>
       <c r="F138" t="str">
-        <v>예약 내역 요약</v>
+        <v>예약 상품 요약</v>
       </c>
       <c r="G138" t="str">
-        <v>'결제' 화면에서 예약 내역 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'여행자 정보 입력' 화면에서 예약 상품 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H138" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5234,7 +5234,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B139" t="str">
         <v/>
@@ -5249,13 +5249,13 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>쿠폰</v>
+        <v>대표 예약자 정보(이름·영문명·연락처·이메일)</v>
       </c>
       <c r="G139" t="str">
-        <v>'결제' 화면에서 쿠폰이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'여행자 정보 입력'의 대표 예약자 정보(이름·영문명·연락처·이메일)이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H139" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I139" t="str">
         <v/>
@@ -5266,7 +5266,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B140" t="str">
         <v/>
@@ -5281,13 +5281,13 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>포인트 적용</v>
+        <v>인원별 여행자 정보(영문명·생년월일)</v>
       </c>
       <c r="G140" t="str">
-        <v>'결제' 화면에서 포인트 적용이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'여행자 정보 입력'의 인원별 여행자 정보(영문명·생년월일)이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H140" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I140" t="str">
         <v/>
@@ -5298,7 +5298,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B141" t="str">
         <v/>
@@ -5313,13 +5313,13 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>결제 수단 선택(카드·간편결제·해외결제)</v>
+        <v>픽업 호텔 입력</v>
       </c>
       <c r="G141" t="str">
-        <v>'결제'에서 결제 수단 선택(카드·간편결제·해외결제)를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'여행자 정보 입력'의 픽업 호텔 입력에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H141" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I141" t="str">
         <v/>
@@ -5330,7 +5330,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B142" t="str">
         <v/>
@@ -5345,13 +5345,13 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>최종 금액 계산</v>
+        <v>요청사항</v>
       </c>
       <c r="G142" t="str">
-        <v>'결제'의 최종 금액 계산이 실제 데이터와 같은지 대조한다.</v>
+        <v>'여행자 정보 입력' 화면에서 요청사항이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H142" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I142" t="str">
         <v/>
@@ -5362,7 +5362,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B143" t="str">
         <v/>
@@ -5377,10 +5377,10 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>환율 안내</v>
+        <v>약관 동의</v>
       </c>
       <c r="G143" t="str">
-        <v>'결제' 화면에서 환율 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'여행자 정보 입력' 화면에서 약관 동의가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H143" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5397,25 +5397,25 @@
         <v>SCN-017</v>
       </c>
       <c r="B144" t="str">
-        <v/>
+        <v>예약·결제</v>
       </c>
       <c r="C144" t="str">
-        <v/>
+        <v>결제</v>
       </c>
       <c r="D144" t="str">
-        <v/>
+        <v>BK-02</v>
       </c>
       <c r="E144" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F144" t="str">
-        <v>결제 진행</v>
+        <v>예약 내역 요약</v>
       </c>
       <c r="G144" t="str">
-        <v>'결제'에서 결제 진행을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'결제' 화면에서 예약 내역 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H144" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I144" t="str">
         <v/>
@@ -5426,25 +5426,25 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B145" t="str">
-        <v>예약·결제</v>
+        <v/>
       </c>
       <c r="C145" t="str">
-        <v>예약 완료</v>
+        <v/>
       </c>
       <c r="D145" t="str">
-        <v>BK-03</v>
+        <v/>
       </c>
       <c r="E145" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F145" t="str">
-        <v>완료 아이콘과 예약번호</v>
+        <v>쿠폰</v>
       </c>
       <c r="G145" t="str">
-        <v>'예약 완료' 화면에서 완료 아이콘과 예약번호가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'결제' 화면에서 쿠폰이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H145" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5458,7 +5458,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B146" t="str">
         <v/>
@@ -5473,10 +5473,10 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>예약 상품 요약</v>
+        <v>포인트 적용</v>
       </c>
       <c r="G146" t="str">
-        <v>'예약 완료' 화면에서 예약 상품 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'결제' 화면에서 포인트 적용이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H146" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5490,7 +5490,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B147" t="str">
         <v/>
@@ -5505,13 +5505,13 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>바우처 발급 안내</v>
+        <v>결제 수단 선택(카드·간편결제·해외결제)</v>
       </c>
       <c r="G147" t="str">
-        <v>'예약 완료' 화면에서 바우처 발급 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'결제'에서 결제 수단 선택(카드·간편결제·해외결제)를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H147" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I147" t="str">
         <v/>
@@ -5522,7 +5522,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B148" t="str">
         <v/>
@@ -5537,13 +5537,13 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>미팅 장소와 시간 재안내</v>
+        <v>최종 금액 계산</v>
       </c>
       <c r="G148" t="str">
-        <v>'예약 완료' 화면에서 미팅 장소와 시간 재안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'결제'의 최종 금액 계산이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H148" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I148" t="str">
         <v/>
@@ -5554,7 +5554,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B149" t="str">
         <v/>
@@ -5569,13 +5569,13 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>준비물 체크리스트</v>
+        <v>환율 안내</v>
       </c>
       <c r="G149" t="str">
-        <v>'예약 완료'의 준비물 체크리스트를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'결제' 화면에서 환율 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H149" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I149" t="str">
         <v/>
@@ -5586,7 +5586,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B150" t="str">
         <v/>
@@ -5601,13 +5601,13 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>예약 내역 바로가기</v>
+        <v>결제 진행</v>
       </c>
       <c r="G150" t="str">
-        <v>'예약 완료'에서 예약 내역 바로가기를 눌러 본다.</v>
+        <v>'결제'에서 결제 진행을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H150" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I150" t="str">
         <v/>
@@ -5618,28 +5618,28 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B151" t="str">
         <v>예약·결제</v>
       </c>
       <c r="C151" t="str">
-        <v>결제 실패</v>
+        <v>예약 완료</v>
       </c>
       <c r="D151" t="str">
-        <v>BK-04</v>
+        <v>BK-03</v>
       </c>
       <c r="E151" t="str">
-        <v>예외·상태</v>
+        <v>기본</v>
       </c>
       <c r="F151" t="str">
-        <v>실패 아이콘과 사유를 쉬운 말로 안내</v>
+        <v>완료 아이콘과 예약번호</v>
       </c>
       <c r="G151" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 실패 아이콘과 사유를 쉬운 말로 안내가 보이는지 확인한다.</v>
+        <v>'예약 완료' 화면에서 완료 아이콘과 예약번호가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H151" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I151" t="str">
         <v/>
@@ -5650,7 +5650,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B152" t="str">
         <v/>
@@ -5665,13 +5665,13 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>자주 있는 원인 3가지</v>
+        <v>예약 상품 요약</v>
       </c>
       <c r="G152" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 자주 있는 원인 3가지가 보이는지 확인한다.</v>
+        <v>'예약 완료' 화면에서 예약 상품 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H152" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I152" t="str">
         <v/>
@@ -5682,7 +5682,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B153" t="str">
         <v/>
@@ -5697,13 +5697,13 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>다시 시도 버튼</v>
+        <v>바우처 발급 안내</v>
       </c>
       <c r="G153" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 다시 시도 버튼이 보이는지 확인한다.</v>
+        <v>'예약 완료' 화면에서 바우처 발급 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H153" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I153" t="str">
         <v/>
@@ -5714,7 +5714,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B154" t="str">
         <v/>
@@ -5729,13 +5729,13 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>다른 결제 수단 안내</v>
+        <v>미팅 장소와 시간 재안내</v>
       </c>
       <c r="G154" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 다른 결제 수단 안내가 보이는지 확인한다.</v>
+        <v>'예약 완료' 화면에서 미팅 장소와 시간 재안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H154" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I154" t="str">
         <v/>
@@ -5746,7 +5746,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B155" t="str">
         <v/>
@@ -5761,13 +5761,13 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>고객센터 연결</v>
+        <v>준비물 체크리스트</v>
       </c>
       <c r="G155" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 고객센터 연결이 보이는지 확인한다.</v>
+        <v>'예약 완료'의 준비물 체크리스트를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H155" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I155" t="str">
         <v/>
@@ -5778,28 +5778,28 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>SCN-020</v>
+        <v>SCN-018</v>
       </c>
       <c r="B156" t="str">
-        <v>예약·결제</v>
+        <v/>
       </c>
       <c r="C156" t="str">
-        <v>예약 확정 대기</v>
+        <v/>
       </c>
       <c r="D156" t="str">
-        <v>BK-05</v>
+        <v/>
       </c>
       <c r="E156" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F156" t="str">
-        <v>대기 상태 안내와 예상 확정 시각</v>
+        <v>예약 내역 바로가기</v>
       </c>
       <c r="G156" t="str">
-        <v>일부러 그 상황을 만들어 '예약 확정 대기' 화면이 나오게 한 뒤, 대기 상태 안내와 예상 확정 시각이 보이는지 확인한다.</v>
+        <v>'예약 완료'에서 예약 내역 바로가기를 눌러 본다.</v>
       </c>
       <c r="H156" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I156" t="str">
         <v/>
@@ -5810,25 +5810,25 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>SCN-020</v>
+        <v>SCN-019</v>
       </c>
       <c r="B157" t="str">
-        <v/>
+        <v>예약·결제</v>
       </c>
       <c r="C157" t="str">
-        <v/>
+        <v>결제 실패</v>
       </c>
       <c r="D157" t="str">
-        <v/>
+        <v>BK-04</v>
       </c>
       <c r="E157" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F157" t="str">
-        <v>왜 대기가 필요한지 설명</v>
+        <v>실패 아이콘과 사유를 쉬운 말로 안내</v>
       </c>
       <c r="G157" t="str">
-        <v>일부러 그 상황을 만들어 '예약 확정 대기' 화면이 나오게 한 뒤, 왜 대기가 필요한지 설명이 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 실패 아이콘과 사유를 쉬운 말로 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H157" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -5842,7 +5842,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>SCN-020</v>
+        <v>SCN-019</v>
       </c>
       <c r="B158" t="str">
         <v/>
@@ -5857,10 +5857,10 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>확정 알림 방법 안내</v>
+        <v>자주 있는 원인 3가지</v>
       </c>
       <c r="G158" t="str">
-        <v>일부러 그 상황을 만들어 '예약 확정 대기' 화면이 나오게 한 뒤, 확정 알림 방법 안내가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 자주 있는 원인 3가지가 보이는지 확인한다.</v>
       </c>
       <c r="H158" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -5874,7 +5874,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>SCN-020</v>
+        <v>SCN-019</v>
       </c>
       <c r="B159" t="str">
         <v/>
@@ -5889,10 +5889,10 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>대기 중 취소 시 전액 환불 안내</v>
+        <v>다시 시도 버튼</v>
       </c>
       <c r="G159" t="str">
-        <v>일부러 그 상황을 만들어 '예약 확정 대기' 화면이 나오게 한 뒤, 대기 중 취소 시 전액 환불 안내가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 다시 시도 버튼이 보이는지 확인한다.</v>
       </c>
       <c r="H159" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -5906,7 +5906,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>SCN-020</v>
+        <v>SCN-019</v>
       </c>
       <c r="B160" t="str">
         <v/>
@@ -5921,10 +5921,10 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>예약 내역 바로가기</v>
+        <v>다른 결제 수단 안내</v>
       </c>
       <c r="G160" t="str">
-        <v>일부러 그 상황을 만들어 '예약 확정 대기' 화면이 나오게 한 뒤, 예약 내역 바로가기가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 다른 결제 수단 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H160" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -5938,25 +5938,25 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>SCN-021</v>
+        <v>SCN-019</v>
       </c>
       <c r="B161" t="str">
-        <v>예약·결제</v>
+        <v/>
       </c>
       <c r="C161" t="str">
-        <v>최소 인원 미달 안내</v>
+        <v/>
       </c>
       <c r="D161" t="str">
-        <v>BK-06</v>
+        <v/>
       </c>
       <c r="E161" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F161" t="str">
-        <v>출발 확정 인원과 현재 인원 표시</v>
+        <v>고객센터 연결</v>
       </c>
       <c r="G161" t="str">
-        <v>일부러 그 상황을 만들어 '최소 인원 미달 안내' 화면이 나오게 한 뒤, 출발 확정 인원과 현재 인원 표시가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 고객센터 연결이 보이는지 확인한다.</v>
       </c>
       <c r="H161" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -5970,25 +5970,25 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>SCN-021</v>
+        <v>SCN-020</v>
       </c>
       <c r="B162" t="str">
-        <v/>
+        <v>예약·결제</v>
       </c>
       <c r="C162" t="str">
-        <v/>
+        <v>예약 확정 대기</v>
       </c>
       <c r="D162" t="str">
-        <v/>
+        <v>BK-05</v>
       </c>
       <c r="E162" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F162" t="str">
-        <v>확정 마감 시각 안내</v>
+        <v>대기 상태 안내와 예상 확정 시각</v>
       </c>
       <c r="G162" t="str">
-        <v>일부러 그 상황을 만들어 '최소 인원 미달 안내' 화면이 나오게 한 뒤, 확정 마감 시각 안내가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '예약 확정 대기' 화면이 나오게 한 뒤, 대기 상태 안내와 예상 확정 시각이 보이는지 확인한다.</v>
       </c>
       <c r="H162" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -6002,7 +6002,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>SCN-021</v>
+        <v>SCN-020</v>
       </c>
       <c r="B163" t="str">
         <v/>
@@ -6017,10 +6017,10 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>미달 시 전액 환불 안내</v>
+        <v>왜 대기가 필요한지 설명</v>
       </c>
       <c r="G163" t="str">
-        <v>일부러 그 상황을 만들어 '최소 인원 미달 안내' 화면이 나오게 한 뒤, 미달 시 전액 환불 안내가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '예약 확정 대기' 화면이 나오게 한 뒤, 왜 대기가 필요한지 설명이 보이는지 확인한다.</v>
       </c>
       <c r="H163" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -6034,7 +6034,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>SCN-021</v>
+        <v>SCN-020</v>
       </c>
       <c r="B164" t="str">
         <v/>
@@ -6049,10 +6049,10 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>대체 상품 추천</v>
+        <v>확정 알림 방법 안내</v>
       </c>
       <c r="G164" t="str">
-        <v>일부러 그 상황을 만들어 '최소 인원 미달 안내' 화면이 나오게 한 뒤, 대체 상품 추천이 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '예약 확정 대기' 화면이 나오게 한 뒤, 확정 알림 방법 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H164" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -6066,7 +6066,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>SCN-021</v>
+        <v>SCN-020</v>
       </c>
       <c r="B165" t="str">
         <v/>
@@ -6081,10 +6081,10 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>친구 초대 공유</v>
+        <v>대기 중 취소 시 전액 환불 안내</v>
       </c>
       <c r="G165" t="str">
-        <v>일부러 그 상황을 만들어 '최소 인원 미달 안내' 화면이 나오게 한 뒤, 친구 초대 공유가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '예약 확정 대기' 화면이 나오게 한 뒤, 대기 중 취소 시 전액 환불 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H165" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -6098,28 +6098,28 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>SCN-022</v>
+        <v>SCN-020</v>
       </c>
       <c r="B166" t="str">
-        <v>바우처</v>
+        <v/>
       </c>
       <c r="C166" t="str">
-        <v>바우처 목록</v>
+        <v/>
       </c>
       <c r="D166" t="str">
-        <v>VC-01</v>
+        <v/>
       </c>
       <c r="E166" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F166" t="str">
-        <v>사용 예정</v>
+        <v>예약 내역 바로가기</v>
       </c>
       <c r="G166" t="str">
-        <v>'바우처 목록' 화면에서 사용 예정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '예약 확정 대기' 화면이 나오게 한 뒤, 예약 내역 바로가기가 보이는지 확인한다.</v>
       </c>
       <c r="H166" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I166" t="str">
         <v/>
@@ -6130,28 +6130,28 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B167" t="str">
-        <v/>
+        <v>예약·결제</v>
       </c>
       <c r="C167" t="str">
-        <v/>
+        <v>최소 인원 미달 안내</v>
       </c>
       <c r="D167" t="str">
-        <v/>
+        <v>BK-06</v>
       </c>
       <c r="E167" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F167" t="str">
-        <v>사용 완료</v>
+        <v>출발 확정 인원과 현재 인원 표시</v>
       </c>
       <c r="G167" t="str">
-        <v>'바우처 목록' 화면에서 사용 완료가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '최소 인원 미달 안내' 화면이 나오게 한 뒤, 출발 확정 인원과 현재 인원 표시가 보이는지 확인한다.</v>
       </c>
       <c r="H167" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I167" t="str">
         <v/>
@@ -6162,7 +6162,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B168" t="str">
         <v/>
@@ -6177,13 +6177,13 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>만료 탭</v>
+        <v>확정 마감 시각 안내</v>
       </c>
       <c r="G168" t="str">
-        <v>'바우처 목록'에서 만료 탭의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>일부러 그 상황을 만들어 '최소 인원 미달 안내' 화면이 나오게 한 뒤, 확정 마감 시각 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H168" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I168" t="str">
         <v/>
@@ -6194,7 +6194,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B169" t="str">
         <v/>
@@ -6209,13 +6209,13 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>바우처 카드(상품명·사용일·QR 미리보기·상태 배지)</v>
+        <v>미달 시 전액 환불 안내</v>
       </c>
       <c r="G169" t="str">
-        <v>'바우처 목록'의 바우처 카드(상품명·사용일·QR 미리보기·상태 배지)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '최소 인원 미달 안내' 화면이 나오게 한 뒤, 미달 시 전액 환불 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H169" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I169" t="str">
         <v/>
@@ -6226,7 +6226,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B170" t="str">
         <v/>
@@ -6241,13 +6241,13 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>오프라인 저장 안내</v>
+        <v>대체 상품 추천</v>
       </c>
       <c r="G170" t="str">
-        <v>'바우처 목록' 화면에서 오프라인 저장 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '최소 인원 미달 안내' 화면이 나오게 한 뒤, 대체 상품 추천이 보이는지 확인한다.</v>
       </c>
       <c r="H170" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I170" t="str">
         <v/>
@@ -6258,7 +6258,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B171" t="str">
         <v/>
@@ -6273,13 +6273,13 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>인쇄</v>
+        <v>친구 초대 공유</v>
       </c>
       <c r="G171" t="str">
-        <v>'바우처 목록' 화면에서 인쇄가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '최소 인원 미달 안내' 화면이 나오게 한 뒤, 친구 초대 공유가 보이는지 확인한다.</v>
       </c>
       <c r="H171" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I171" t="str">
         <v/>
@@ -6293,25 +6293,25 @@
         <v>SCN-022</v>
       </c>
       <c r="B172" t="str">
-        <v/>
+        <v>바우처</v>
       </c>
       <c r="C172" t="str">
-        <v/>
+        <v>바우처 목록</v>
       </c>
       <c r="D172" t="str">
-        <v/>
+        <v>VC-01</v>
       </c>
       <c r="E172" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F172" t="str">
-        <v>이미지 저장 버튼</v>
+        <v>사용 예정</v>
       </c>
       <c r="G172" t="str">
-        <v>'바우처 목록'에서 이미지 저장 버튼을 눌러 본다.</v>
+        <v>'바우처 목록' 화면에서 사용 예정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H172" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I172" t="str">
         <v/>
@@ -6322,25 +6322,25 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B173" t="str">
-        <v>바우처</v>
+        <v/>
       </c>
       <c r="C173" t="str">
-        <v>바우처 상세</v>
+        <v/>
       </c>
       <c r="D173" t="str">
-        <v>VC-02</v>
+        <v/>
       </c>
       <c r="E173" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F173" t="str">
-        <v>큰 QR 코드와 예약번호</v>
+        <v>사용 완료</v>
       </c>
       <c r="G173" t="str">
-        <v>'바우처 상세' 화면에서 큰 QR 코드와 예약번호가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'바우처 목록' 화면에서 사용 완료가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H173" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6354,7 +6354,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B174" t="str">
         <v/>
@@ -6369,13 +6369,13 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>상품명과 이용 일시</v>
+        <v>만료 탭</v>
       </c>
       <c r="G174" t="str">
-        <v>'바우처 상세' 화면에서 상품명과 이용 일시가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'바우처 목록'에서 만료 탭의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H174" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I174" t="str">
         <v/>
@@ -6386,7 +6386,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B175" t="str">
         <v/>
@@ -6401,13 +6401,13 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>미팅 장소 지도와 길찾기</v>
+        <v>바우처 카드(상품명·사용일·QR 미리보기·상태 배지)</v>
       </c>
       <c r="G175" t="str">
-        <v>'바우처 상세' 화면에서 미팅 장소 지도와 길찾기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'바우처 목록'의 바우처 카드(상품명·사용일·QR 미리보기·상태 배지)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H175" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I175" t="str">
         <v/>
@@ -6418,7 +6418,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B176" t="str">
         <v/>
@@ -6433,10 +6433,10 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>현지 연락처</v>
+        <v>오프라인 저장 안내</v>
       </c>
       <c r="G176" t="str">
-        <v>'바우처 상세' 화면에서 현지 연락처가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'바우처 목록' 화면에서 오프라인 저장 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H176" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6450,7 +6450,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B177" t="str">
         <v/>
@@ -6465,10 +6465,10 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>이용 안내와 주의사항</v>
+        <v>인쇄</v>
       </c>
       <c r="G177" t="str">
-        <v>'바우처 상세' 화면에서 이용 안내와 주의사항이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'바우처 목록' 화면에서 인쇄가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H177" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6482,7 +6482,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B178" t="str">
         <v/>
@@ -6497,13 +6497,13 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>화면 밝기 자동 최대 안내</v>
+        <v>이미지 저장 버튼</v>
       </c>
       <c r="G178" t="str">
-        <v>'바우처 상세' 화면에서 화면 밝기 자동 최대 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'바우처 목록'에서 이미지 저장 버튼을 눌러 본다.</v>
       </c>
       <c r="H178" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I178" t="str">
         <v/>
@@ -6517,22 +6517,22 @@
         <v>SCN-023</v>
       </c>
       <c r="B179" t="str">
-        <v/>
+        <v>바우처</v>
       </c>
       <c r="C179" t="str">
-        <v/>
+        <v>바우처 상세</v>
       </c>
       <c r="D179" t="str">
-        <v/>
+        <v>VC-02</v>
       </c>
       <c r="E179" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F179" t="str">
-        <v>저장</v>
+        <v>큰 QR 코드와 예약번호</v>
       </c>
       <c r="G179" t="str">
-        <v>'바우처 상세' 화면에서 저장이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'바우처 상세' 화면에서 큰 QR 코드와 예약번호가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H179" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6561,10 +6561,10 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>인쇄</v>
+        <v>상품명과 이용 일시</v>
       </c>
       <c r="G180" t="str">
-        <v>'바우처 상세' 화면에서 인쇄가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'바우처 상세' 화면에서 상품명과 이용 일시가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H180" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6578,28 +6578,28 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B181" t="str">
-        <v>바우처</v>
+        <v/>
       </c>
       <c r="C181" t="str">
-        <v>바우처 만료</v>
+        <v/>
       </c>
       <c r="D181" t="str">
-        <v>VC-03</v>
+        <v/>
       </c>
       <c r="E181" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F181" t="str">
-        <v>만료 안내와 만료일 표시</v>
+        <v>미팅 장소 지도와 길찾기</v>
       </c>
       <c r="G181" t="str">
-        <v>일부러 그 상황을 만들어 '바우처 만료' 화면이 나오게 한 뒤, 만료 안내와 만료일 표시가 보이는지 확인한다.</v>
+        <v>'바우처 상세' 화면에서 미팅 장소 지도와 길찾기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H181" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I181" t="str">
         <v/>
@@ -6610,7 +6610,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B182" t="str">
         <v/>
@@ -6625,13 +6625,13 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>만료 사유 설명</v>
+        <v>현지 연락처</v>
       </c>
       <c r="G182" t="str">
-        <v>일부러 그 상황을 만들어 '바우처 만료' 화면이 나오게 한 뒤, 만료 사유 설명이 보이는지 확인한다.</v>
+        <v>'바우처 상세' 화면에서 현지 연락처가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H182" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I182" t="str">
         <v/>
@@ -6642,7 +6642,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B183" t="str">
         <v/>
@@ -6657,13 +6657,13 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>재발급 가능 여부 안내</v>
+        <v>이용 안내와 주의사항</v>
       </c>
       <c r="G183" t="str">
-        <v>일부러 그 상황을 만들어 '바우처 만료' 화면이 나오게 한 뒤, 재발급 가능 여부 안내가 보이는지 확인한다.</v>
+        <v>'바우처 상세' 화면에서 이용 안내와 주의사항이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H183" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I183" t="str">
         <v/>
@@ -6674,7 +6674,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B184" t="str">
         <v/>
@@ -6689,13 +6689,13 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>고객센터 문의 버튼</v>
+        <v>화면 밝기 자동 최대 안내</v>
       </c>
       <c r="G184" t="str">
-        <v>일부러 그 상황을 만들어 '바우처 만료' 화면이 나오게 한 뒤, 고객센터 문의 버튼이 보이는지 확인한다.</v>
+        <v>'바우처 상세' 화면에서 화면 밝기 자동 최대 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H184" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I184" t="str">
         <v/>
@@ -6706,7 +6706,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B185" t="str">
         <v/>
@@ -6721,13 +6721,13 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>같은 상품 다시 예약</v>
+        <v>저장</v>
       </c>
       <c r="G185" t="str">
-        <v>일부러 그 상황을 만들어 '바우처 만료' 화면이 나오게 한 뒤, 같은 상품 다시 예약이 보이는지 확인한다.</v>
+        <v>'바우처 상세' 화면에서 저장이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H185" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I185" t="str">
         <v/>
@@ -6738,25 +6738,25 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>SCN-025</v>
+        <v>SCN-023</v>
       </c>
       <c r="B186" t="str">
-        <v>바우처</v>
+        <v/>
       </c>
       <c r="C186" t="str">
-        <v>바우처 재발급 요청</v>
+        <v/>
       </c>
       <c r="D186" t="str">
-        <v>VC-04</v>
+        <v/>
       </c>
       <c r="E186" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F186" t="str">
-        <v>재발급 사유 선택</v>
+        <v>인쇄</v>
       </c>
       <c r="G186" t="str">
-        <v>'바우처 재발급 요청' 화면에서 재발급 사유 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'바우처 상세' 화면에서 인쇄가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H186" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6770,28 +6770,28 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>SCN-025</v>
+        <v>SCN-024</v>
       </c>
       <c r="B187" t="str">
-        <v/>
+        <v>바우처</v>
       </c>
       <c r="C187" t="str">
-        <v/>
+        <v>바우처 만료</v>
       </c>
       <c r="D187" t="str">
-        <v/>
+        <v>VC-03</v>
       </c>
       <c r="E187" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F187" t="str">
-        <v>예약번호 확인</v>
+        <v>만료 안내와 만료일 표시</v>
       </c>
       <c r="G187" t="str">
-        <v>'바우처 재발급 요청' 화면에서 예약번호 확인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '바우처 만료' 화면이 나오게 한 뒤, 만료 안내와 만료일 표시가 보이는지 확인한다.</v>
       </c>
       <c r="H187" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I187" t="str">
         <v/>
@@ -6802,7 +6802,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>SCN-025</v>
+        <v>SCN-024</v>
       </c>
       <c r="B188" t="str">
         <v/>
@@ -6817,13 +6817,13 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>받을 이메일 입력</v>
+        <v>만료 사유 설명</v>
       </c>
       <c r="G188" t="str">
-        <v>'바우처 재발급 요청'의 받을 이메일 입력에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>일부러 그 상황을 만들어 '바우처 만료' 화면이 나오게 한 뒤, 만료 사유 설명이 보이는지 확인한다.</v>
       </c>
       <c r="H188" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I188" t="str">
         <v/>
@@ -6834,7 +6834,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>SCN-025</v>
+        <v>SCN-024</v>
       </c>
       <c r="B189" t="str">
         <v/>
@@ -6849,13 +6849,13 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>처리 소요시간 안내</v>
+        <v>재발급 가능 여부 안내</v>
       </c>
       <c r="G189" t="str">
-        <v>'바우처 재발급 요청' 화면에서 처리 소요시간 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '바우처 만료' 화면이 나오게 한 뒤, 재발급 가능 여부 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H189" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I189" t="str">
         <v/>
@@ -6866,7 +6866,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>SCN-025</v>
+        <v>SCN-024</v>
       </c>
       <c r="B190" t="str">
         <v/>
@@ -6881,13 +6881,13 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>요청 완료 안내</v>
+        <v>고객센터 문의 버튼</v>
       </c>
       <c r="G190" t="str">
-        <v>'바우처 재발급 요청' 화면에서 요청 완료 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '바우처 만료' 화면이 나오게 한 뒤, 고객센터 문의 버튼이 보이는지 확인한다.</v>
       </c>
       <c r="H190" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I190" t="str">
         <v/>
@@ -6898,28 +6898,28 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>SCN-026</v>
+        <v>SCN-024</v>
       </c>
       <c r="B191" t="str">
-        <v>마이페이지</v>
+        <v/>
       </c>
       <c r="C191" t="str">
-        <v>로그인</v>
+        <v/>
       </c>
       <c r="D191" t="str">
-        <v>MY-01</v>
+        <v/>
       </c>
       <c r="E191" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F191" t="str">
-        <v>이메일</v>
+        <v>같은 상품 다시 예약</v>
       </c>
       <c r="G191" t="str">
-        <v>'로그인' 화면에서 이메일이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '바우처 만료' 화면이 나오게 한 뒤, 같은 상품 다시 예약이 보이는지 확인한다.</v>
       </c>
       <c r="H191" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I191" t="str">
         <v/>
@@ -6930,28 +6930,28 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B192" t="str">
-        <v/>
+        <v>바우처</v>
       </c>
       <c r="C192" t="str">
-        <v/>
+        <v>바우처 재발급 요청</v>
       </c>
       <c r="D192" t="str">
-        <v/>
+        <v>VC-04</v>
       </c>
       <c r="E192" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F192" t="str">
-        <v>비밀번호 입력</v>
+        <v>재발급 사유 선택</v>
       </c>
       <c r="G192" t="str">
-        <v>'로그인'의 비밀번호 입력에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'바우처 재발급 요청' 화면에서 재발급 사유 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H192" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I192" t="str">
         <v/>
@@ -6962,7 +6962,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B193" t="str">
         <v/>
@@ -6977,13 +6977,13 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>소셜 로그인(카카오·구글·애플)</v>
+        <v>예약번호 확인</v>
       </c>
       <c r="G193" t="str">
-        <v>'로그인'에서 소셜 로그인(카카오·구글·애플)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'바우처 재발급 요청' 화면에서 예약번호 확인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H193" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I193" t="str">
         <v/>
@@ -6994,7 +6994,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B194" t="str">
         <v/>
@@ -7009,13 +7009,13 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>자동 로그인</v>
+        <v>받을 이메일 입력</v>
       </c>
       <c r="G194" t="str">
-        <v>'로그인'에서 자동 로그인을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'바우처 재발급 요청'의 받을 이메일 입력에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H194" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I194" t="str">
         <v/>
@@ -7026,7 +7026,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B195" t="str">
         <v/>
@@ -7041,10 +7041,10 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>비밀번호 찾기</v>
+        <v>처리 소요시간 안내</v>
       </c>
       <c r="G195" t="str">
-        <v>'로그인' 화면에서 비밀번호 찾기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'바우처 재발급 요청' 화면에서 처리 소요시간 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H195" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7058,7 +7058,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B196" t="str">
         <v/>
@@ -7073,13 +7073,13 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>비회원 예약 조회 링크</v>
+        <v>요청 완료 안내</v>
       </c>
       <c r="G196" t="str">
-        <v>'로그인'에서 비회원 예약 조회 링크를 눌러 본다.</v>
+        <v>'바우처 재발급 요청' 화면에서 요청 완료 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H196" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I196" t="str">
         <v/>
@@ -7090,16 +7090,16 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B197" t="str">
         <v>마이페이지</v>
       </c>
       <c r="C197" t="str">
-        <v>회원가입</v>
+        <v>로그인</v>
       </c>
       <c r="D197" t="str">
-        <v>MY-02</v>
+        <v>MY-01</v>
       </c>
       <c r="E197" t="str">
         <v>기본</v>
@@ -7108,7 +7108,7 @@
         <v>이메일</v>
       </c>
       <c r="G197" t="str">
-        <v>'회원가입' 화면에서 이메일이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'로그인' 화면에서 이메일이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H197" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7122,7 +7122,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B198" t="str">
         <v/>
@@ -7137,13 +7137,13 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>비밀번호</v>
+        <v>비밀번호 입력</v>
       </c>
       <c r="G198" t="str">
-        <v>'회원가입' 화면에서 비밀번호가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'로그인'의 비밀번호 입력에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H198" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I198" t="str">
         <v/>
@@ -7154,7 +7154,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B199" t="str">
         <v/>
@@ -7169,13 +7169,13 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>이름</v>
+        <v>소셜 로그인(카카오·구글·애플)</v>
       </c>
       <c r="G199" t="str">
-        <v>'회원가입' 화면에서 이름이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'로그인'에서 소셜 로그인(카카오·구글·애플)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H199" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I199" t="str">
         <v/>
@@ -7186,7 +7186,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B200" t="str">
         <v/>
@@ -7201,13 +7201,13 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>영문명 입력</v>
+        <v>자동 로그인</v>
       </c>
       <c r="G200" t="str">
-        <v>'회원가입'의 영문명 입력에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'로그인'에서 자동 로그인을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H200" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I200" t="str">
         <v/>
@@ -7218,7 +7218,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B201" t="str">
         <v/>
@@ -7233,13 +7233,13 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>비밀번호 조건 실시간 표시</v>
+        <v>비밀번호 찾기</v>
       </c>
       <c r="G201" t="str">
-        <v>'회원가입'의 비밀번호 조건 실시간 표시가 실제 데이터와 같은지 대조한다.</v>
+        <v>'로그인' 화면에서 비밀번호 찾기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H201" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I201" t="str">
         <v/>
@@ -7250,7 +7250,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B202" t="str">
         <v/>
@@ -7265,13 +7265,13 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>약관 동의(필수·선택 구분)</v>
+        <v>비회원 예약 조회 링크</v>
       </c>
       <c r="G202" t="str">
-        <v>'회원가입' 화면에서 약관 동의(필수·선택 구분)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'로그인'에서 비회원 예약 조회 링크를 눌러 본다.</v>
       </c>
       <c r="H202" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I202" t="str">
         <v/>
@@ -7285,22 +7285,22 @@
         <v>SCN-027</v>
       </c>
       <c r="B203" t="str">
-        <v/>
+        <v>마이페이지</v>
       </c>
       <c r="C203" t="str">
-        <v/>
+        <v>회원가입</v>
       </c>
       <c r="D203" t="str">
-        <v/>
+        <v>MY-02</v>
       </c>
       <c r="E203" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F203" t="str">
-        <v>마케팅 수신 동의</v>
+        <v>이메일</v>
       </c>
       <c r="G203" t="str">
-        <v>'회원가입' 화면에서 마케팅 수신 동의가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'회원가입' 화면에서 이메일이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H203" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7329,10 +7329,10 @@
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>가입 혜택 안내</v>
+        <v>비밀번호</v>
       </c>
       <c r="G204" t="str">
-        <v>'회원가입' 화면에서 가입 혜택 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'회원가입' 화면에서 비밀번호가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H204" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7346,28 +7346,28 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B205" t="str">
-        <v>마이페이지</v>
+        <v/>
       </c>
       <c r="C205" t="str">
-        <v>예약 내역</v>
+        <v/>
       </c>
       <c r="D205" t="str">
-        <v>MY-03</v>
+        <v/>
       </c>
       <c r="E205" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F205" t="str">
-        <v>상태 탭(예정·완료·취소)</v>
+        <v>이름</v>
       </c>
       <c r="G205" t="str">
-        <v>'예약 내역'에서 상태 탭(예정·완료·취소)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'회원가입' 화면에서 이름이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H205" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I205" t="str">
         <v/>
@@ -7378,7 +7378,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B206" t="str">
         <v/>
@@ -7393,13 +7393,13 @@
         <v/>
       </c>
       <c r="F206" t="str">
-        <v>예약 카드(상품명·날짜·인원·상태 배지·금액)</v>
+        <v>영문명 입력</v>
       </c>
       <c r="G206" t="str">
-        <v>'예약 내역'의 예약 카드(상품명·날짜·인원·상태 배지·금액)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'회원가입'의 영문명 입력에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H206" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I206" t="str">
         <v/>
@@ -7410,7 +7410,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B207" t="str">
         <v/>
@@ -7425,10 +7425,10 @@
         <v/>
       </c>
       <c r="F207" t="str">
-        <v>D-day 표시</v>
+        <v>비밀번호 조건 실시간 표시</v>
       </c>
       <c r="G207" t="str">
-        <v>'예약 내역'의 D-day 표시가 실제 데이터와 같은지 대조한다.</v>
+        <v>'회원가입'의 비밀번호 조건 실시간 표시가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H207" t="str">
         <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
@@ -7442,7 +7442,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B208" t="str">
         <v/>
@@ -7457,13 +7457,13 @@
         <v/>
       </c>
       <c r="F208" t="str">
-        <v>바우처 바로가기</v>
+        <v>약관 동의(필수·선택 구분)</v>
       </c>
       <c r="G208" t="str">
-        <v>'예약 내역'에서 바우처 바로가기를 눌러 본다.</v>
+        <v>'회원가입' 화면에서 약관 동의(필수·선택 구분)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H208" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I208" t="str">
         <v/>
@@ -7474,7 +7474,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B209" t="str">
         <v/>
@@ -7489,10 +7489,10 @@
         <v/>
       </c>
       <c r="F209" t="str">
-        <v>후기 쓰기 유도</v>
+        <v>마케팅 수신 동의</v>
       </c>
       <c r="G209" t="str">
-        <v>'예약 내역' 화면에서 후기 쓰기 유도가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'회원가입' 화면에서 마케팅 수신 동의가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H209" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7506,28 +7506,28 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>SCN-029</v>
+        <v>SCN-027</v>
       </c>
       <c r="B210" t="str">
-        <v>마이페이지</v>
+        <v/>
       </c>
       <c r="C210" t="str">
-        <v>예약 내역 없음</v>
+        <v/>
       </c>
       <c r="D210" t="str">
-        <v>MY-04</v>
+        <v/>
       </c>
       <c r="E210" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F210" t="str">
-        <v>빈 상태 일러스트와 안내</v>
+        <v>가입 혜택 안내</v>
       </c>
       <c r="G210" t="str">
-        <v>일부러 그 상황을 만들어 '예약 내역 없음' 화면이 나오게 한 뒤, 빈 상태 일러스트와 안내가 보이는지 확인한다.</v>
+        <v>'회원가입' 화면에서 가입 혜택 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H210" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I210" t="str">
         <v/>
@@ -7538,28 +7538,28 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>SCN-029</v>
+        <v>SCN-028</v>
       </c>
       <c r="B211" t="str">
-        <v/>
+        <v>마이페이지</v>
       </c>
       <c r="C211" t="str">
-        <v/>
+        <v>예약 내역</v>
       </c>
       <c r="D211" t="str">
-        <v/>
+        <v>MY-03</v>
       </c>
       <c r="E211" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F211" t="str">
-        <v>인기 여행지 바로가기</v>
+        <v>상태 탭(예정·완료·취소)</v>
       </c>
       <c r="G211" t="str">
-        <v>일부러 그 상황을 만들어 '예약 내역 없음' 화면이 나오게 한 뒤, 인기 여행지 바로가기가 보이는지 확인한다.</v>
+        <v>'예약 내역'에서 상태 탭(예정·완료·취소)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H211" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I211" t="str">
         <v/>
@@ -7570,7 +7570,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>SCN-029</v>
+        <v>SCN-028</v>
       </c>
       <c r="B212" t="str">
         <v/>
@@ -7585,13 +7585,13 @@
         <v/>
       </c>
       <c r="F212" t="str">
-        <v>첫 예약 쿠폰 안내</v>
+        <v>예약 카드(상품명·날짜·인원·상태 배지·금액)</v>
       </c>
       <c r="G212" t="str">
-        <v>일부러 그 상황을 만들어 '예약 내역 없음' 화면이 나오게 한 뒤, 첫 예약 쿠폰 안내가 보이는지 확인한다.</v>
+        <v>'예약 내역'의 예약 카드(상품명·날짜·인원·상태 배지·금액)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H212" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I212" t="str">
         <v/>
@@ -7602,25 +7602,25 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>SCN-030</v>
+        <v>SCN-028</v>
       </c>
       <c r="B213" t="str">
-        <v>마이페이지</v>
+        <v/>
       </c>
       <c r="C213" t="str">
-        <v>예약 상세</v>
+        <v/>
       </c>
       <c r="D213" t="str">
-        <v>MY-05</v>
+        <v/>
       </c>
       <c r="E213" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F213" t="str">
-        <v>예약번호와 상태</v>
+        <v>D-day 표시</v>
       </c>
       <c r="G213" t="str">
-        <v>'예약 상세'의 예약번호와 상태가 실제 데이터와 같은지 대조한다.</v>
+        <v>'예약 내역'의 D-day 표시가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H213" t="str">
         <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
@@ -7634,7 +7634,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>SCN-030</v>
+        <v>SCN-028</v>
       </c>
       <c r="B214" t="str">
         <v/>
@@ -7649,13 +7649,13 @@
         <v/>
       </c>
       <c r="F214" t="str">
-        <v>상품</v>
+        <v>바우처 바로가기</v>
       </c>
       <c r="G214" t="str">
-        <v>'예약 상세' 화면에서 상품이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'예약 내역'에서 바우처 바로가기를 눌러 본다.</v>
       </c>
       <c r="H214" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I214" t="str">
         <v/>
@@ -7666,7 +7666,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>SCN-030</v>
+        <v>SCN-028</v>
       </c>
       <c r="B215" t="str">
         <v/>
@@ -7681,13 +7681,13 @@
         <v/>
       </c>
       <c r="F215" t="str">
-        <v>일정 정보</v>
+        <v>후기 쓰기 유도</v>
       </c>
       <c r="G215" t="str">
-        <v>'예약 상세'의 일정 정보가 실제 데이터와 같은지 대조한다.</v>
+        <v>'예약 내역' 화면에서 후기 쓰기 유도가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H215" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I215" t="str">
         <v/>
@@ -7698,28 +7698,28 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>SCN-030</v>
+        <v>SCN-029</v>
       </c>
       <c r="B216" t="str">
-        <v/>
+        <v>마이페이지</v>
       </c>
       <c r="C216" t="str">
-        <v/>
+        <v>예약 내역 없음</v>
       </c>
       <c r="D216" t="str">
-        <v/>
+        <v>MY-04</v>
       </c>
       <c r="E216" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F216" t="str">
-        <v>여행자 명단</v>
+        <v>빈 상태 일러스트와 안내</v>
       </c>
       <c r="G216" t="str">
-        <v>'예약 상세' 화면에서 여행자 명단이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '예약 내역 없음' 화면이 나오게 한 뒤, 빈 상태 일러스트와 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H216" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I216" t="str">
         <v/>
@@ -7730,7 +7730,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>SCN-030</v>
+        <v>SCN-029</v>
       </c>
       <c r="B217" t="str">
         <v/>
@@ -7745,13 +7745,13 @@
         <v/>
       </c>
       <c r="F217" t="str">
-        <v>결제 내역(금액·수단·영수증)</v>
+        <v>인기 여행지 바로가기</v>
       </c>
       <c r="G217" t="str">
-        <v>'예약 상세'에서 결제 내역(금액·수단·영수증)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>일부러 그 상황을 만들어 '예약 내역 없음' 화면이 나오게 한 뒤, 인기 여행지 바로가기가 보이는지 확인한다.</v>
       </c>
       <c r="H217" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I217" t="str">
         <v/>
@@ -7762,7 +7762,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>SCN-030</v>
+        <v>SCN-029</v>
       </c>
       <c r="B218" t="str">
         <v/>
@@ -7777,13 +7777,13 @@
         <v/>
       </c>
       <c r="F218" t="str">
-        <v>미팅 장소</v>
+        <v>첫 예약 쿠폰 안내</v>
       </c>
       <c r="G218" t="str">
-        <v>'예약 상세' 화면에서 미팅 장소가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '예약 내역 없음' 화면이 나오게 한 뒤, 첫 예약 쿠폰 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H218" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I218" t="str">
         <v/>
@@ -7797,25 +7797,25 @@
         <v>SCN-030</v>
       </c>
       <c r="B219" t="str">
-        <v/>
+        <v>마이페이지</v>
       </c>
       <c r="C219" t="str">
-        <v/>
+        <v>예약 상세</v>
       </c>
       <c r="D219" t="str">
-        <v/>
+        <v>MY-05</v>
       </c>
       <c r="E219" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F219" t="str">
-        <v>취소</v>
+        <v>예약번호와 상태</v>
       </c>
       <c r="G219" t="str">
-        <v>'예약 상세'에서 취소를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'예약 상세'의 예약번호와 상태가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H219" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I219" t="str">
         <v/>
@@ -7841,13 +7841,13 @@
         <v/>
       </c>
       <c r="F220" t="str">
-        <v>환불 규정 요약</v>
+        <v>상품</v>
       </c>
       <c r="G220" t="str">
-        <v>'예약 상세'에서 환불 규정 요약을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'예약 상세' 화면에서 상품이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H220" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I220" t="str">
         <v/>
@@ -7873,13 +7873,13 @@
         <v/>
       </c>
       <c r="F221" t="str">
-        <v>취소하기</v>
+        <v>일정 정보</v>
       </c>
       <c r="G221" t="str">
-        <v>'예약 상세'에서 취소하기를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'예약 상세'의 일정 정보가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H221" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I221" t="str">
         <v/>
@@ -7905,13 +7905,13 @@
         <v/>
       </c>
       <c r="F222" t="str">
-        <v>문의하기 버튼</v>
+        <v>여행자 명단</v>
       </c>
       <c r="G222" t="str">
-        <v>'예약 상세'에서 문의하기 버튼을 눌러 본다.</v>
+        <v>'예약 상세' 화면에서 여행자 명단이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H222" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I222" t="str">
         <v/>
@@ -7922,25 +7922,25 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B223" t="str">
-        <v>마이페이지</v>
+        <v/>
       </c>
       <c r="C223" t="str">
-        <v>예약 취소 신청</v>
+        <v/>
       </c>
       <c r="D223" t="str">
-        <v>MY-06</v>
+        <v/>
       </c>
       <c r="E223" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F223" t="str">
-        <v>출발일 기준 환불 수수료 자동 계산</v>
+        <v>결제 내역(금액·수단·영수증)</v>
       </c>
       <c r="G223" t="str">
-        <v>'예약 취소 신청'에서 출발일 기준 환불 수수료 자동 계산을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'예약 상세'에서 결제 내역(금액·수단·영수증)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H223" t="str">
         <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
@@ -7954,7 +7954,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B224" t="str">
         <v/>
@@ -7969,13 +7969,13 @@
         <v/>
       </c>
       <c r="F224" t="str">
-        <v>환불 예정 금액 표시</v>
+        <v>미팅 장소</v>
       </c>
       <c r="G224" t="str">
-        <v>'예약 취소 신청'에서 환불 예정 금액 표시를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'예약 상세' 화면에서 미팅 장소가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H224" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I224" t="str">
         <v/>
@@ -7986,7 +7986,7 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B225" t="str">
         <v/>
@@ -8001,10 +8001,10 @@
         <v/>
       </c>
       <c r="F225" t="str">
-        <v>취소 사유 선택</v>
+        <v>취소</v>
       </c>
       <c r="G225" t="str">
-        <v>'예약 취소 신청'에서 취소 사유 선택을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'예약 상세'에서 취소를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H225" t="str">
         <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
@@ -8018,7 +8018,7 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B226" t="str">
         <v/>
@@ -8033,10 +8033,10 @@
         <v/>
       </c>
       <c r="F226" t="str">
-        <v>환불 계좌</v>
+        <v>환불 규정 요약</v>
       </c>
       <c r="G226" t="str">
-        <v>'예약 취소 신청'에서 환불 계좌를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'예약 상세'에서 환불 규정 요약을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H226" t="str">
         <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
@@ -8050,7 +8050,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B227" t="str">
         <v/>
@@ -8065,13 +8065,13 @@
         <v/>
       </c>
       <c r="F227" t="str">
-        <v>수단 확인</v>
+        <v>취소하기</v>
       </c>
       <c r="G227" t="str">
-        <v>'예약 취소 신청' 화면에서 수단 확인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'예약 상세'에서 취소하기를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H227" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I227" t="str">
         <v/>
@@ -8082,7 +8082,7 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B228" t="str">
         <v/>
@@ -8097,13 +8097,13 @@
         <v/>
       </c>
       <c r="F228" t="str">
-        <v>취소 확인 재확인</v>
+        <v>문의하기 버튼</v>
       </c>
       <c r="G228" t="str">
-        <v>'예약 취소 신청'에서 취소 확인 재확인을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'예약 상세'에서 문의하기 버튼을 눌러 본다.</v>
       </c>
       <c r="H228" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I228" t="str">
         <v/>
@@ -8114,28 +8114,28 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>SCN-032</v>
+        <v>SCN-031</v>
       </c>
       <c r="B229" t="str">
         <v>마이페이지</v>
       </c>
       <c r="C229" t="str">
-        <v>취소 불가 안내</v>
+        <v>예약 취소 신청</v>
       </c>
       <c r="D229" t="str">
-        <v>MY-07</v>
+        <v>MY-06</v>
       </c>
       <c r="E229" t="str">
-        <v>예외·상태</v>
+        <v>기본</v>
       </c>
       <c r="F229" t="str">
-        <v>취소 불가 사유와 기준일 안내</v>
+        <v>출발일 기준 환불 수수료 자동 계산</v>
       </c>
       <c r="G229" t="str">
-        <v>일부러 그 상황을 만들어 '취소 불가 안내' 화면이 나오게 한 뒤, 취소 불가 사유와 기준일 안내가 보이는지 확인한다.</v>
+        <v>'예약 취소 신청'에서 출발일 기준 환불 수수료 자동 계산을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H229" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I229" t="str">
         <v/>
@@ -8146,7 +8146,7 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>SCN-032</v>
+        <v>SCN-031</v>
       </c>
       <c r="B230" t="str">
         <v/>
@@ -8161,13 +8161,13 @@
         <v/>
       </c>
       <c r="F230" t="str">
-        <v>규정 원문 표시</v>
+        <v>환불 예정 금액 표시</v>
       </c>
       <c r="G230" t="str">
-        <v>일부러 그 상황을 만들어 '취소 불가 안내' 화면이 나오게 한 뒤, 규정 원문 표시가 보이는지 확인한다.</v>
+        <v>'예약 취소 신청'에서 환불 예정 금액 표시를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H230" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I230" t="str">
         <v/>
@@ -8178,7 +8178,7 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>SCN-032</v>
+        <v>SCN-031</v>
       </c>
       <c r="B231" t="str">
         <v/>
@@ -8193,13 +8193,13 @@
         <v/>
       </c>
       <c r="F231" t="str">
-        <v>예외 요청 안내</v>
+        <v>취소 사유 선택</v>
       </c>
       <c r="G231" t="str">
-        <v>일부러 그 상황을 만들어 '취소 불가 안내' 화면이 나오게 한 뒤, 예외 요청 안내가 보이는지 확인한다.</v>
+        <v>'예약 취소 신청'에서 취소 사유 선택을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H231" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I231" t="str">
         <v/>
@@ -8210,7 +8210,7 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>SCN-032</v>
+        <v>SCN-031</v>
       </c>
       <c r="B232" t="str">
         <v/>
@@ -8225,13 +8225,13 @@
         <v/>
       </c>
       <c r="F232" t="str">
-        <v>고객센터 연결</v>
+        <v>환불 계좌</v>
       </c>
       <c r="G232" t="str">
-        <v>일부러 그 상황을 만들어 '취소 불가 안내' 화면이 나오게 한 뒤, 고객센터 연결이 보이는지 확인한다.</v>
+        <v>'예약 취소 신청'에서 환불 계좌를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H232" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I232" t="str">
         <v/>
@@ -8242,25 +8242,25 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>SCN-033</v>
+        <v>SCN-031</v>
       </c>
       <c r="B233" t="str">
-        <v>마이페이지</v>
+        <v/>
       </c>
       <c r="C233" t="str">
-        <v>후기 작성</v>
+        <v/>
       </c>
       <c r="D233" t="str">
-        <v>MY-08</v>
+        <v/>
       </c>
       <c r="E233" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F233" t="str">
-        <v>별점 선택</v>
+        <v>수단 확인</v>
       </c>
       <c r="G233" t="str">
-        <v>'후기 작성' 화면에서 별점 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'예약 취소 신청' 화면에서 수단 확인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H233" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8274,7 +8274,7 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>SCN-033</v>
+        <v>SCN-031</v>
       </c>
       <c r="B234" t="str">
         <v/>
@@ -8289,13 +8289,13 @@
         <v/>
       </c>
       <c r="F234" t="str">
-        <v>세부 항목 평가(가이드·일정·가격만족도)</v>
+        <v>취소 확인 재확인</v>
       </c>
       <c r="G234" t="str">
-        <v>'후기 작성' 화면에서 세부 항목 평가(가이드·일정·가격만족도)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'예약 취소 신청'에서 취소 확인 재확인을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H234" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I234" t="str">
         <v/>
@@ -8306,28 +8306,28 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>SCN-033</v>
+        <v>SCN-032</v>
       </c>
       <c r="B235" t="str">
-        <v/>
+        <v>마이페이지</v>
       </c>
       <c r="C235" t="str">
-        <v/>
+        <v>취소 불가 안내</v>
       </c>
       <c r="D235" t="str">
-        <v/>
+        <v>MY-07</v>
       </c>
       <c r="E235" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F235" t="str">
-        <v>본문 입력(글자수 안내)</v>
+        <v>취소 불가 사유와 기준일 안내</v>
       </c>
       <c r="G235" t="str">
-        <v>'후기 작성'의 본문 입력(글자수 안내)에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>일부러 그 상황을 만들어 '취소 불가 안내' 화면이 나오게 한 뒤, 취소 불가 사유와 기준일 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H235" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I235" t="str">
         <v/>
@@ -8338,7 +8338,7 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>SCN-033</v>
+        <v>SCN-032</v>
       </c>
       <c r="B236" t="str">
         <v/>
@@ -8353,13 +8353,13 @@
         <v/>
       </c>
       <c r="F236" t="str">
-        <v>사진 첨부 최대 5장</v>
+        <v>규정 원문 표시</v>
       </c>
       <c r="G236" t="str">
-        <v>'후기 작성' 화면을 열고 사진 첨부 최대 5장이 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>일부러 그 상황을 만들어 '취소 불가 안내' 화면이 나오게 한 뒤, 규정 원문 표시가 보이는지 확인한다.</v>
       </c>
       <c r="H236" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I236" t="str">
         <v/>
@@ -8370,7 +8370,7 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>SCN-033</v>
+        <v>SCN-032</v>
       </c>
       <c r="B237" t="str">
         <v/>
@@ -8385,13 +8385,13 @@
         <v/>
       </c>
       <c r="F237" t="str">
-        <v>동행 유형 선택</v>
+        <v>예외 요청 안내</v>
       </c>
       <c r="G237" t="str">
-        <v>'후기 작성' 화면에서 동행 유형 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '취소 불가 안내' 화면이 나오게 한 뒤, 예외 요청 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H237" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I237" t="str">
         <v/>
@@ -8402,7 +8402,7 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>SCN-033</v>
+        <v>SCN-032</v>
       </c>
       <c r="B238" t="str">
         <v/>
@@ -8417,13 +8417,13 @@
         <v/>
       </c>
       <c r="F238" t="str">
-        <v>포인트 지급 안내</v>
+        <v>고객센터 연결</v>
       </c>
       <c r="G238" t="str">
-        <v>'후기 작성' 화면에서 포인트 지급 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '취소 불가 안내' 화면이 나오게 한 뒤, 고객센터 연결이 보이는지 확인한다.</v>
       </c>
       <c r="H238" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I238" t="str">
         <v/>
@@ -8434,25 +8434,25 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B239" t="str">
         <v>마이페이지</v>
       </c>
       <c r="C239" t="str">
-        <v>쿠폰함</v>
+        <v>후기 작성</v>
       </c>
       <c r="D239" t="str">
-        <v>MY-09</v>
+        <v>MY-08</v>
       </c>
       <c r="E239" t="str">
         <v>기본</v>
       </c>
       <c r="F239" t="str">
-        <v>사용 가능</v>
+        <v>별점 선택</v>
       </c>
       <c r="G239" t="str">
-        <v>'쿠폰함' 화면에서 사용 가능이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'후기 작성' 화면에서 별점 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H239" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8466,7 +8466,7 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B240" t="str">
         <v/>
@@ -8481,10 +8481,10 @@
         <v/>
       </c>
       <c r="F240" t="str">
-        <v>사용 완료</v>
+        <v>세부 항목 평가(가이드·일정·가격만족도)</v>
       </c>
       <c r="G240" t="str">
-        <v>'쿠폰함' 화면에서 사용 완료가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'후기 작성' 화면에서 세부 항목 평가(가이드·일정·가격만족도)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H240" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8498,7 +8498,7 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B241" t="str">
         <v/>
@@ -8513,13 +8513,13 @@
         <v/>
       </c>
       <c r="F241" t="str">
-        <v>만료 탭</v>
+        <v>본문 입력(글자수 안내)</v>
       </c>
       <c r="G241" t="str">
-        <v>'쿠폰함'에서 만료 탭의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'후기 작성'의 본문 입력(글자수 안내)에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H241" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I241" t="str">
         <v/>
@@ -8530,7 +8530,7 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B242" t="str">
         <v/>
@@ -8545,13 +8545,13 @@
         <v/>
       </c>
       <c r="F242" t="str">
-        <v>쿠폰 카드(할인율·최소금액·유효기간·적용 대상)</v>
+        <v>사진 첨부 최대 5장</v>
       </c>
       <c r="G242" t="str">
-        <v>'쿠폰함'의 쿠폰 카드(할인율·최소금액·유효기간·적용 대상)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'후기 작성' 화면을 열고 사진 첨부 최대 5장이 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H242" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I242" t="str">
         <v/>
@@ -8562,7 +8562,7 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B243" t="str">
         <v/>
@@ -8577,10 +8577,10 @@
         <v/>
       </c>
       <c r="F243" t="str">
-        <v>만료 임박 강조</v>
+        <v>동행 유형 선택</v>
       </c>
       <c r="G243" t="str">
-        <v>'쿠폰함' 화면에서 만료 임박 강조가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'후기 작성' 화면에서 동행 유형 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H243" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8594,7 +8594,7 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B244" t="str">
         <v/>
@@ -8609,13 +8609,13 @@
         <v/>
       </c>
       <c r="F244" t="str">
-        <v>쿠폰 코드 등록</v>
+        <v>포인트 지급 안내</v>
       </c>
       <c r="G244" t="str">
-        <v>'쿠폰함'의 쿠폰 코드 등록에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'후기 작성' 화면에서 포인트 지급 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H244" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I244" t="str">
         <v/>
@@ -8626,28 +8626,28 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B245" t="str">
         <v>마이페이지</v>
       </c>
       <c r="C245" t="str">
-        <v>내 여정</v>
+        <v>쿠폰함</v>
       </c>
       <c r="D245" t="str">
-        <v>MY-10</v>
+        <v>MY-09</v>
       </c>
       <c r="E245" t="str">
         <v>기본</v>
       </c>
       <c r="F245" t="str">
-        <v>여행 단위 카드(도시·기간·예약 건수)</v>
+        <v>사용 가능</v>
       </c>
       <c r="G245" t="str">
-        <v>'내 여정'의 여행 단위 카드(도시·기간·예약 건수)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'쿠폰함' 화면에서 사용 가능이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H245" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I245" t="str">
         <v/>
@@ -8658,7 +8658,7 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B246" t="str">
         <v/>
@@ -8673,10 +8673,10 @@
         <v/>
       </c>
       <c r="F246" t="str">
-        <v>날짜별 타임라인에 예약을 시간순 배치</v>
+        <v>사용 완료</v>
       </c>
       <c r="G246" t="str">
-        <v>'내 여정' 화면에서 날짜별 타임라인에 예약을 시간순 배치가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'쿠폰함' 화면에서 사용 완료가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H246" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8690,7 +8690,7 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B247" t="str">
         <v/>
@@ -8705,13 +8705,13 @@
         <v/>
       </c>
       <c r="F247" t="str">
-        <v>시간이 겹치는 예약 경고</v>
+        <v>만료 탭</v>
       </c>
       <c r="G247" t="str">
-        <v>'내 여정' 화면에서 시간이 겹치는 예약 경고가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'쿠폰함'에서 만료 탭의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H247" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I247" t="str">
         <v/>
@@ -8722,7 +8722,7 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B248" t="str">
         <v/>
@@ -8737,13 +8737,13 @@
         <v/>
       </c>
       <c r="F248" t="str">
-        <v>앞뒤 일정 사이 이동 시간 여유 안내</v>
+        <v>쿠폰 카드(할인율·최소금액·유효기간·적용 대상)</v>
       </c>
       <c r="G248" t="str">
-        <v>'내 여정'에서 앞뒤 일정 사이 이동 시간 여유 안내를 눌러 본다.</v>
+        <v>'쿠폰함'의 쿠폰 카드(할인율·최소금액·유효기간·적용 대상)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H248" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I248" t="str">
         <v/>
@@ -8754,7 +8754,7 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B249" t="str">
         <v/>
@@ -8769,13 +8769,13 @@
         <v/>
       </c>
       <c r="F249" t="str">
-        <v>현지 시각과 한국 시차 표시</v>
+        <v>만료 임박 강조</v>
       </c>
       <c r="G249" t="str">
-        <v>'내 여정'의 현지 시각과 한국 시차 표시가 실제 데이터와 같은지 대조한다.</v>
+        <v>'쿠폰함' 화면에서 만료 임박 강조가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H249" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I249" t="str">
         <v/>
@@ -8786,7 +8786,7 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B250" t="str">
         <v/>
@@ -8801,13 +8801,13 @@
         <v/>
       </c>
       <c r="F250" t="str">
-        <v>빈 시간대에 추천 상품 노출</v>
+        <v>쿠폰 코드 등록</v>
       </c>
       <c r="G250" t="str">
-        <v>'내 여정' 화면에서 빈 시간대에 추천 상품 노출이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'쿠폰함'의 쿠폰 코드 등록에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H250" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I250" t="str">
         <v/>
@@ -8821,25 +8821,25 @@
         <v>SCN-035</v>
       </c>
       <c r="B251" t="str">
-        <v/>
+        <v>마이페이지</v>
       </c>
       <c r="C251" t="str">
-        <v/>
+        <v>내 여정</v>
       </c>
       <c r="D251" t="str">
-        <v/>
+        <v>MY-10</v>
       </c>
       <c r="E251" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F251" t="str">
-        <v>일정별 바우처</v>
+        <v>여행 단위 카드(도시·기간·예약 건수)</v>
       </c>
       <c r="G251" t="str">
-        <v>'내 여정' 화면에서 일정별 바우처가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 여정'의 여행 단위 카드(도시·기간·예약 건수)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H251" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I251" t="str">
         <v/>
@@ -8865,13 +8865,13 @@
         <v/>
       </c>
       <c r="F252" t="str">
-        <v>예약 상세 바로가기</v>
+        <v>날짜별 타임라인에 예약을 시간순 배치</v>
       </c>
       <c r="G252" t="str">
-        <v>'내 여정'에서 예약 상세 바로가기를 눌러 본다.</v>
+        <v>'내 여정' 화면에서 날짜별 타임라인에 예약을 시간순 배치가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H252" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I252" t="str">
         <v/>
@@ -8897,10 +8897,10 @@
         <v/>
       </c>
       <c r="F253" t="str">
-        <v>당일 날씨와 준비물 체크</v>
+        <v>시간이 겹치는 예약 경고</v>
       </c>
       <c r="G253" t="str">
-        <v>'내 여정' 화면에서 당일 날씨와 준비물 체크가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 여정' 화면에서 시간이 겹치는 예약 경고가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H253" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8929,13 +8929,13 @@
         <v/>
       </c>
       <c r="F254" t="str">
-        <v>동행자에게 일정 공유</v>
+        <v>앞뒤 일정 사이 이동 시간 여유 안내</v>
       </c>
       <c r="G254" t="str">
-        <v>'내 여정' 화면에서 동행자에게 일정 공유가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 여정'에서 앞뒤 일정 사이 이동 시간 여유 안내를 눌러 본다.</v>
       </c>
       <c r="H254" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I254" t="str">
         <v/>
@@ -8961,13 +8961,13 @@
         <v/>
       </c>
       <c r="F255" t="str">
-        <v>일정표 이미지</v>
+        <v>현지 시각과 한국 시차 표시</v>
       </c>
       <c r="G255" t="str">
-        <v>'내 여정' 화면에서 일정표 이미지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 여정'의 현지 시각과 한국 시차 표시가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H255" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I255" t="str">
         <v/>
@@ -8993,10 +8993,10 @@
         <v/>
       </c>
       <c r="F256" t="str">
-        <v>PDF 저장</v>
+        <v>빈 시간대에 추천 상품 노출</v>
       </c>
       <c r="G256" t="str">
-        <v>'내 여정' 화면에서 PDF 저장이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 여정' 화면에서 빈 시간대에 추천 상품 노출이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H256" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9010,28 +9010,28 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B257" t="str">
-        <v>마이페이지</v>
+        <v/>
       </c>
       <c r="C257" t="str">
-        <v>내 후기</v>
+        <v/>
       </c>
       <c r="D257" t="str">
-        <v>MY-11</v>
+        <v/>
       </c>
       <c r="E257" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F257" t="str">
-        <v>작성 가능</v>
+        <v>일정별 바우처</v>
       </c>
       <c r="G257" t="str">
-        <v>'내 후기'의 작성 가능에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'내 여정' 화면에서 일정별 바우처가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H257" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I257" t="str">
         <v/>
@@ -9042,7 +9042,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B258" t="str">
         <v/>
@@ -9057,13 +9057,13 @@
         <v/>
       </c>
       <c r="F258" t="str">
-        <v>작성 완료 탭</v>
+        <v>예약 상세 바로가기</v>
       </c>
       <c r="G258" t="str">
-        <v>'내 후기'의 작성 완료 탭에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'내 여정'에서 예약 상세 바로가기를 눌러 본다.</v>
       </c>
       <c r="H258" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I258" t="str">
         <v/>
@@ -9074,7 +9074,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B259" t="str">
         <v/>
@@ -9089,13 +9089,13 @@
         <v/>
       </c>
       <c r="F259" t="str">
-        <v>미작성 후기 카드(상품·이용일·작성 기한 D-day)</v>
+        <v>당일 날씨와 준비물 체크</v>
       </c>
       <c r="G259" t="str">
-        <v>'내 후기'의 미작성 후기 카드(상품·이용일·작성 기한 D-day)에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'내 여정' 화면에서 당일 날씨와 준비물 체크가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H259" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I259" t="str">
         <v/>
@@ -9106,7 +9106,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B260" t="str">
         <v/>
@@ -9121,13 +9121,13 @@
         <v/>
       </c>
       <c r="F260" t="str">
-        <v>작성한 후기 목록(별점·본문·사진·작성일)</v>
+        <v>동행자에게 일정 공유</v>
       </c>
       <c r="G260" t="str">
-        <v>'내 후기'의 작성한 후기 목록(별점·본문·사진·작성일)에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'내 여정' 화면에서 동행자에게 일정 공유가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H260" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I260" t="str">
         <v/>
@@ -9138,7 +9138,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B261" t="str">
         <v/>
@@ -9153,10 +9153,10 @@
         <v/>
       </c>
       <c r="F261" t="str">
-        <v>후기 수정과 삭제</v>
+        <v>일정표 이미지</v>
       </c>
       <c r="G261" t="str">
-        <v>'내 후기' 화면에서 후기 수정과 삭제가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 여정' 화면에서 일정표 이미지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H261" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9170,7 +9170,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B262" t="str">
         <v/>
@@ -9185,13 +9185,13 @@
         <v/>
       </c>
       <c r="F262" t="str">
-        <v>판매자 답변 표시</v>
+        <v>PDF 저장</v>
       </c>
       <c r="G262" t="str">
-        <v>'내 후기'의 판매자 답변 표시가 실제 데이터와 같은지 대조한다.</v>
+        <v>'내 여정' 화면에서 PDF 저장이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H262" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I262" t="str">
         <v/>
@@ -9205,25 +9205,25 @@
         <v>SCN-036</v>
       </c>
       <c r="B263" t="str">
-        <v/>
+        <v>마이페이지</v>
       </c>
       <c r="C263" t="str">
-        <v/>
+        <v>내 후기</v>
       </c>
       <c r="D263" t="str">
-        <v/>
+        <v>MY-11</v>
       </c>
       <c r="E263" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F263" t="str">
-        <v>받은 도움돼요 수</v>
+        <v>작성 가능</v>
       </c>
       <c r="G263" t="str">
-        <v>'내 후기' 화면에서 받은 도움돼요 수가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 후기'의 작성 가능에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H263" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I263" t="str">
         <v/>
@@ -9249,13 +9249,13 @@
         <v/>
       </c>
       <c r="F264" t="str">
-        <v>후기로 받은 포인트 합계</v>
+        <v>작성 완료 탭</v>
       </c>
       <c r="G264" t="str">
-        <v>'내 후기'의 후기로 받은 포인트 합계가 실제 데이터와 같은지 대조한다.</v>
+        <v>'내 후기'의 작성 완료 탭에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H264" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I264" t="str">
         <v/>
@@ -9281,10 +9281,10 @@
         <v/>
       </c>
       <c r="F265" t="str">
-        <v>작성 기한 만료 안내</v>
+        <v>미작성 후기 카드(상품·이용일·작성 기한 D-day)</v>
       </c>
       <c r="G265" t="str">
-        <v>'내 후기'의 작성 기한 만료 안내에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'내 후기'의 미작성 후기 카드(상품·이용일·작성 기한 D-day)에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H265" t="str">
         <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
@@ -9313,13 +9313,13 @@
         <v/>
       </c>
       <c r="F266" t="str">
-        <v>후기가 없을 때 빈 상태</v>
+        <v>작성한 후기 목록(별점·본문·사진·작성일)</v>
       </c>
       <c r="G266" t="str">
-        <v>'내 후기'의 후기가 없을 때 빈 상태가 실제 데이터와 같은지 대조한다.</v>
+        <v>'내 후기'의 작성한 후기 목록(별점·본문·사진·작성일)에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H266" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I266" t="str">
         <v/>
@@ -9345,13 +9345,13 @@
         <v/>
       </c>
       <c r="F267" t="str">
-        <v>상품 상세로 이동</v>
+        <v>후기 수정과 삭제</v>
       </c>
       <c r="G267" t="str">
-        <v>'내 후기'에서 상품 상세로 이동을 눌러 본다.</v>
+        <v>'내 후기' 화면에서 후기 수정과 삭제가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H267" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I267" t="str">
         <v/>
@@ -9362,28 +9362,28 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B268" t="str">
-        <v>마이페이지</v>
+        <v/>
       </c>
       <c r="C268" t="str">
-        <v>알림함</v>
+        <v/>
       </c>
       <c r="D268" t="str">
-        <v>MY-12</v>
+        <v/>
       </c>
       <c r="E268" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F268" t="str">
-        <v>전체</v>
+        <v>판매자 답변 표시</v>
       </c>
       <c r="G268" t="str">
-        <v>'알림함' 화면에서 전체가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 후기'의 판매자 답변 표시가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H268" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I268" t="str">
         <v/>
@@ -9394,7 +9394,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B269" t="str">
         <v/>
@@ -9409,10 +9409,10 @@
         <v/>
       </c>
       <c r="F269" t="str">
-        <v>예약</v>
+        <v>받은 도움돼요 수</v>
       </c>
       <c r="G269" t="str">
-        <v>'알림함' 화면에서 예약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 후기' 화면에서 받은 도움돼요 수가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H269" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9426,7 +9426,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B270" t="str">
         <v/>
@@ -9441,13 +9441,13 @@
         <v/>
       </c>
       <c r="F270" t="str">
-        <v>혜택</v>
+        <v>후기로 받은 포인트 합계</v>
       </c>
       <c r="G270" t="str">
-        <v>'알림함' 화면에서 혜택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 후기'의 후기로 받은 포인트 합계가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H270" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I270" t="str">
         <v/>
@@ -9458,7 +9458,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B271" t="str">
         <v/>
@@ -9473,13 +9473,13 @@
         <v/>
       </c>
       <c r="F271" t="str">
-        <v>공지 탭</v>
+        <v>작성 기한 만료 안내</v>
       </c>
       <c r="G271" t="str">
-        <v>'알림함'에서 공지 탭의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'내 후기'의 작성 기한 만료 안내에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H271" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I271" t="str">
         <v/>
@@ -9490,7 +9490,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B272" t="str">
         <v/>
@@ -9505,13 +9505,13 @@
         <v/>
       </c>
       <c r="F272" t="str">
-        <v>알림 카드(아이콘·제목·본문 요약·받은 시각)</v>
+        <v>후기가 없을 때 빈 상태</v>
       </c>
       <c r="G272" t="str">
-        <v>'알림함'의 알림 카드(아이콘·제목·본문 요약·받은 시각)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'내 후기'의 후기가 없을 때 빈 상태가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H272" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I272" t="str">
         <v/>
@@ -9522,7 +9522,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B273" t="str">
         <v/>
@@ -9537,13 +9537,13 @@
         <v/>
       </c>
       <c r="F273" t="str">
-        <v>읽지 않음 점 표시와 모두 읽음 처리</v>
+        <v>상품 상세로 이동</v>
       </c>
       <c r="G273" t="str">
-        <v>'알림함'의 읽지 않음 점 표시와 모두 읽음 처리가 실제 데이터와 같은지 대조한다.</v>
+        <v>'내 후기'에서 상품 상세로 이동을 눌러 본다.</v>
       </c>
       <c r="H273" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I273" t="str">
         <v/>
@@ -9557,25 +9557,25 @@
         <v>SCN-037</v>
       </c>
       <c r="B274" t="str">
-        <v/>
+        <v>마이페이지</v>
       </c>
       <c r="C274" t="str">
-        <v/>
+        <v>알림함</v>
       </c>
       <c r="D274" t="str">
-        <v/>
+        <v>MY-12</v>
       </c>
       <c r="E274" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F274" t="str">
-        <v>알림별 관련 화면 바로가기</v>
+        <v>전체</v>
       </c>
       <c r="G274" t="str">
-        <v>'알림함'에서 알림별 관련 화면 바로가기를 눌러 본다.</v>
+        <v>'알림함' 화면에서 전체가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H274" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I274" t="str">
         <v/>
@@ -9601,10 +9601,10 @@
         <v/>
       </c>
       <c r="F275" t="str">
-        <v>출발 임박</v>
+        <v>예약</v>
       </c>
       <c r="G275" t="str">
-        <v>'알림함' 화면에서 출발 임박이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'알림함' 화면에서 예약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H275" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9633,10 +9633,10 @@
         <v/>
       </c>
       <c r="F276" t="str">
-        <v>확정 알림 상단 고정</v>
+        <v>혜택</v>
       </c>
       <c r="G276" t="str">
-        <v>'알림함' 화면에서 확정 알림 상단 고정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'알림함' 화면에서 혜택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H276" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9665,13 +9665,13 @@
         <v/>
       </c>
       <c r="F277" t="str">
-        <v>현지 이슈 알림 붉게 강조</v>
+        <v>공지 탭</v>
       </c>
       <c r="G277" t="str">
-        <v>'알림함' 화면에서 현지 이슈 알림 붉게 강조가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'알림함'에서 공지 탭의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H277" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I277" t="str">
         <v/>
@@ -9697,13 +9697,13 @@
         <v/>
       </c>
       <c r="F278" t="str">
-        <v>개별 삭제와 전체 비우기</v>
+        <v>알림 카드(아이콘·제목·본문 요약·받은 시각)</v>
       </c>
       <c r="G278" t="str">
-        <v>'알림함' 화면에서 개별 삭제와 전체 비우기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'알림함'의 알림 카드(아이콘·제목·본문 요약·받은 시각)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H278" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I278" t="str">
         <v/>
@@ -9729,13 +9729,13 @@
         <v/>
       </c>
       <c r="F279" t="str">
-        <v>알림 수신 설정 바로가기</v>
+        <v>읽지 않음 점 표시와 모두 읽음 처리</v>
       </c>
       <c r="G279" t="str">
-        <v>'알림함'에서 알림 수신 설정 바로가기를 눌러 본다.</v>
+        <v>'알림함'의 읽지 않음 점 표시와 모두 읽음 처리가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H279" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I279" t="str">
         <v/>
@@ -9761,13 +9761,13 @@
         <v/>
       </c>
       <c r="F280" t="str">
-        <v>30일 지난 알림 자동 삭제 안내</v>
+        <v>알림별 관련 화면 바로가기</v>
       </c>
       <c r="G280" t="str">
-        <v>'알림함' 화면에서 30일 지난 알림 자동 삭제 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'알림함'에서 알림별 관련 화면 바로가기를 눌러 본다.</v>
       </c>
       <c r="H280" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I280" t="str">
         <v/>
@@ -9793,13 +9793,13 @@
         <v/>
       </c>
       <c r="F281" t="str">
-        <v>알림이 없을 때 빈 상태</v>
+        <v>출발 임박</v>
       </c>
       <c r="G281" t="str">
-        <v>'알림함'의 알림이 없을 때 빈 상태가 실제 데이터와 같은지 대조한다.</v>
+        <v>'알림함' 화면에서 출발 임박이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H281" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I281" t="str">
         <v/>
@@ -9810,28 +9810,28 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>SCN-038</v>
+        <v>SCN-037</v>
       </c>
       <c r="B282" t="str">
-        <v>마이페이지</v>
+        <v/>
       </c>
       <c r="C282" t="str">
-        <v>계정 설정</v>
+        <v/>
       </c>
       <c r="D282" t="str">
-        <v>MY-13</v>
+        <v/>
       </c>
       <c r="E282" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F282" t="str">
-        <v>프로필 정보 수정(이름·여권 영문명·연락처)</v>
+        <v>확정 알림 상단 고정</v>
       </c>
       <c r="G282" t="str">
-        <v>'계정 설정'의 프로필 정보 수정(이름·여권 영문명·연락처)가 실제 데이터와 같은지 대조한다.</v>
+        <v>'알림함' 화면에서 확정 알림 상단 고정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H282" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I282" t="str">
         <v/>
@@ -9842,7 +9842,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>SCN-038</v>
+        <v>SCN-037</v>
       </c>
       <c r="B283" t="str">
         <v/>
@@ -9857,10 +9857,10 @@
         <v/>
       </c>
       <c r="F283" t="str">
-        <v>이메일 변경과 인증 메일 발송</v>
+        <v>현지 이슈 알림 붉게 강조</v>
       </c>
       <c r="G283" t="str">
-        <v>'계정 설정' 화면에서 이메일 변경과 인증 메일 발송이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'알림함' 화면에서 현지 이슈 알림 붉게 강조가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H283" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9874,7 +9874,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>SCN-038</v>
+        <v>SCN-037</v>
       </c>
       <c r="B284" t="str">
         <v/>
@@ -9889,10 +9889,10 @@
         <v/>
       </c>
       <c r="F284" t="str">
-        <v>비밀번호 변경(현재·새 비밀번호·조건 표시)</v>
+        <v>개별 삭제와 전체 비우기</v>
       </c>
       <c r="G284" t="str">
-        <v>'계정 설정' 화면에서 비밀번호 변경(현재·새 비밀번호·조건 표시)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'알림함' 화면에서 개별 삭제와 전체 비우기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H284" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9906,7 +9906,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>SCN-038</v>
+        <v>SCN-037</v>
       </c>
       <c r="B285" t="str">
         <v/>
@@ -9921,13 +9921,13 @@
         <v/>
       </c>
       <c r="F285" t="str">
-        <v>소셜 계정 연결과 해제</v>
+        <v>알림 수신 설정 바로가기</v>
       </c>
       <c r="G285" t="str">
-        <v>'계정 설정' 화면에서 소셜 계정 연결과 해제가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'알림함'에서 알림 수신 설정 바로가기를 눌러 본다.</v>
       </c>
       <c r="H285" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I285" t="str">
         <v/>
@@ -9938,7 +9938,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>SCN-038</v>
+        <v>SCN-037</v>
       </c>
       <c r="B286" t="str">
         <v/>
@@ -9953,10 +9953,10 @@
         <v/>
       </c>
       <c r="F286" t="str">
-        <v>알림 수신 설정(카톡·이메일·앱 푸시 개별 토글)</v>
+        <v>30일 지난 알림 자동 삭제 안내</v>
       </c>
       <c r="G286" t="str">
-        <v>'계정 설정' 화면에서 알림 수신 설정(카톡·이메일·앱 푸시 개별 토글)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'알림함' 화면에서 30일 지난 알림 자동 삭제 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H286" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9970,7 +9970,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>SCN-038</v>
+        <v>SCN-037</v>
       </c>
       <c r="B287" t="str">
         <v/>
@@ -9985,13 +9985,13 @@
         <v/>
       </c>
       <c r="F287" t="str">
-        <v>마케팅 수신 동의와 변경 이력</v>
+        <v>알림이 없을 때 빈 상태</v>
       </c>
       <c r="G287" t="str">
-        <v>'계정 설정' 화면에서 마케팅 수신 동의와 변경 이력이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'알림함'의 알림이 없을 때 빈 상태가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H287" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I287" t="str">
         <v/>
@@ -10005,25 +10005,25 @@
         <v>SCN-038</v>
       </c>
       <c r="B288" t="str">
-        <v/>
+        <v>마이페이지</v>
       </c>
       <c r="C288" t="str">
-        <v/>
+        <v>계정 설정</v>
       </c>
       <c r="D288" t="str">
-        <v/>
+        <v>MY-13</v>
       </c>
       <c r="E288" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F288" t="str">
-        <v>표시 언어와 결제 통화 설정</v>
+        <v>프로필 정보 수정(이름·여권 영문명·연락처)</v>
       </c>
       <c r="G288" t="str">
-        <v>'계정 설정'에서 표시 언어와 결제 통화 설정을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'계정 설정'의 프로필 정보 수정(이름·여권 영문명·연락처)가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H288" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I288" t="str">
         <v/>
@@ -10049,13 +10049,13 @@
         <v/>
       </c>
       <c r="F289" t="str">
-        <v>자주 쓰는 여행자 정보 저장</v>
+        <v>이메일 변경과 인증 메일 발송</v>
       </c>
       <c r="G289" t="str">
-        <v>'계정 설정'의 자주 쓰는 여행자 정보 저장이 실제 데이터와 같은지 대조한다.</v>
+        <v>'계정 설정' 화면에서 이메일 변경과 인증 메일 발송이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H289" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I289" t="str">
         <v/>
@@ -10081,10 +10081,10 @@
         <v/>
       </c>
       <c r="F290" t="str">
-        <v>관리</v>
+        <v>비밀번호 변경(현재·새 비밀번호·조건 표시)</v>
       </c>
       <c r="G290" t="str">
-        <v>'계정 설정' 화면에서 관리가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'계정 설정' 화면에서 비밀번호 변경(현재·새 비밀번호·조건 표시)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H290" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10113,13 +10113,13 @@
         <v/>
       </c>
       <c r="F291" t="str">
-        <v>내 개인정보 내려받기</v>
+        <v>소셜 계정 연결과 해제</v>
       </c>
       <c r="G291" t="str">
-        <v>'계정 설정'의 내 개인정보 내려받기가 실제 데이터와 같은지 대조한다.</v>
+        <v>'계정 설정' 화면에서 소셜 계정 연결과 해제가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H291" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I291" t="str">
         <v/>
@@ -10145,10 +10145,10 @@
         <v/>
       </c>
       <c r="F292" t="str">
-        <v>회원 탈퇴와 유의사항</v>
+        <v>알림 수신 설정(카톡·이메일·앱 푸시 개별 토글)</v>
       </c>
       <c r="G292" t="str">
-        <v>'계정 설정' 화면에서 회원 탈퇴와 유의사항이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'계정 설정' 화면에서 알림 수신 설정(카톡·이메일·앱 푸시 개별 토글)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H292" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10162,28 +10162,28 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>SCN-039</v>
+        <v>SCN-038</v>
       </c>
       <c r="B293" t="str">
-        <v>고객센터</v>
+        <v/>
       </c>
       <c r="C293" t="str">
-        <v>자주 묻는 질문</v>
+        <v/>
       </c>
       <c r="D293" t="str">
-        <v>CS-01</v>
+        <v/>
       </c>
       <c r="E293" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F293" t="str">
-        <v>카테고리 탭(예약·결제·취소환불·바우처·현지이용)</v>
+        <v>마케팅 수신 동의와 변경 이력</v>
       </c>
       <c r="G293" t="str">
-        <v>'자주 묻는 질문'에서 카테고리 탭(예약·결제·취소환불·바우처·현지이용)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'계정 설정' 화면에서 마케팅 수신 동의와 변경 이력이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H293" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I293" t="str">
         <v/>
@@ -10194,7 +10194,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>SCN-039</v>
+        <v>SCN-038</v>
       </c>
       <c r="B294" t="str">
         <v/>
@@ -10209,13 +10209,13 @@
         <v/>
       </c>
       <c r="F294" t="str">
-        <v>검색창</v>
+        <v>표시 언어와 결제 통화 설정</v>
       </c>
       <c r="G294" t="str">
-        <v>'자주 묻는 질문'의 검색창에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'계정 설정'에서 표시 언어와 결제 통화 설정을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H294" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I294" t="str">
         <v/>
@@ -10226,7 +10226,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>SCN-039</v>
+        <v>SCN-038</v>
       </c>
       <c r="B295" t="str">
         <v/>
@@ -10241,13 +10241,13 @@
         <v/>
       </c>
       <c r="F295" t="str">
-        <v>아코디언 질문 목록</v>
+        <v>자주 쓰는 여행자 정보 저장</v>
       </c>
       <c r="G295" t="str">
-        <v>'자주 묻는 질문'의 아코디언 질문 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'계정 설정'의 자주 쓰는 여행자 정보 저장이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H295" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I295" t="str">
         <v/>
@@ -10258,7 +10258,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>SCN-039</v>
+        <v>SCN-038</v>
       </c>
       <c r="B296" t="str">
         <v/>
@@ -10273,13 +10273,13 @@
         <v/>
       </c>
       <c r="F296" t="str">
-        <v>도움됐어요 버튼</v>
+        <v>관리</v>
       </c>
       <c r="G296" t="str">
-        <v>'자주 묻는 질문'에서 도움됐어요 버튼을 눌러 본다.</v>
+        <v>'계정 설정' 화면에서 관리가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H296" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I296" t="str">
         <v/>
@@ -10290,7 +10290,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>SCN-039</v>
+        <v>SCN-038</v>
       </c>
       <c r="B297" t="str">
         <v/>
@@ -10305,13 +10305,13 @@
         <v/>
       </c>
       <c r="F297" t="str">
-        <v>문의하기 유도</v>
+        <v>내 개인정보 내려받기</v>
       </c>
       <c r="G297" t="str">
-        <v>'자주 묻는 질문' 화면에서 문의하기 유도가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'계정 설정'의 내 개인정보 내려받기가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H297" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I297" t="str">
         <v/>
@@ -10322,25 +10322,25 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>SCN-040</v>
+        <v>SCN-038</v>
       </c>
       <c r="B298" t="str">
-        <v>고객센터</v>
+        <v/>
       </c>
       <c r="C298" t="str">
-        <v>1:1 문의 작성</v>
+        <v/>
       </c>
       <c r="D298" t="str">
-        <v>CS-02</v>
+        <v/>
       </c>
       <c r="E298" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F298" t="str">
-        <v>문의 유형 선택</v>
+        <v>회원 탈퇴와 유의사항</v>
       </c>
       <c r="G298" t="str">
-        <v>'1:1 문의 작성' 화면에서 문의 유형 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'계정 설정' 화면에서 회원 탈퇴와 유의사항이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H298" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10354,28 +10354,28 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>SCN-040</v>
+        <v>SCN-039</v>
       </c>
       <c r="B299" t="str">
-        <v/>
+        <v>고객센터</v>
       </c>
       <c r="C299" t="str">
-        <v/>
+        <v>자주 묻는 질문</v>
       </c>
       <c r="D299" t="str">
-        <v/>
+        <v>CS-01</v>
       </c>
       <c r="E299" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F299" t="str">
-        <v>관련 예약 선택</v>
+        <v>카테고리 탭(예약·결제·취소환불·바우처·현지이용)</v>
       </c>
       <c r="G299" t="str">
-        <v>'1:1 문의 작성' 화면에서 관련 예약 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'자주 묻는 질문'에서 카테고리 탭(예약·결제·취소환불·바우처·현지이용)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H299" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I299" t="str">
         <v/>
@@ -10386,7 +10386,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>SCN-040</v>
+        <v>SCN-039</v>
       </c>
       <c r="B300" t="str">
         <v/>
@@ -10401,13 +10401,13 @@
         <v/>
       </c>
       <c r="F300" t="str">
-        <v>제목</v>
+        <v>검색창</v>
       </c>
       <c r="G300" t="str">
-        <v>'1:1 문의 작성' 화면에서 제목이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'자주 묻는 질문'의 검색창에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H300" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I300" t="str">
         <v/>
@@ -10418,7 +10418,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>SCN-040</v>
+        <v>SCN-039</v>
       </c>
       <c r="B301" t="str">
         <v/>
@@ -10433,13 +10433,13 @@
         <v/>
       </c>
       <c r="F301" t="str">
-        <v>내용 입력</v>
+        <v>아코디언 질문 목록</v>
       </c>
       <c r="G301" t="str">
-        <v>'1:1 문의 작성'의 내용 입력에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'자주 묻는 질문'의 아코디언 질문 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H301" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I301" t="str">
         <v/>
@@ -10450,7 +10450,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>SCN-040</v>
+        <v>SCN-039</v>
       </c>
       <c r="B302" t="str">
         <v/>
@@ -10465,13 +10465,13 @@
         <v/>
       </c>
       <c r="F302" t="str">
-        <v>파일 첨부</v>
+        <v>도움됐어요 버튼</v>
       </c>
       <c r="G302" t="str">
-        <v>'1:1 문의 작성'의 파일 첨부에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'자주 묻는 질문'에서 도움됐어요 버튼을 눌러 본다.</v>
       </c>
       <c r="H302" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I302" t="str">
         <v/>
@@ -10482,7 +10482,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>SCN-040</v>
+        <v>SCN-039</v>
       </c>
       <c r="B303" t="str">
         <v/>
@@ -10497,10 +10497,10 @@
         <v/>
       </c>
       <c r="F303" t="str">
-        <v>답변 받을 방법 선택</v>
+        <v>문의하기 유도</v>
       </c>
       <c r="G303" t="str">
-        <v>'1:1 문의 작성' 화면에서 답변 받을 방법 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'자주 묻는 질문' 화면에서 문의하기 유도가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H303" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10517,22 +10517,22 @@
         <v>SCN-040</v>
       </c>
       <c r="B304" t="str">
-        <v/>
+        <v>고객센터</v>
       </c>
       <c r="C304" t="str">
-        <v/>
+        <v>1:1 문의 작성</v>
       </c>
       <c r="D304" t="str">
-        <v/>
+        <v>CS-02</v>
       </c>
       <c r="E304" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F304" t="str">
-        <v>예상 답변 시간 안내</v>
+        <v>문의 유형 선택</v>
       </c>
       <c r="G304" t="str">
-        <v>'1:1 문의 작성' 화면에서 예상 답변 시간 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'1:1 문의 작성' 화면에서 문의 유형 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H304" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10546,28 +10546,28 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>SCN-041</v>
+        <v>SCN-040</v>
       </c>
       <c r="B305" t="str">
-        <v>고객센터</v>
+        <v/>
       </c>
       <c r="C305" t="str">
-        <v>문의 내역</v>
+        <v/>
       </c>
       <c r="D305" t="str">
-        <v>CS-03</v>
+        <v/>
       </c>
       <c r="E305" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F305" t="str">
-        <v>문의 목록(제목·유형·작성일·상태 배지)</v>
+        <v>관련 예약 선택</v>
       </c>
       <c r="G305" t="str">
-        <v>'문의 내역'의 문의 목록(제목·유형·작성일·상태 배지)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'1:1 문의 작성' 화면에서 관련 예약 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H305" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I305" t="str">
         <v/>
@@ -10578,7 +10578,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>SCN-041</v>
+        <v>SCN-040</v>
       </c>
       <c r="B306" t="str">
         <v/>
@@ -10593,13 +10593,13 @@
         <v/>
       </c>
       <c r="F306" t="str">
-        <v>답변 완료 여부 표시</v>
+        <v>제목</v>
       </c>
       <c r="G306" t="str">
-        <v>'문의 내역'의 답변 완료 여부 표시가 실제 데이터와 같은지 대조한다.</v>
+        <v>'1:1 문의 작성' 화면에서 제목이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H306" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I306" t="str">
         <v/>
@@ -10610,7 +10610,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>SCN-041</v>
+        <v>SCN-040</v>
       </c>
       <c r="B307" t="str">
         <v/>
@@ -10625,13 +10625,13 @@
         <v/>
       </c>
       <c r="F307" t="str">
-        <v>문의 상세 펼치기</v>
+        <v>내용 입력</v>
       </c>
       <c r="G307" t="str">
-        <v>'문의 내역' 화면에서 문의 상세 펼치기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'1:1 문의 작성'의 내용 입력에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H307" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I307" t="str">
         <v/>
@@ -10642,7 +10642,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>SCN-041</v>
+        <v>SCN-040</v>
       </c>
       <c r="B308" t="str">
         <v/>
@@ -10657,13 +10657,13 @@
         <v/>
       </c>
       <c r="F308" t="str">
-        <v>추가 질문 이어쓰기</v>
+        <v>파일 첨부</v>
       </c>
       <c r="G308" t="str">
-        <v>'문의 내역' 화면에서 추가 질문 이어쓰기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'1:1 문의 작성'의 파일 첨부에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H308" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I308" t="str">
         <v/>
@@ -10674,25 +10674,25 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>SCN-042</v>
+        <v>SCN-040</v>
       </c>
       <c r="B309" t="str">
-        <v>고객센터</v>
+        <v/>
       </c>
       <c r="C309" t="str">
-        <v>공지사항</v>
+        <v/>
       </c>
       <c r="D309" t="str">
-        <v>CS-04</v>
+        <v/>
       </c>
       <c r="E309" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F309" t="str">
-        <v>중요 공지 상단 고정</v>
+        <v>답변 받을 방법 선택</v>
       </c>
       <c r="G309" t="str">
-        <v>'공지사항' 화면에서 중요 공지 상단 고정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'1:1 문의 작성' 화면에서 답변 받을 방법 선택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H309" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10706,7 +10706,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>SCN-042</v>
+        <v>SCN-040</v>
       </c>
       <c r="B310" t="str">
         <v/>
@@ -10721,13 +10721,13 @@
         <v/>
       </c>
       <c r="F310" t="str">
-        <v>공지 목록(제목·작성일·카테고리)</v>
+        <v>예상 답변 시간 안내</v>
       </c>
       <c r="G310" t="str">
-        <v>'공지사항'의 공지 목록(제목·작성일·카테고리)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'1:1 문의 작성' 화면에서 예상 답변 시간 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H310" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I310" t="str">
         <v/>
@@ -10738,28 +10738,28 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>SCN-042</v>
+        <v>SCN-041</v>
       </c>
       <c r="B311" t="str">
-        <v/>
+        <v>고객센터</v>
       </c>
       <c r="C311" t="str">
-        <v/>
+        <v>문의 내역</v>
       </c>
       <c r="D311" t="str">
-        <v/>
+        <v>CS-03</v>
       </c>
       <c r="E311" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F311" t="str">
-        <v>상세 펼치기</v>
+        <v>문의 목록(제목·유형·작성일·상태 배지)</v>
       </c>
       <c r="G311" t="str">
-        <v>'공지사항' 화면에서 상세 펼치기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'문의 내역'의 문의 목록(제목·유형·작성일·상태 배지)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H311" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I311" t="str">
         <v/>
@@ -10770,7 +10770,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>SCN-042</v>
+        <v>SCN-041</v>
       </c>
       <c r="B312" t="str">
         <v/>
@@ -10785,13 +10785,13 @@
         <v/>
       </c>
       <c r="F312" t="str">
-        <v>현지 이슈 알림 배너</v>
+        <v>답변 완료 여부 표시</v>
       </c>
       <c r="G312" t="str">
-        <v>'공지사항'에서 현지 이슈 알림 배너를 눌러 본다.</v>
+        <v>'문의 내역'의 답변 완료 여부 표시가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H312" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I312" t="str">
         <v/>
@@ -10802,28 +10802,28 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>SCN-043</v>
+        <v>SCN-041</v>
       </c>
       <c r="B313" t="str">
-        <v>고객센터</v>
+        <v/>
       </c>
       <c r="C313" t="str">
-        <v>취소·환불 규정 안내</v>
+        <v/>
       </c>
       <c r="D313" t="str">
-        <v>CS-05</v>
+        <v/>
       </c>
       <c r="E313" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F313" t="str">
-        <v>상품 유형별 환불 규정 표(투어·입장권·패스)</v>
+        <v>문의 상세 펼치기</v>
       </c>
       <c r="G313" t="str">
-        <v>'취소·환불 규정 안내'에서 상품 유형별 환불 규정 표(투어·입장권·패스)를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'문의 내역' 화면에서 문의 상세 펼치기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H313" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I313" t="str">
         <v/>
@@ -10834,7 +10834,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>SCN-043</v>
+        <v>SCN-041</v>
       </c>
       <c r="B314" t="str">
         <v/>
@@ -10849,10 +10849,10 @@
         <v/>
       </c>
       <c r="F314" t="str">
-        <v>출발일 기준 수수료율 단계</v>
+        <v>추가 질문 이어쓰기</v>
       </c>
       <c r="G314" t="str">
-        <v>'취소·환불 규정 안내' 화면에서 출발일 기준 수수료율 단계가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'문의 내역' 화면에서 추가 질문 이어쓰기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H314" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10866,28 +10866,28 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>SCN-043</v>
+        <v>SCN-042</v>
       </c>
       <c r="B315" t="str">
-        <v/>
+        <v>고객센터</v>
       </c>
       <c r="C315" t="str">
-        <v/>
+        <v>공지사항</v>
       </c>
       <c r="D315" t="str">
-        <v/>
+        <v>CS-04</v>
       </c>
       <c r="E315" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F315" t="str">
-        <v>무료 취소 기한 계산 예시</v>
+        <v>중요 공지 상단 고정</v>
       </c>
       <c r="G315" t="str">
-        <v>'취소·환불 규정 안내'에서 무료 취소 기한 계산 예시를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'공지사항' 화면에서 중요 공지 상단 고정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H315" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I315" t="str">
         <v/>
@@ -10898,7 +10898,7 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>SCN-043</v>
+        <v>SCN-042</v>
       </c>
       <c r="B316" t="str">
         <v/>
@@ -10913,13 +10913,13 @@
         <v/>
       </c>
       <c r="F316" t="str">
-        <v>현지 시각 기준이라는 안내</v>
+        <v>공지 목록(제목·작성일·카테고리)</v>
       </c>
       <c r="G316" t="str">
-        <v>'취소·환불 규정 안내' 화면에서 현지 시각 기준이라는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공지사항'의 공지 목록(제목·작성일·카테고리)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H316" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I316" t="str">
         <v/>
@@ -10930,7 +10930,7 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>SCN-043</v>
+        <v>SCN-042</v>
       </c>
       <c r="B317" t="str">
         <v/>
@@ -10945,10 +10945,10 @@
         <v/>
       </c>
       <c r="F317" t="str">
-        <v>기상</v>
+        <v>상세 펼치기</v>
       </c>
       <c r="G317" t="str">
-        <v>'취소·환불 규정 안내' 화면에서 기상이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공지사항' 화면에서 상세 펼치기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H317" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10962,7 +10962,7 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>SCN-043</v>
+        <v>SCN-042</v>
       </c>
       <c r="B318" t="str">
         <v/>
@@ -10977,13 +10977,13 @@
         <v/>
       </c>
       <c r="F318" t="str">
-        <v>천재지변 취소 처리</v>
+        <v>현지 이슈 알림 배너</v>
       </c>
       <c r="G318" t="str">
-        <v>'취소·환불 규정 안내'에서 천재지변 취소 처리를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'공지사항'에서 현지 이슈 알림 배너를 눌러 본다.</v>
       </c>
       <c r="H318" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I318" t="str">
         <v/>
@@ -10997,22 +10997,22 @@
         <v>SCN-043</v>
       </c>
       <c r="B319" t="str">
-        <v/>
+        <v>고객센터</v>
       </c>
       <c r="C319" t="str">
-        <v/>
+        <v>취소·환불 규정 안내</v>
       </c>
       <c r="D319" t="str">
-        <v/>
+        <v>CS-05</v>
       </c>
       <c r="E319" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F319" t="str">
-        <v>최소 인원 미달 자동 취소와 전액 환불</v>
+        <v>상품 유형별 환불 규정 표(투어·입장권·패스)</v>
       </c>
       <c r="G319" t="str">
-        <v>'취소·환불 규정 안내'에서 최소 인원 미달 자동 취소와 전액 환불을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'취소·환불 규정 안내'에서 상품 유형별 환불 규정 표(투어·입장권·패스)를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H319" t="str">
         <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
@@ -11041,10 +11041,10 @@
         <v/>
       </c>
       <c r="F320" t="str">
-        <v>노쇼와 부분 사용 처리 기준</v>
+        <v>출발일 기준 수수료율 단계</v>
       </c>
       <c r="G320" t="str">
-        <v>'취소·환불 규정 안내' 화면에서 노쇼와 부분 사용 처리 기준이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'취소·환불 규정 안내' 화면에서 출발일 기준 수수료율 단계가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H320" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11073,10 +11073,10 @@
         <v/>
       </c>
       <c r="F321" t="str">
-        <v>환불 소요 기간과 결제 수단별 차이</v>
+        <v>무료 취소 기한 계산 예시</v>
       </c>
       <c r="G321" t="str">
-        <v>'취소·환불 규정 안내'에서 환불 소요 기간과 결제 수단별 차이를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'취소·환불 규정 안내'에서 무료 취소 기한 계산 예시를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H321" t="str">
         <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
@@ -11105,13 +11105,13 @@
         <v/>
       </c>
       <c r="F322" t="str">
-        <v>자주 묻는 취소 질문 5개</v>
+        <v>현지 시각 기준이라는 안내</v>
       </c>
       <c r="G322" t="str">
-        <v>'취소·환불 규정 안내'에서 자주 묻는 취소 질문 5개를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'취소·환불 규정 안내' 화면에서 현지 시각 기준이라는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H322" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I322" t="str">
         <v/>
@@ -11137,24 +11137,216 @@
         <v/>
       </c>
       <c r="F323" t="str">
+        <v>기상</v>
+      </c>
+      <c r="G323" t="str">
+        <v>'취소·환불 규정 안내' 화면에서 기상이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+      </c>
+      <c r="H323" t="str">
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+      </c>
+      <c r="I323" t="str">
+        <v/>
+      </c>
+      <c r="J323" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>SCN-043</v>
+      </c>
+      <c r="B324" t="str">
+        <v/>
+      </c>
+      <c r="C324" t="str">
+        <v/>
+      </c>
+      <c r="D324" t="str">
+        <v/>
+      </c>
+      <c r="E324" t="str">
+        <v/>
+      </c>
+      <c r="F324" t="str">
+        <v>천재지변 취소 처리</v>
+      </c>
+      <c r="G324" t="str">
+        <v>'취소·환불 규정 안내'에서 천재지변 취소 처리를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+      </c>
+      <c r="H324" t="str">
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+      </c>
+      <c r="I324" t="str">
+        <v/>
+      </c>
+      <c r="J324" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>SCN-043</v>
+      </c>
+      <c r="B325" t="str">
+        <v/>
+      </c>
+      <c r="C325" t="str">
+        <v/>
+      </c>
+      <c r="D325" t="str">
+        <v/>
+      </c>
+      <c r="E325" t="str">
+        <v/>
+      </c>
+      <c r="F325" t="str">
+        <v>최소 인원 미달 자동 취소와 전액 환불</v>
+      </c>
+      <c r="G325" t="str">
+        <v>'취소·환불 규정 안내'에서 최소 인원 미달 자동 취소와 전액 환불을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+      </c>
+      <c r="H325" t="str">
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+      </c>
+      <c r="I325" t="str">
+        <v/>
+      </c>
+      <c r="J325" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>SCN-043</v>
+      </c>
+      <c r="B326" t="str">
+        <v/>
+      </c>
+      <c r="C326" t="str">
+        <v/>
+      </c>
+      <c r="D326" t="str">
+        <v/>
+      </c>
+      <c r="E326" t="str">
+        <v/>
+      </c>
+      <c r="F326" t="str">
+        <v>노쇼와 부분 사용 처리 기준</v>
+      </c>
+      <c r="G326" t="str">
+        <v>'취소·환불 규정 안내' 화면에서 노쇼와 부분 사용 처리 기준이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+      </c>
+      <c r="H326" t="str">
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+      </c>
+      <c r="I326" t="str">
+        <v/>
+      </c>
+      <c r="J326" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>SCN-043</v>
+      </c>
+      <c r="B327" t="str">
+        <v/>
+      </c>
+      <c r="C327" t="str">
+        <v/>
+      </c>
+      <c r="D327" t="str">
+        <v/>
+      </c>
+      <c r="E327" t="str">
+        <v/>
+      </c>
+      <c r="F327" t="str">
+        <v>환불 소요 기간과 결제 수단별 차이</v>
+      </c>
+      <c r="G327" t="str">
+        <v>'취소·환불 규정 안내'에서 환불 소요 기간과 결제 수단별 차이를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+      </c>
+      <c r="H327" t="str">
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+      </c>
+      <c r="I327" t="str">
+        <v/>
+      </c>
+      <c r="J327" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>SCN-043</v>
+      </c>
+      <c r="B328" t="str">
+        <v/>
+      </c>
+      <c r="C328" t="str">
+        <v/>
+      </c>
+      <c r="D328" t="str">
+        <v/>
+      </c>
+      <c r="E328" t="str">
+        <v/>
+      </c>
+      <c r="F328" t="str">
+        <v>자주 묻는 취소 질문 5개</v>
+      </c>
+      <c r="G328" t="str">
+        <v>'취소·환불 규정 안내'에서 자주 묻는 취소 질문 5개를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+      </c>
+      <c r="H328" t="str">
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+      </c>
+      <c r="I328" t="str">
+        <v/>
+      </c>
+      <c r="J328" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v>SCN-043</v>
+      </c>
+      <c r="B329" t="str">
+        <v/>
+      </c>
+      <c r="C329" t="str">
+        <v/>
+      </c>
+      <c r="D329" t="str">
+        <v/>
+      </c>
+      <c r="E329" t="str">
+        <v/>
+      </c>
+      <c r="F329" t="str">
         <v>내 예약의 규정 바로 확인</v>
       </c>
-      <c r="G323" t="str">
+      <c r="G329" t="str">
         <v>'취소·환불 규정 안내' 화면에서 내 예약의 규정 바로 확인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
-      <c r="H323" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
-      </c>
-      <c r="I323" t="str">
-        <v/>
-      </c>
-      <c r="J323" t="str">
+      <c r="H329" t="str">
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+      </c>
+      <c r="I329" t="str">
+        <v/>
+      </c>
+      <c r="J329" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J323"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J329"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/판매용_템플릿/_판매팩/여행_디럭스/08_검수시나리오.xlsx
+++ b/판매용_템플릿/_판매팩/여행_디럭스/08_검수시나리오.xlsx
@@ -1412,10 +1412,10 @@
         <v>좁은 화면(모바일)에서 가로 스크롤</v>
       </c>
       <c r="G19" t="str">
-        <v>브라우저 폭을 375px로 좁혀 화면을 훑는다.</v>
+        <v>브라우저 폭을 390px 로 좁혀 화면을 훑고, 360px 로 한 번 더 훑는다. ⚠ 세로 flex 로 바꾼 상자의 자식이 밀리는 것은 390px 에서는 안 보이고 360px 에서만 나온다.</v>
       </c>
       <c r="H19" t="str">
-        <v>가로 스크롤이 생기지 않고, 내용이 화면 밖으로 나가지 않는다.</v>
+        <v>두 폭 모두에서 가로 스크롤이 생기지 않고, 내용이 화면 밖으로 나가지 않는다.</v>
       </c>
       <c r="I19" t="str">
         <v/>

--- a/판매용_템플릿/_판매팩/여행_디럭스/08_검수시나리오.xlsx
+++ b/판매용_템플릿/_판매팩/여행_디럭스/08_검수시나리오.xlsx
@@ -1572,7 +1572,7 @@
         <v>글자 대비 — 색을 고른 뒤 반드시 잰다</v>
       </c>
       <c r="G24" t="str">
-        <v>스펙팩 7-9-2 가 가리키는 대로 브라우저에서 잰다. ⚠ 반투명 배경(10% 배지 등)은 «쌓아서» 진짜 바탕색을 구한 뒤 재야 한다 — 알파를 빼고 재면 멀쩡한 배지가 미달로 잡힌다.</v>
+        <v>스펙팩 7-9 의 글을 화면에 붙여 넣으면 ⑧번이 잰다(7-9-2 는 파일만 보므로 대비를 재지 않는다). ⚠ 반투명 배경(10% 배지 등)은 «쌓아서» 진짜 바탕색을 구한 뒤 재야 한다 — 알파를 빼고 재면 멀쩡한 배지가 미달로 잡힌다.</v>
       </c>
       <c r="H24" t="str">
         <v>본문 4.5 이상, 24px 이상이거나 굵은 18.66px 이상은 3.0 이상. 미달 0건.</v>
